--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D74C49C-92AA-4F72-BC2D-58E98991FC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1432" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93002DCA-D76C-46DC-9743-074698C67C83}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="6" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="99">
   <si>
     <t>TOTAL</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>Tomate</t>
-  </si>
-  <si>
-    <t>Epifania Lopez</t>
   </si>
   <si>
     <t>VENTAS</t>
@@ -264,9 +261,6 @@
     <t>20260507-02</t>
   </si>
   <si>
-    <t>20260509-01</t>
-  </si>
-  <si>
     <t>Retorno Com</t>
   </si>
   <si>
@@ -289,12 +283,6 @@
   </si>
   <si>
     <t>20260505-01</t>
-  </si>
-  <si>
-    <t>20260508-02</t>
-  </si>
-  <si>
-    <t>20260508-03</t>
   </si>
   <si>
     <t>20260427-01</t>
@@ -332,21 +320,42 @@
   <si>
     <t>comision cxp</t>
   </si>
+  <si>
+    <t>20260509-01</t>
+  </si>
+  <si>
+    <t>20260508-03</t>
+  </si>
+  <si>
+    <t>20260508-02</t>
+  </si>
+  <si>
+    <t>Epifania Lopez</t>
+  </si>
+  <si>
+    <t>20260511-01</t>
+  </si>
+  <si>
+    <t>20260511-02</t>
+  </si>
+  <si>
+    <t>20260511-03</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="169" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,11 +993,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -999,31 +1008,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1032,10 +1041,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1047,16 +1056,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1065,22 +1074,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1089,16 +1098,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1107,22 +1116,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1131,7 +1140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1140,22 +1149,22 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,16 +1179,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1188,31 +1197,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1221,13 +1230,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1236,10 +1245,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1251,7 +1260,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1266,7 +1275,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1287,13 +1296,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1317,10 +1326,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1332,7 +1341,7 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1347,28 +1356,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1383,13 +1392,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1404,16 +1413,16 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="9" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1425,13 +1434,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1449,13 +1458,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1464,7 +1473,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1479,17 +1488,17 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1498,10 +1507,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,12 +1519,24 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -1894,7 +1915,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FC3981-8E5A-4436-B2C6-E1A6D261A1E4}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1925,7 +1946,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -1990,7 +2011,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2049,7 +2070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>46128</v>
       </c>
@@ -2114,7 +2135,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="24">
         <v>46128</v>
       </c>
@@ -2179,7 +2200,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>46128</v>
       </c>
@@ -2244,7 +2265,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="24">
         <v>46128</v>
       </c>
@@ -2310,7 +2331,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="24">
         <v>46128</v>
       </c>
@@ -2377,7 +2398,7 @@
         <v>99878.399999999994</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="24">
         <v>46129</v>
       </c>
@@ -2443,7 +2464,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="24">
         <v>46129</v>
       </c>
@@ -2510,7 +2531,7 @@
         <v>57283.199999999997</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="24">
         <v>46129</v>
       </c>
@@ -2576,7 +2597,7 @@
         <v>15134.4</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24">
         <v>46130</v>
       </c>
@@ -2643,7 +2664,7 @@
         <v>31487.4</v>
       </c>
     </row>
-    <row r="13" spans="2:22">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="24">
         <v>46130</v>
       </c>
@@ -2709,7 +2730,7 @@
         <v>39015</v>
       </c>
     </row>
-    <row r="14" spans="2:22">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="24">
         <v>46132</v>
       </c>
@@ -2777,7 +2798,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="24">
         <v>46132</v>
       </c>
@@ -2844,7 +2865,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="24">
         <v>46133</v>
       </c>
@@ -2883,7 +2904,9 @@
         <f t="shared" si="0"/>
         <v>54400</v>
       </c>
-      <c r="N16" s="27"/>
+      <c r="N16" s="27">
+        <v>0</v>
+      </c>
       <c r="O16" s="40">
         <f t="shared" si="1"/>
         <v>54400</v>
@@ -2908,7 +2931,7 @@
         <v>48960</v>
       </c>
     </row>
-    <row r="17" spans="2:21">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="118">
         <v>46133</v>
       </c>
@@ -2972,7 +2995,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:21">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="24">
         <v>46134</v>
       </c>
@@ -3037,7 +3060,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="19" spans="2:21">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="24">
         <v>46134</v>
       </c>
@@ -3102,7 +3125,7 @@
         <v>76377.600000000006</v>
       </c>
     </row>
-    <row r="20" spans="2:21">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="24">
         <v>46136</v>
       </c>
@@ -3168,7 +3191,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="21" spans="2:21">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="24">
         <v>46046</v>
       </c>
@@ -3234,7 +3257,7 @@
         <v>184977</v>
       </c>
     </row>
-    <row r="22" spans="2:21">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="24">
         <v>46137</v>
       </c>
@@ -3300,7 +3323,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="23" spans="2:21">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="24">
         <v>46142</v>
       </c>
@@ -3366,7 +3389,7 @@
         <v>3855.6</v>
       </c>
     </row>
-    <row r="24" spans="2:21">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="24">
         <v>46142</v>
       </c>
@@ -3432,7 +3455,7 @@
         <v>70502.399999999994</v>
       </c>
     </row>
-    <row r="25" spans="2:21">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="24">
         <v>46143</v>
       </c>
@@ -3498,7 +3521,7 @@
         <v>15912</v>
       </c>
     </row>
-    <row r="26" spans="2:21">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="24">
         <v>46146</v>
       </c>
@@ -3537,7 +3560,9 @@
         <f t="shared" si="0"/>
         <v>148512</v>
       </c>
-      <c r="N26" s="27"/>
+      <c r="N26" s="27">
+        <v>0</v>
+      </c>
       <c r="O26" s="40">
         <f t="shared" si="1"/>
         <v>148512</v>
@@ -3562,7 +3587,7 @@
         <v>133660.79999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:21">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="24">
         <v>46147</v>
       </c>
@@ -3601,7 +3626,9 @@
         <f t="shared" si="0"/>
         <v>59653</v>
       </c>
-      <c r="N27" s="27"/>
+      <c r="N27" s="27">
+        <v>0</v>
+      </c>
       <c r="O27" s="40">
         <f t="shared" si="1"/>
         <v>59653</v>
@@ -3626,7 +3653,7 @@
         <v>53687.7</v>
       </c>
     </row>
-    <row r="28" spans="2:21">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="24">
         <v>46149</v>
       </c>
@@ -3665,7 +3692,9 @@
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="N28" s="27"/>
+      <c r="N28" s="27">
+        <v>0</v>
+      </c>
       <c r="O28" s="40">
         <f t="shared" si="1"/>
         <v>136</v>
@@ -3690,7 +3719,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="29" spans="2:21">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="24">
         <v>46149</v>
       </c>
@@ -3729,7 +3758,9 @@
         <f t="shared" si="0"/>
         <v>7021</v>
       </c>
-      <c r="N29" s="27"/>
+      <c r="N29" s="27">
+        <v>0</v>
+      </c>
       <c r="O29" s="40">
         <f t="shared" si="1"/>
         <v>7021</v>
@@ -3754,7 +3785,7 @@
         <v>6318.9</v>
       </c>
     </row>
-    <row r="30" spans="2:21">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="24">
         <v>46150</v>
       </c>
@@ -3792,7 +3823,9 @@
         <f t="shared" si="0"/>
         <v>16320</v>
       </c>
-      <c r="N30" s="27"/>
+      <c r="N30" s="27">
+        <v>0</v>
+      </c>
       <c r="O30" s="40">
         <f t="shared" si="1"/>
         <v>16320</v>
@@ -3817,7 +3850,7 @@
         <v>14688</v>
       </c>
     </row>
-    <row r="31" spans="2:21">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -3862,7 +3895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:21">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -3907,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -3952,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -3997,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -4042,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -4087,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -4132,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -4177,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -4222,7 +4255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -4274,7 +4307,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -4319,7 +4352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -4365,7 +4398,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -4410,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -4457,7 +4490,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -4502,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -4547,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -4592,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -4637,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -4682,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -4727,7 +4760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -4772,7 +4805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -4817,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -4862,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -4907,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -4952,7 +4985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -4997,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -5042,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -5087,7 +5120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -5132,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -5177,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -5222,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -5267,7 +5300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -5314,7 +5347,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -5360,7 +5393,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -5406,7 +5439,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -5453,7 +5486,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -5499,7 +5532,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -5544,7 +5577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -5589,7 +5622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -5634,7 +5667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -5679,7 +5712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -5724,7 +5757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -5769,7 +5802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -5814,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -5859,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -5904,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -5949,7 +5982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -5994,7 +6027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -6039,7 +6072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -6084,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -6129,7 +6162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -6174,7 +6207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -6219,7 +6252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -6264,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -6312,7 +6345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -6357,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -6402,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -6447,7 +6480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -6492,7 +6525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -6537,7 +6570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -6582,7 +6615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -6627,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -6672,7 +6705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1">
+    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -6718,7 +6751,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -6763,7 +6796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -6808,7 +6841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -6853,7 +6886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -6898,7 +6931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -6943,7 +6976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -6988,7 +7021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -7033,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -7078,7 +7111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -7123,7 +7156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -7168,7 +7201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20">
+    <row r="105" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -7226,7 +7259,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BDE71B-B4DE-46F0-B853-4D73D3E1167B}">
   <dimension ref="A2:AC104"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -7257,7 +7290,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -7322,7 +7355,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -7381,7 +7414,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>46139</v>
       </c>
@@ -7446,7 +7479,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="24">
         <v>46151</v>
       </c>
@@ -7511,7 +7544,7 @@
         <v>5382</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="24"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -7558,7 +7591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="24"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
@@ -7605,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="24"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -7652,7 +7685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="24"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -7699,7 +7732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="24"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
@@ -7746,7 +7779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="24"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -7793,7 +7826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -7840,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:22">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="24"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -7887,7 +7920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:22">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -7936,7 +7969,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="24"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -7985,7 +8018,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -8032,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -8079,7 +8112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:20">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -8126,7 +8159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:20">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="24"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -8173,7 +8206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:20">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -8220,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -8267,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -8314,7 +8347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -8361,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -8408,7 +8441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -8455,7 +8488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -8502,7 +8535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -8549,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -8596,7 +8629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -8643,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -8690,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -8737,7 +8770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -8784,7 +8817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -8831,7 +8864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -8878,7 +8911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -8925,7 +8958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -8972,7 +9005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -9019,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -9066,7 +9099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -9120,7 +9153,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -9167,7 +9200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -9215,7 +9248,7 @@
       </c>
       <c r="Z41" s="35"/>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -9262,7 +9295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -9311,7 +9344,7 @@
       <c r="V43" s="34"/>
       <c r="W43" s="35"/>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -9358,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -9405,7 +9438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -9452,7 +9485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -9499,7 +9532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -9546,7 +9579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -9593,7 +9626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -9640,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -9687,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -9734,7 +9767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -9781,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -9828,7 +9861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -9875,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -9922,7 +9955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -9969,7 +10002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -10016,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -10063,7 +10096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -10110,7 +10143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -10157,7 +10190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -10206,7 +10239,7 @@
       <c r="U62" s="37"/>
       <c r="V62" s="105"/>
     </row>
-    <row r="63" spans="2:22">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -10254,7 +10287,7 @@
       </c>
       <c r="U63" s="37"/>
     </row>
-    <row r="64" spans="2:22">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -10302,7 +10335,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -10351,7 +10384,7 @@
       <c r="U65" s="37"/>
       <c r="V65" s="106"/>
     </row>
-    <row r="66" spans="2:22">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -10399,7 +10432,7 @@
       </c>
       <c r="U66" s="37"/>
     </row>
-    <row r="67" spans="2:22">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -10446,7 +10479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:22">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -10493,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -10540,7 +10573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -10587,7 +10620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -10634,7 +10667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -10681,7 +10714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -10728,7 +10761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -10775,7 +10808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -10822,7 +10855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -10869,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -10916,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -10963,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -11010,7 +11043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -11057,7 +11090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -11104,7 +11137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -11151,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -11198,7 +11231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="36">
         <v>46057</v>
       </c>
@@ -11248,7 +11281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
@@ -11295,7 +11328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -11342,7 +11375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -11389,7 +11422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -11436,7 +11469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -11483,7 +11516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -11530,7 +11563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -11577,7 +11610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -11624,7 +11657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="2" customFormat="1">
+    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -11672,7 +11705,7 @@
       </c>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -11719,7 +11752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -11766,7 +11799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -11813,7 +11846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -11860,7 +11893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -11907,7 +11940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -11954,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -12001,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -12048,7 +12081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -12095,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -12142,7 +12175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -12202,7 +12235,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631DB7E5-46D0-410B-A49E-BCCBB7DAB626}">
   <dimension ref="A2:AC104"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -12233,7 +12266,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -12242,11 +12275,11 @@
       </c>
       <c r="G2" s="4">
         <f>SUM(G4:G494)</f>
-        <v>971</v>
+        <v>1250</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(H4:H494)</f>
-        <v>971</v>
+        <v>1250</v>
       </c>
       <c r="I2" s="6">
         <f>SUM(I4:I494)</f>
@@ -12258,15 +12291,15 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>512.4664232749742</v>
+        <v>478.05431040000002</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>33.494537468952572</v>
+        <v>31.245379764705884</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M494)</f>
-        <v>552894.33000000007</v>
+        <v>663964.32000000007</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N494)</f>
@@ -12274,7 +12307,7 @@
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O494)</f>
-        <v>552894.33000000007</v>
+        <v>663964.32000000007</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
@@ -12282,11 +12315,11 @@
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q494)</f>
-        <v>55289.433000000005</v>
+        <v>66396.432000000001</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R494)</f>
-        <v>497604.897</v>
+        <v>597567.88800000004</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S494)</f>
@@ -12294,11 +12327,11 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T494)</f>
-        <v>497604.897</v>
+        <v>597567.88800000004</v>
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -12357,7 +12390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>46135</v>
       </c>
@@ -12422,7 +12455,7 @@
         <v>18360</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="24">
         <v>46140</v>
       </c>
@@ -12487,7 +12520,7 @@
         <v>48802.256999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>46142</v>
       </c>
@@ -12552,7 +12585,7 @@
         <v>58914.108</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="24">
         <v>46144</v>
       </c>
@@ -12617,7 +12650,7 @@
         <v>99854.937000000005</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="24">
         <v>46147</v>
       </c>
@@ -12683,7 +12716,7 @@
         <v>121355.59499999999</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="24">
         <v>46149</v>
       </c>
@@ -12748,7 +12781,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="24">
         <v>46150</v>
       </c>
@@ -12813,7 +12846,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="24">
         <v>46150</v>
       </c>
@@ -12878,7 +12911,7 @@
         <v>97200</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24">
         <v>46153</v>
       </c>
@@ -12889,7 +12922,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>34</v>
@@ -12943,43 +12976,61 @@
         <v>30960</v>
       </c>
     </row>
-    <row r="13" spans="2:22">
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="20"/>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="24">
+        <v>46153</v>
+      </c>
+      <c r="C13" s="25">
+        <v>43</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="26">
+        <v>39</v>
+      </c>
+      <c r="H13" s="20">
+        <v>39</v>
+      </c>
       <c r="I13" s="44"/>
       <c r="J13" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K13" s="27"/>
+      <c r="K13" s="27">
+        <v>386.41</v>
+      </c>
       <c r="L13" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="M13" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15069.990000000002</v>
       </c>
       <c r="N13" s="27">
         <v>0</v>
       </c>
       <c r="O13" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="22"/>
+        <v>15069.990000000002</v>
+      </c>
+      <c r="P13" s="22">
+        <v>0.1</v>
+      </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1506.9990000000003</v>
       </c>
       <c r="R13" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13562.991000000002</v>
       </c>
       <c r="S13" s="40">
         <f t="shared" si="3"/>
@@ -12987,46 +13038,64 @@
       </c>
       <c r="T13" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22">
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="20"/>
+        <v>13562.991000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="24">
+        <v>46153</v>
+      </c>
+      <c r="C14" s="25">
+        <v>44</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="26">
+        <v>240</v>
+      </c>
+      <c r="H14" s="20">
+        <v>240</v>
+      </c>
       <c r="I14" s="19"/>
       <c r="J14" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="27">
+        <v>400</v>
+      </c>
       <c r="L14" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.529411764705884</v>
       </c>
       <c r="M14" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="N14" s="27">
         <v>0</v>
       </c>
       <c r="O14" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="22"/>
+        <v>96000</v>
+      </c>
+      <c r="P14" s="22">
+        <v>0.1</v>
+      </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="R14" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>86400</v>
       </c>
       <c r="S14" s="40">
         <f t="shared" si="3"/>
@@ -13034,12 +13103,12 @@
       </c>
       <c r="T14" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>86400</v>
       </c>
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="24"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -13088,7 +13157,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -13135,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -13182,7 +13251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:20">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -13229,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:20">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="24"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -13276,7 +13345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:20">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -13323,7 +13392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -13370,7 +13439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -13417,7 +13486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -13464,7 +13533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -13511,7 +13580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -13558,7 +13627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -13605,7 +13674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -13652,7 +13721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -13699,7 +13768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -13746,7 +13815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -13793,7 +13862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -13840,7 +13909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -13887,7 +13956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -13934,7 +14003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -13981,7 +14050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -14028,7 +14097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -14075,7 +14144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -14122,7 +14191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -14169,7 +14238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -14223,7 +14292,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -14270,7 +14339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -14318,7 +14387,7 @@
       </c>
       <c r="Z41" s="35"/>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -14365,7 +14434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -14414,7 +14483,7 @@
       <c r="V43" s="34"/>
       <c r="W43" s="35"/>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -14461,7 +14530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -14508,7 +14577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -14555,7 +14624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -14602,7 +14671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -14649,7 +14718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -14696,7 +14765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -14743,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -14790,7 +14859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -14837,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -14884,7 +14953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -14931,7 +15000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -14978,7 +15047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -15025,7 +15094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -15072,7 +15141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -15119,7 +15188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -15166,7 +15235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -15213,7 +15282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -15260,7 +15329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -15309,7 +15378,7 @@
       <c r="U62" s="37"/>
       <c r="V62" s="105"/>
     </row>
-    <row r="63" spans="2:22">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -15357,7 +15426,7 @@
       </c>
       <c r="U63" s="37"/>
     </row>
-    <row r="64" spans="2:22">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -15405,7 +15474,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -15454,7 +15523,7 @@
       <c r="U65" s="37"/>
       <c r="V65" s="106"/>
     </row>
-    <row r="66" spans="2:22">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -15502,7 +15571,7 @@
       </c>
       <c r="U66" s="37"/>
     </row>
-    <row r="67" spans="2:22">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -15549,7 +15618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:22">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -15596,7 +15665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -15643,7 +15712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -15690,7 +15759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -15737,7 +15806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -15784,7 +15853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -15831,7 +15900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -15878,7 +15947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -15925,7 +15994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -15972,7 +16041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -16019,7 +16088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -16066,7 +16135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -16113,7 +16182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -16160,7 +16229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -16207,7 +16276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -16254,7 +16323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -16301,7 +16370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="36">
         <v>46057</v>
       </c>
@@ -16351,7 +16420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
@@ -16398,7 +16467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -16445,7 +16514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -16492,7 +16561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -16539,7 +16608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -16586,7 +16655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -16633,7 +16702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -16680,7 +16749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -16727,7 +16796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="2" customFormat="1">
+    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -16775,7 +16844,7 @@
       </c>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -16822,7 +16891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -16869,7 +16938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -16916,7 +16985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -16963,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -17010,7 +17079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -17057,7 +17126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -17104,7 +17173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -17151,7 +17220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -17198,7 +17267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -17245,7 +17314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -17305,7 +17374,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14DF8A7-7A30-473E-8FAB-92CB0FE83A84}">
   <dimension ref="B1:P106"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" style="47"/>
@@ -17325,19 +17394,19 @@
     <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>10.835580665156026</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="49" t="s">
         <v>17</v>
       </c>
@@ -17366,13 +17435,13 @@
         <v>360097</v>
       </c>
       <c r="L2" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
@@ -17380,13 +17449,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="59" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>10</v>
@@ -17395,25 +17464,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="K3" s="65">
+        <v>0</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" s="65">
-        <v>0</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>44</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="107">
         <f>Tomatillo!B4</f>
         <v>46128</v>
@@ -17423,7 +17492,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="108" t="str">
         <f>Tomatillo!E4</f>
@@ -17446,14 +17515,14 @@
         <v>15300</v>
       </c>
       <c r="J4" s="112" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="68">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N4" s="69">
         <v>46128</v>
@@ -17462,7 +17531,7 @@
         <v>36720</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15.75" thickBot="1">
+    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="107">
         <f>Tomatillo!B5</f>
         <v>46128</v>
@@ -17472,7 +17541,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" s="108" t="str">
         <f>Tomatillo!E5</f>
@@ -17495,7 +17564,7 @@
         <v>3060</v>
       </c>
       <c r="J5" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N5" s="71">
         <v>46129</v>
@@ -17505,7 +17574,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" ht="15.75" thickBot="1">
+    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="107">
         <f>Tomatillo!B6</f>
         <v>46128</v>
@@ -17515,7 +17584,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="108" t="str">
         <f>Tomatillo!E6</f>
@@ -17538,7 +17607,7 @@
         <v>6120</v>
       </c>
       <c r="J6" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="71">
         <v>46133</v>
@@ -17547,7 +17616,7 @@
         <v>40086</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15.75" thickBot="1">
+    <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="107">
         <f>Tomatillo!B7</f>
         <v>46128</v>
@@ -17557,7 +17626,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="108" t="str">
         <f>Tomatillo!E7</f>
@@ -17580,7 +17649,7 @@
         <v>12240</v>
       </c>
       <c r="J7" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="73">
         <f>95764/(434*17)</f>
@@ -17593,7 +17662,7 @@
         <v>123114</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="15.75" thickBot="1">
+    <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="107">
         <f>Tomatillo!B8</f>
         <v>46128</v>
@@ -17603,7 +17672,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="108" t="str">
         <f>Tomatillo!E8</f>
@@ -17626,7 +17695,7 @@
         <v>110976</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="73"/>
       <c r="N8" s="71">
@@ -17636,7 +17705,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15.75" thickBot="1">
+    <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="107">
         <f>Tomatillo!B9</f>
         <v>46129</v>
@@ -17646,7 +17715,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="108" t="str">
         <f>Tomatillo!E9</f>
@@ -17668,7 +17737,7 @@
         <v>15300</v>
       </c>
       <c r="J9" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9:K15" si="1">G9/17</f>
@@ -17681,7 +17750,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="107">
         <f>Tomatillo!B10</f>
         <v>46129</v>
@@ -17691,7 +17760,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="108" t="str">
         <f>Tomatillo!E10</f>
@@ -17713,7 +17782,7 @@
         <v>63648</v>
       </c>
       <c r="J10" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10" s="73">
         <f t="shared" si="1"/>
@@ -17726,7 +17795,7 @@
         <v>5530</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="116">
         <f>Tomatillo!B11</f>
         <v>46129</v>
@@ -17736,7 +17805,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" s="81" t="str">
         <f>Tomatillo!E11</f>
@@ -17759,7 +17828,7 @@
         <v>16816</v>
       </c>
       <c r="J11" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K11" s="73">
         <f t="shared" si="1"/>
@@ -17776,7 +17845,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="107">
         <f>Tomatillo!B12</f>
         <v>46130</v>
@@ -17786,7 +17855,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="108" t="str">
         <f>Tomatillo!E12</f>
@@ -17809,7 +17878,7 @@
         <v>34986</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K12" s="73">
         <f t="shared" si="1"/>
@@ -17822,7 +17891,7 @@
         <v>110976</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="107">
         <f>Tomatillo!B13</f>
         <v>46130</v>
@@ -17832,7 +17901,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="113" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="108" t="str">
         <f>Tomatillo!E13</f>
@@ -17855,7 +17924,7 @@
         <v>43350</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K13" s="73">
         <f t="shared" si="1"/>
@@ -17868,7 +17937,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15.75" thickBot="1">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="107">
         <f>Tomatillo!B14</f>
         <v>46132</v>
@@ -17878,7 +17947,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="108" t="str">
         <f>Tomatillo!E14</f>
@@ -17901,7 +17970,7 @@
         <v>5100</v>
       </c>
       <c r="J14" s="117" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" s="73">
         <f t="shared" si="1"/>
@@ -17916,7 +17985,7 @@
         <v>97750</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="107">
         <f>Tomatillo!B15</f>
         <v>46132</v>
@@ -17926,7 +17995,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="113" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="108" t="str">
         <f>Tomatillo!E15</f>
@@ -17949,7 +18018,7 @@
         <v>38250</v>
       </c>
       <c r="J15" s="117" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K15" s="73">
         <f t="shared" si="1"/>
@@ -17960,7 +18029,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="107">
         <f>Tomatillo!B16</f>
         <v>46133</v>
@@ -17970,7 +18039,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="113" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" s="108" t="str">
         <f>Tomatillo!E16</f>
@@ -17993,12 +18062,12 @@
         <v>54400</v>
       </c>
       <c r="J16" s="117" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" ht="15.75" thickBot="1">
+    <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="128">
         <f>Tomatillo!B17</f>
         <v>46133</v>
@@ -18008,7 +18077,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="130" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="129" t="str">
         <f>Tomatillo!E17</f>
@@ -18034,7 +18103,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" ht="15.75" thickBot="1">
+    <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="136">
         <f>Tomatillo!B18</f>
         <v>46134</v>
@@ -18044,7 +18113,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" s="81" t="str">
         <f>Tomatillo!E18</f>
@@ -18067,12 +18136,12 @@
         <v>12240</v>
       </c>
       <c r="J18" s="137" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" ht="15.75" thickBot="1">
+    <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="107">
         <f>Tomatillo!B19</f>
         <v>46134</v>
@@ -18082,7 +18151,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="108" t="str">
         <f>Tomatillo!E19</f>
@@ -18105,12 +18174,12 @@
         <v>84864</v>
       </c>
       <c r="J19" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" ht="15.75" thickBot="1">
+    <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="107">
         <f>Tomatillo!B20</f>
         <v>46136</v>
@@ -18120,7 +18189,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="163" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="108" t="str">
         <f>Tomatillo!E20</f>
@@ -18142,12 +18211,12 @@
         <v>6120</v>
       </c>
       <c r="J20" s="165" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" ht="15.75" thickBot="1">
+    <row r="21" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="107">
         <f>Tomatillo!B21</f>
         <v>46046</v>
@@ -18157,7 +18226,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="158" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" s="108" t="str">
         <f>Tomatillo!E21</f>
@@ -18179,12 +18248,12 @@
         <v>205530</v>
       </c>
       <c r="J21" s="160" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" ht="15.75" thickBot="1">
+    <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="136">
         <f>Tomatillo!B22</f>
         <v>46137</v>
@@ -18194,7 +18263,7 @@
         <v>23</v>
       </c>
       <c r="D22" s="161" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="81" t="str">
         <f>Tomatillo!E22</f>
@@ -18216,12 +18285,12 @@
         <v>6120</v>
       </c>
       <c r="J22" s="162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" ht="15.75" thickBot="1">
+    <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="136">
         <f>Tomatillo!B23</f>
         <v>46142</v>
@@ -18231,7 +18300,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="161" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="81" t="str">
         <f>Tomatillo!E23</f>
@@ -18253,12 +18322,12 @@
         <v>4284</v>
       </c>
       <c r="J23" s="162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" ht="15.75" thickBot="1">
+    <row r="24" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="136">
         <f>Tomatillo!B24</f>
         <v>46142</v>
@@ -18268,7 +18337,7 @@
         <v>28</v>
       </c>
       <c r="D24" s="161" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" s="81" t="str">
         <f>Tomatillo!E24</f>
@@ -18290,12 +18359,12 @@
         <v>78336</v>
       </c>
       <c r="J24" s="162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" ht="15.75" thickBot="1">
+    <row r="25" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="136">
         <f>Tomatillo!B25</f>
         <v>46143</v>
@@ -18305,7 +18374,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="161" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E25" s="81" t="str">
         <f>Tomatillo!E25</f>
@@ -18327,12 +18396,12 @@
         <v>17680</v>
       </c>
       <c r="J25" s="162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" ht="15.75" thickBot="1">
+    <row r="26" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="136">
         <f>Tomatillo!B26</f>
         <v>46146</v>
@@ -18342,7 +18411,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E26" s="81" t="str">
         <f>Tomatillo!E26</f>
@@ -18364,12 +18433,12 @@
         <v>148512</v>
       </c>
       <c r="J26" s="94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" ht="15.75" thickBot="1">
+    <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="136">
         <f>Tomatillo!B27</f>
         <v>46147</v>
@@ -18379,7 +18448,7 @@
         <v>34</v>
       </c>
       <c r="D27" s="86" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="81" t="str">
         <f>Tomatillo!E27</f>
@@ -18401,12 +18470,12 @@
         <v>59653</v>
       </c>
       <c r="J27" s="137" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" ht="15.75" thickBot="1">
+    <row r="28" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="107">
         <f>Tomatillo!B28</f>
         <v>46149</v>
@@ -18416,7 +18485,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28" s="108" t="str">
         <f>Tomatillo!E28</f>
@@ -18438,12 +18507,12 @@
         <v>136</v>
       </c>
       <c r="J28" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" ht="15.75" thickBot="1">
+    <row r="29" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="107">
         <f>Tomatillo!B29</f>
         <v>46149</v>
@@ -18453,7 +18522,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" s="108" t="str">
         <f>Tomatillo!E29</f>
@@ -18475,12 +18544,12 @@
         <v>7021</v>
       </c>
       <c r="J29" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" ht="15.75" thickBot="1">
+    <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="136">
         <f>Tomatillo!B30</f>
         <v>46150</v>
@@ -18490,7 +18559,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="86" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E30" s="81" t="str">
         <f>Tomatillo!E30</f>
@@ -18512,12 +18581,12 @@
         <v>16320</v>
       </c>
       <c r="J30" s="94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" ht="15.75" thickBot="1">
+    <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="136"/>
       <c r="C31" s="81"/>
       <c r="D31" s="85"/>
@@ -18530,7 +18599,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="136"/>
       <c r="C32" s="81"/>
       <c r="D32" s="86"/>
@@ -18543,7 +18612,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -18556,7 +18625,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -18569,7 +18638,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -18582,7 +18651,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -18595,7 +18664,7 @@
       <c r="N36" s="71"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -18608,7 +18677,7 @@
       <c r="N37" s="76"/>
       <c r="O37" s="72"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -18621,7 +18690,7 @@
       <c r="N38" s="77"/>
       <c r="O38" s="78"/>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -18639,7 +18708,7 @@
         <v>706265</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="89"/>
       <c r="C40" s="86"/>
       <c r="D40" s="86"/>
@@ -18650,7 +18719,7 @@
       <c r="I40" s="88"/>
       <c r="J40" s="90"/>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -18661,14 +18730,14 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
       <c r="N41" s="66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O41" s="67">
         <f>Tomatillo!Q2</f>
         <v>106636.20000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -18679,7 +18748,7 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -18690,14 +18759,14 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
       <c r="N43" s="66" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O43" s="67">
         <f>Tomatillo!T2</f>
         <v>959725.8</v>
       </c>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="89"/>
       <c r="C44" s="86"/>
       <c r="D44" s="86"/>
@@ -18708,7 +18777,7 @@
       <c r="I44" s="75"/>
       <c r="J44" s="90"/>
     </row>
-    <row r="45" spans="2:15" ht="15.75" thickBot="1">
+    <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -18719,14 +18788,14 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
       <c r="N45" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O45" s="67">
         <f>+O43+O41-O39</f>
         <v>360097</v>
       </c>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -18737,7 +18806,7 @@
       <c r="I46" s="75"/>
       <c r="J46" s="92"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="89"/>
       <c r="C47" s="86"/>
       <c r="D47" s="86"/>
@@ -18749,7 +18818,7 @@
       <c r="J47" s="90"/>
       <c r="O47" s="79"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -18760,7 +18829,7 @@
       <c r="I48" s="75"/>
       <c r="J48" s="92"/>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -18772,7 +18841,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -18784,7 +18853,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="96"/>
       <c r="C51" s="87"/>
       <c r="D51" s="86"/>
@@ -18796,7 +18865,7 @@
       <c r="J51" s="90"/>
       <c r="O51" s="80"/>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="96"/>
       <c r="C52" s="87"/>
       <c r="D52" s="86"/>
@@ -18809,7 +18878,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -18822,7 +18891,7 @@
       <c r="O53" s="80"/>
       <c r="P53" s="80"/>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="96"/>
       <c r="C54" s="87"/>
       <c r="D54" s="86"/>
@@ -18833,7 +18902,7 @@
       <c r="I54" s="88"/>
       <c r="J54" s="90"/>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -18846,7 +18915,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="96"/>
       <c r="C56" s="87"/>
       <c r="D56" s="86"/>
@@ -18859,7 +18928,7 @@
       <c r="O56" s="80"/>
       <c r="P56" s="80"/>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -18870,7 +18939,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -18881,7 +18950,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -18892,7 +18961,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="96"/>
       <c r="C60" s="87"/>
       <c r="D60" s="86"/>
@@ -18903,7 +18972,7 @@
       <c r="I60" s="88"/>
       <c r="J60" s="90"/>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="96"/>
       <c r="C61" s="87"/>
       <c r="D61" s="86"/>
@@ -18914,7 +18983,7 @@
       <c r="I61" s="88"/>
       <c r="J61" s="90"/>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="96"/>
       <c r="C62" s="87"/>
       <c r="D62" s="86"/>
@@ -18925,7 +18994,7 @@
       <c r="I62" s="88"/>
       <c r="J62" s="90"/>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -18936,7 +19005,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -18947,7 +19016,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -18958,7 +19027,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="96"/>
       <c r="C66" s="87"/>
       <c r="D66" s="86"/>
@@ -18969,7 +19038,7 @@
       <c r="I66" s="88"/>
       <c r="J66" s="90"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -18980,7 +19049,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -18991,7 +19060,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="96"/>
       <c r="C69" s="87"/>
       <c r="D69" s="86"/>
@@ -19002,7 +19071,7 @@
       <c r="I69" s="88"/>
       <c r="J69" s="90"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="96"/>
       <c r="C70" s="87"/>
       <c r="D70" s="86"/>
@@ -19013,7 +19082,7 @@
       <c r="I70" s="88"/>
       <c r="J70" s="90"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="96"/>
       <c r="C71" s="87"/>
       <c r="D71" s="86"/>
@@ -19024,7 +19093,7 @@
       <c r="I71" s="88"/>
       <c r="J71" s="90"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -19035,7 +19104,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -19046,7 +19115,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="92"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -19057,7 +19126,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="98"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="96"/>
       <c r="C75" s="87"/>
       <c r="D75" s="86"/>
@@ -19068,7 +19137,7 @@
       <c r="I75" s="88"/>
       <c r="J75" s="90"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="96"/>
       <c r="C76" s="87"/>
       <c r="D76" s="86"/>
@@ -19079,7 +19148,7 @@
       <c r="I76" s="88"/>
       <c r="J76" s="99"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -19090,7 +19159,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -19101,7 +19170,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="96"/>
       <c r="C79" s="87"/>
       <c r="D79" s="86"/>
@@ -19112,7 +19181,7 @@
       <c r="I79" s="88"/>
       <c r="J79" s="90"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="96"/>
       <c r="C80" s="87"/>
       <c r="D80" s="86"/>
@@ -19123,7 +19192,7 @@
       <c r="I80" s="88"/>
       <c r="J80" s="90"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -19134,7 +19203,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="96"/>
       <c r="C82" s="87"/>
       <c r="D82" s="86"/>
@@ -19145,7 +19214,7 @@
       <c r="I82" s="88"/>
       <c r="J82" s="90"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="96"/>
       <c r="C83" s="87"/>
       <c r="D83" s="86"/>
@@ -19156,7 +19225,7 @@
       <c r="I83" s="88"/>
       <c r="J83" s="90"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -19167,7 +19236,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="96"/>
       <c r="C85" s="87"/>
       <c r="D85" s="86"/>
@@ -19178,7 +19247,7 @@
       <c r="I85" s="88"/>
       <c r="J85" s="90"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -19189,7 +19258,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="96"/>
       <c r="C87" s="87"/>
       <c r="D87" s="86"/>
@@ -19200,7 +19269,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="90"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -19211,7 +19280,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="96"/>
       <c r="C89" s="87"/>
       <c r="D89" s="86"/>
@@ -19222,7 +19291,7 @@
       <c r="I89" s="88"/>
       <c r="J89" s="90"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -19233,7 +19302,7 @@
       <c r="I90" s="88"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -19244,7 +19313,7 @@
       <c r="I91" s="88"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="96"/>
       <c r="C92" s="87"/>
       <c r="D92" s="86"/>
@@ -19255,7 +19324,7 @@
       <c r="I92" s="93"/>
       <c r="J92" s="103"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -19266,7 +19335,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -19277,7 +19346,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -19288,7 +19357,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -19299,7 +19368,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -19310,7 +19379,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="92"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -19321,7 +19390,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="94"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -19332,7 +19401,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -19343,7 +19412,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -19354,7 +19423,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -19365,7 +19434,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="92"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -19376,7 +19445,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="94"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -19387,7 +19456,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -19398,7 +19467,7 @@
       <c r="I105" s="75"/>
       <c r="J105" s="92"/>
     </row>
-    <row r="106" spans="2:10">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="91"/>
       <c r="C106" s="85"/>
       <c r="D106" s="85"/>
@@ -19418,7 +19487,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A884314C-68A6-4266-8FA4-11EA17178DDD}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" style="47"/>
@@ -19438,29 +19507,29 @@
     <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>34.230826566316765</v>
+        <v>31.245379764705884</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="145">
         <f>SUM(F4:F390)</f>
-        <v>891</v>
+        <v>1250</v>
       </c>
       <c r="G2" s="146">
         <f>I2/F2</f>
-        <v>581.92405162738498</v>
+        <v>531.17145600000003</v>
       </c>
       <c r="H2" s="147">
         <f>SUM(H4:H390)</f>
@@ -19468,7 +19537,7 @@
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I390)</f>
-        <v>518494.33</v>
+        <v>663964.32000000007</v>
       </c>
       <c r="J2" s="148">
         <f>O38</f>
@@ -19476,16 +19545,16 @@
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>54799.329999999958</v>
+        <v>165869.32000000007</v>
       </c>
       <c r="L2" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -19493,13 +19562,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="152" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="154" t="s">
         <v>10</v>
@@ -19508,25 +19577,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="156" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="K3" s="143">
+        <v>0</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" s="143">
-        <v>0</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>44</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="149">
         <v>46135</v>
       </c>
@@ -19534,7 +19603,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E4" s="150" t="s">
         <v>29</v>
@@ -19553,14 +19622,14 @@
         <v>20400</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K4" s="142">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N4" s="69">
         <v>46140</v>
@@ -19569,7 +19638,7 @@
         <v>54225</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="173">
         <f>Roma!B5</f>
         <v>46140</v>
@@ -19579,7 +19648,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" s="113" t="str">
         <f>Roma!E5</f>
@@ -19602,7 +19671,7 @@
         <v>54224.729999999996</v>
       </c>
       <c r="J5" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N5" s="71">
         <v>46142</v>
@@ -19612,7 +19681,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="173">
         <f>Roma!B6</f>
         <v>46142</v>
@@ -19622,7 +19691,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E6" s="113" t="str">
         <f>Roma!E6</f>
@@ -19644,7 +19713,7 @@
         <v>65460.12</v>
       </c>
       <c r="J6" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="71">
         <v>46146</v>
@@ -19653,7 +19722,7 @@
         <v>110950</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="173">
         <f>Roma!B7</f>
         <v>46144</v>
@@ -19663,7 +19732,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E7" s="113" t="str">
         <f>Roma!E7</f>
@@ -19683,7 +19752,7 @@
         <v>110949.93000000001</v>
       </c>
       <c r="J7" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="73"/>
       <c r="N7" s="71">
@@ -19693,7 +19762,7 @@
         <v>134840</v>
       </c>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="173">
         <f>Roma!B8</f>
         <v>46147</v>
@@ -19703,7 +19772,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" s="113" t="str">
         <f>Roma!E8</f>
@@ -19725,7 +19794,7 @@
         <v>134839.54999999999</v>
       </c>
       <c r="J8" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="73"/>
       <c r="N8" s="71">
@@ -19736,7 +19805,7 @@
         <v>132620</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="173">
         <f>Roma!B9</f>
         <v>46149</v>
@@ -19746,7 +19815,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" s="113" t="str">
         <f>Roma!E9</f>
@@ -19768,13 +19837,13 @@
         <v>620</v>
       </c>
       <c r="J9" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="73"/>
       <c r="N9" s="71"/>
       <c r="O9" s="72"/>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="173">
         <f>Roma!B10</f>
         <v>46150</v>
@@ -19784,7 +19853,7 @@
         <v>38</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E10" s="113" t="str">
         <f>Roma!E10</f>
@@ -19806,13 +19875,13 @@
         <v>24000</v>
       </c>
       <c r="J10" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10" s="73"/>
       <c r="N10" s="71"/>
       <c r="O10" s="72"/>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="173">
         <f>Roma!B11</f>
         <v>46150</v>
@@ -19822,7 +19891,7 @@
         <v>39</v>
       </c>
       <c r="D11" s="113" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E11" s="113" t="str">
         <f>Roma!E11</f>
@@ -19844,86 +19913,138 @@
         <v>108000</v>
       </c>
       <c r="J11" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="79"/>
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16">
-      <c r="B12" s="91"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="75"/>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="176">
+        <f>Roma!B12</f>
+        <v>46153</v>
+      </c>
+      <c r="C12" s="175">
+        <f>Roma!C12</f>
+        <v>42</v>
+      </c>
+      <c r="D12" s="175" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="175" t="str">
+        <f>Roma!E12</f>
+        <v>Epifania Lopez</v>
+      </c>
+      <c r="F12" s="177">
+        <f>Roma!H12</f>
+        <v>80</v>
+      </c>
+      <c r="G12" s="75">
+        <f>Roma!K12</f>
+        <v>430</v>
+      </c>
       <c r="H12" s="84">
         <v>0</v>
       </c>
       <c r="I12" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="92"/>
+        <v>34400</v>
+      </c>
+      <c r="J12" s="178" t="s">
+        <v>54</v>
+      </c>
       <c r="K12" s="73"/>
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16">
-      <c r="B13" s="91"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="75"/>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="176">
+        <f>Roma!B13</f>
+        <v>46153</v>
+      </c>
+      <c r="C13" s="175">
+        <f>Roma!C13</f>
+        <v>43</v>
+      </c>
+      <c r="D13" s="175" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="175" t="str">
+        <f>Roma!E13</f>
+        <v>Mayojoa</v>
+      </c>
+      <c r="F13" s="177">
+        <f>Roma!H13</f>
+        <v>39</v>
+      </c>
+      <c r="G13" s="75">
+        <f>Roma!K13</f>
+        <v>386.41</v>
+      </c>
       <c r="H13" s="84">
         <v>0</v>
       </c>
       <c r="I13" s="75">
         <f>F13*G13-H13</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="94"/>
+        <v>15069.990000000002</v>
+      </c>
+      <c r="J13" s="178" t="s">
+        <v>54</v>
+      </c>
       <c r="K13" s="73"/>
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16">
-      <c r="B14" s="91"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="75"/>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="176">
+        <f>Roma!B14</f>
+        <v>46153</v>
+      </c>
+      <c r="C14" s="175">
+        <f>Roma!C14</f>
+        <v>44</v>
+      </c>
+      <c r="D14" s="175" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="175" t="str">
+        <f>Roma!E14</f>
+        <v>Efrén Medina</v>
+      </c>
+      <c r="F14" s="177">
+        <f>Roma!H14</f>
+        <v>240</v>
+      </c>
+      <c r="G14" s="75">
+        <f>Roma!K14</f>
+        <v>400</v>
+      </c>
       <c r="H14" s="84">
         <v>0</v>
       </c>
       <c r="I14" s="75">
         <f t="shared" ref="I14:I18" si="2">F14*G14-H14</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="92"/>
+        <v>96000</v>
+      </c>
+      <c r="J14" s="178" t="s">
+        <v>54</v>
+      </c>
       <c r="K14" s="73"/>
       <c r="L14" s="74"/>
       <c r="M14" s="74"/>
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="91"/>
-      <c r="C15" s="85"/>
+      <c r="C15" s="175"/>
       <c r="D15" s="85"/>
       <c r="E15" s="85"/>
       <c r="F15" s="25"/>
       <c r="G15" s="75"/>
-      <c r="H15" s="84">
-        <v>0</v>
-      </c>
-      <c r="I15" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="H15" s="84"/>
+      <c r="I15" s="75"/>
       <c r="J15" s="92"/>
       <c r="K15" s="73"/>
       <c r="L15" s="74"/>
@@ -19931,61 +20052,46 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="91"/>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
       <c r="E16" s="85"/>
       <c r="F16" s="25"/>
       <c r="G16" s="75"/>
-      <c r="H16" s="84">
-        <v>0</v>
-      </c>
-      <c r="I16" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="H16" s="84"/>
+      <c r="I16" s="75"/>
       <c r="J16" s="94"/>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="91"/>
       <c r="C17" s="85"/>
       <c r="D17" s="85"/>
       <c r="E17" s="85"/>
       <c r="F17" s="25"/>
       <c r="G17" s="75"/>
-      <c r="H17" s="84">
-        <v>0</v>
-      </c>
-      <c r="I17" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="H17" s="84"/>
+      <c r="I17" s="75"/>
       <c r="J17" s="94"/>
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="91"/>
       <c r="C18" s="85"/>
       <c r="D18" s="85"/>
       <c r="E18" s="85"/>
       <c r="F18" s="25"/>
       <c r="G18" s="75"/>
-      <c r="H18" s="84">
-        <v>0</v>
-      </c>
-      <c r="I18" s="75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="H18" s="84"/>
+      <c r="I18" s="75"/>
       <c r="J18" s="92"/>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -19998,7 +20104,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -20011,7 +20117,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -20024,7 +20130,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -20037,7 +20143,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -20050,7 +20156,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -20063,7 +20169,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -20076,7 +20182,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -20089,7 +20195,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -20102,7 +20208,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -20115,7 +20221,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -20128,7 +20234,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -20141,7 +20247,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -20154,7 +20260,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -20167,7 +20273,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -20180,7 +20286,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -20193,7 +20299,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -20206,7 +20312,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -20219,7 +20325,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1">
+    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -20232,7 +20338,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -20250,7 +20356,7 @@
         <v>498095</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -20261,7 +20367,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -20272,14 +20378,14 @@
       <c r="I40" s="75"/>
       <c r="J40" s="92"/>
       <c r="N40" s="66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O40" s="67">
         <f>Roma!Q2</f>
-        <v>55289.433000000005</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1">
+        <v>66396.432000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -20290,7 +20396,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -20301,14 +20407,14 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
       <c r="N42" s="66" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O42" s="67">
         <f>+Roma!R2</f>
-        <v>497604.897</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1">
+        <v>597567.88800000004</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -20319,7 +20425,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -20330,14 +20436,14 @@
       <c r="I44" s="75"/>
       <c r="J44" s="92"/>
       <c r="N44" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>54799.329999999958</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15">
+        <v>165869.32000000007</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -20348,7 +20454,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -20360,7 +20466,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -20371,7 +20477,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -20383,7 +20489,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -20395,7 +20501,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -20407,7 +20513,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -20420,7 +20526,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -20433,7 +20539,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -20444,7 +20550,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -20457,7 +20563,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -20470,7 +20576,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -20481,7 +20587,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -20492,7 +20598,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -20503,7 +20609,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -20514,7 +20620,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -20525,7 +20631,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -20536,7 +20642,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -20547,7 +20653,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -20558,7 +20664,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -20569,7 +20675,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -20580,7 +20686,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -20591,7 +20697,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -20602,7 +20708,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -20613,7 +20719,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -20624,7 +20730,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -20635,7 +20741,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -20646,7 +20752,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -20657,7 +20763,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -20668,7 +20774,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -20679,7 +20785,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -20690,7 +20796,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -20701,7 +20807,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -20712,7 +20818,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -20723,7 +20829,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -20734,7 +20840,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -20745,7 +20851,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -20756,7 +20862,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -20767,7 +20873,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -20778,7 +20884,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -20789,7 +20895,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -20800,7 +20906,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -20811,7 +20917,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -20822,7 +20928,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -20833,7 +20939,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -20844,7 +20950,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -20855,7 +20961,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -20866,7 +20972,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -20877,7 +20983,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -20888,7 +20994,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -20899,7 +21005,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -20910,7 +21016,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -20921,7 +21027,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -20932,7 +21038,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -20943,7 +21049,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -20954,7 +21060,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -20965,7 +21071,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -20976,7 +21082,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -20987,7 +21093,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -20998,7 +21104,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -21009,7 +21115,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -21029,7 +21135,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7F0943-67B8-4148-A349-2B4FA39AA366}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" style="47"/>
@@ -21049,19 +21155,19 @@
     <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>14.937611408199643</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
@@ -21090,13 +21196,13 @@
         <v>8380</v>
       </c>
       <c r="L2" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -21104,13 +21210,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="152" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="154" t="s">
         <v>10</v>
@@ -21119,25 +21225,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="156" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="K3" s="143">
+        <v>0</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" s="143">
-        <v>0</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>44</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="149">
         <f>Morrón!B4</f>
         <v>46139</v>
@@ -21147,7 +21253,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E4" s="150" t="str">
         <f>Morrón!E4</f>
@@ -21169,19 +21275,19 @@
         <v>2400</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K4" s="142">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N4" s="69"/>
       <c r="O4" s="70"/>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="149">
         <f>Morrón!B5</f>
         <v>46151</v>
@@ -21191,7 +21297,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="85" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E5" s="150" t="str">
         <f>Morrón!E5</f>
@@ -21213,13 +21319,13 @@
         <v>5980</v>
       </c>
       <c r="J5" s="157" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" s="71"/>
       <c r="O5" s="72"/>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="91"/>
       <c r="C6" s="85"/>
       <c r="D6" s="85"/>
@@ -21237,7 +21343,7 @@
       <c r="N6" s="71"/>
       <c r="O6" s="72"/>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="91"/>
       <c r="C7" s="85"/>
       <c r="D7" s="85"/>
@@ -21256,7 +21362,7 @@
       <c r="N7" s="71"/>
       <c r="O7" s="72"/>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="91"/>
       <c r="C8" s="85"/>
       <c r="D8" s="85"/>
@@ -21275,7 +21381,7 @@
       <c r="N8" s="71"/>
       <c r="O8" s="72"/>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="91"/>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -21294,7 +21400,7 @@
       <c r="N9" s="71"/>
       <c r="O9" s="72"/>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="91"/>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -21313,7 +21419,7 @@
       <c r="N10" s="71"/>
       <c r="O10" s="72"/>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="91"/>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -21333,7 +21439,7 @@
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="91"/>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -21352,7 +21458,7 @@
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="91"/>
       <c r="C13" s="85"/>
       <c r="D13" s="85"/>
@@ -21371,7 +21477,7 @@
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="91"/>
       <c r="C14" s="85"/>
       <c r="D14" s="85"/>
@@ -21392,7 +21498,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="91"/>
       <c r="C15" s="85"/>
       <c r="D15" s="85"/>
@@ -21413,7 +21519,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="91"/>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
@@ -21431,7 +21537,7 @@
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="91"/>
       <c r="C17" s="85"/>
       <c r="D17" s="85"/>
@@ -21449,7 +21555,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="91"/>
       <c r="C18" s="85"/>
       <c r="D18" s="85"/>
@@ -21467,7 +21573,7 @@
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -21480,7 +21586,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -21493,7 +21599,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -21506,7 +21612,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -21519,7 +21625,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -21532,7 +21638,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -21545,7 +21651,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -21558,7 +21664,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -21571,7 +21677,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -21584,7 +21690,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -21597,7 +21703,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -21610,7 +21716,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -21623,7 +21729,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -21636,7 +21742,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -21649,7 +21755,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -21662,7 +21768,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -21675,7 +21781,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -21688,7 +21794,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -21701,7 +21807,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1">
+    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -21714,7 +21820,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -21732,7 +21838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -21743,7 +21849,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -21754,14 +21860,14 @@
       <c r="I40" s="75"/>
       <c r="J40" s="92"/>
       <c r="N40" s="66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O40" s="67">
         <f>Morrón!Q2</f>
         <v>838</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -21772,7 +21878,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -21783,14 +21889,14 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
       <c r="N42" s="66" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O42" s="67">
         <f>+Morrón!R2</f>
         <v>7542</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -21801,7 +21907,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -21812,14 +21918,14 @@
       <c r="I44" s="75"/>
       <c r="J44" s="92"/>
       <c r="N44" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
         <v>8380</v>
       </c>
     </row>
-    <row r="45" spans="2:15">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -21830,7 +21936,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -21842,7 +21948,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -21853,7 +21959,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -21865,7 +21971,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -21877,7 +21983,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -21889,7 +21995,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -21902,7 +22008,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -21915,7 +22021,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -21926,7 +22032,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -21939,7 +22045,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -21952,7 +22058,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -21963,7 +22069,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -21974,7 +22080,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -21985,7 +22091,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -21996,7 +22102,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -22007,7 +22113,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -22018,7 +22124,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -22029,7 +22135,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -22040,7 +22146,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -22051,7 +22157,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -22062,7 +22168,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -22073,7 +22179,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -22084,7 +22190,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -22095,7 +22201,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -22106,7 +22212,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -22117,7 +22223,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -22128,7 +22234,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -22139,7 +22245,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -22150,7 +22256,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -22161,7 +22267,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -22172,7 +22278,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -22183,7 +22289,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -22194,7 +22300,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -22205,7 +22311,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -22216,7 +22322,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -22227,7 +22333,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -22238,7 +22344,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -22249,7 +22355,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -22260,7 +22366,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -22271,7 +22377,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -22282,7 +22388,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -22293,7 +22399,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -22304,7 +22410,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -22315,7 +22421,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -22326,7 +22432,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -22337,7 +22443,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -22348,7 +22454,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -22359,7 +22465,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -22370,7 +22476,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -22381,7 +22487,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -22392,7 +22498,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -22403,7 +22509,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -22414,7 +22520,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -22425,7 +22531,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -22436,7 +22542,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -22447,7 +22553,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -22458,7 +22564,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -22469,7 +22575,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -22480,7 +22586,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -22491,7 +22597,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -22510,7 +22616,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFCC301-F59E-4EF9-AD64-E57A9E70782E}">
   <dimension ref="D2:L12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
@@ -22522,12 +22628,12 @@
     <col min="11" max="11" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:12" ht="30">
+    <row r="2" spans="4:12" ht="30" x14ac:dyDescent="0.25">
       <c r="D2" s="169" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="4:12">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E3" s="47"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -22537,31 +22643,31 @@
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
     </row>
-    <row r="4" spans="4:12" ht="23.25" customHeight="1">
+    <row r="4" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="170" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F4" s="170" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G4" s="170" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H4" s="170"/>
       <c r="I4" s="170" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J4" s="170" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K4" s="170" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L4" s="47"/>
     </row>
-    <row r="5" spans="4:12" ht="23.25" customHeight="1">
+    <row r="5" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
@@ -22588,13 +22694,13 @@
         <v>313609.8</v>
       </c>
     </row>
-    <row r="6" spans="4:12" ht="23.25" customHeight="1">
+    <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
-        <v>552894.33000000007</v>
+        <v>663964.32000000007</v>
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
@@ -22602,24 +22708,24 @@
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>54799.330000000075</v>
+        <v>165869.32000000007</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
         <f>+Roma!Q2</f>
-        <v>55289.433000000005</v>
+        <v>66396.432000000001</v>
       </c>
       <c r="J6" s="167">
         <v>11968</v>
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>11477.89700000007</v>
-      </c>
-    </row>
-    <row r="7" spans="4:12" ht="23.25" customHeight="1">
+        <v>111440.88800000006</v>
+      </c>
+    </row>
+    <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E7" s="167">
         <f>+Morrón!O2</f>
@@ -22646,7 +22752,7 @@
         <v>7542</v>
       </c>
     </row>
-    <row r="8" spans="4:12" ht="23.25" customHeight="1">
+    <row r="8" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
       <c r="G8" s="171"/>
@@ -22655,10 +22761,10 @@
       <c r="J8" s="167"/>
       <c r="K8" s="167"/>
     </row>
-    <row r="9" spans="4:12" ht="23.25" customHeight="1">
+    <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
-        <v>1627636.33</v>
+        <v>1738706.32</v>
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
@@ -22666,12 +22772,12 @@
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>423276.33000000007</v>
+        <v>534346.32000000007</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
         <f>SUM(I5:I8)</f>
-        <v>162763.63300000003</v>
+        <v>173870.63200000001</v>
       </c>
       <c r="J9" s="168">
         <f>SUM(J5:J8)</f>
@@ -22679,10 +22785,10 @@
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>332629.69700000004</v>
-      </c>
-    </row>
-    <row r="10" spans="4:12" ht="23.25" customHeight="1">
+        <v>432592.68800000008</v>
+      </c>
+    </row>
+    <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="167"/>
       <c r="F10" s="167"/>
       <c r="G10" s="167"/>
@@ -22692,26 +22798,26 @@
       <c r="K10" s="166"/>
       <c r="L10" s="167"/>
     </row>
-    <row r="11" spans="4:12" ht="23.25" customHeight="1">
+    <row r="11" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="167"/>
       <c r="F11" s="167"/>
       <c r="G11" s="167"/>
       <c r="H11" s="167"/>
       <c r="I11" s="167">
         <f>+I9-J9</f>
-        <v>90646.633000000031</v>
+        <v>101753.63200000001</v>
       </c>
       <c r="J11" s="167"/>
       <c r="K11" s="166"/>
       <c r="L11" s="167"/>
     </row>
-    <row r="12" spans="4:12">
+    <row r="12" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E12" s="167"/>
       <c r="F12" s="167"/>
       <c r="G12" s="167"/>
       <c r="H12" s="167"/>
       <c r="I12" s="167" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J12" s="167"/>
       <c r="K12" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1432" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93002DCA-D76C-46DC-9743-074698C67C83}"/>
+  <xr:revisionPtr revIDLastSave="1493" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1747E9F-6FB8-4C3B-AA20-08E19BC75B22}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="99">
   <si>
     <t>TOTAL</t>
   </si>
@@ -330,9 +330,6 @@
     <t>20260508-02</t>
   </si>
   <si>
-    <t>Epifania Lopez</t>
-  </si>
-  <si>
     <t>20260511-01</t>
   </si>
   <si>
@@ -340,6 +337,9 @@
   </si>
   <si>
     <t>20260511-03</t>
+  </si>
+  <si>
+    <t>Epifanio Lopez</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1519,17 +1519,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1955,11 +1946,11 @@
       </c>
       <c r="G2" s="4">
         <f>SUM(G4:G495)</f>
-        <v>5789</v>
+        <v>5893</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(H4:H495)</f>
-        <v>5789</v>
+        <v>5893</v>
       </c>
       <c r="I2" s="6">
         <f>SUM(I4:I495)</f>
@@ -1971,35 +1962,35 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>165.78438417688722</v>
+        <v>155.98657661632447</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>10.835580665156026</v>
+        <v>10.101102604286243</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M495)</f>
-        <v>1070762</v>
+        <v>1061338.5599999998</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N495)</f>
-        <v>4400</v>
+        <v>49400</v>
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O495)</f>
-        <v>1066362</v>
+        <v>1011938.56</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
-        <v>0.1</v>
+        <v>9.1615902056346205E-2</v>
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q495)</f>
-        <v>106636.20000000001</v>
+        <v>92709.664000000019</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R495)</f>
-        <v>959725.8</v>
+        <v>919228.89600000007</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S495)</f>
@@ -2007,7 +1998,7 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T495)</f>
-        <v>959725.8</v>
+        <v>919228.89600000007</v>
       </c>
       <c r="V2" s="12"/>
     </row>
@@ -3522,69 +3513,69 @@
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="24">
+      <c r="B26" s="118">
         <v>46146</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="119">
         <v>32</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="F26" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="120">
         <v>1248</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="121">
         <v>1248</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="43">
+      <c r="I26" s="122"/>
+      <c r="J26" s="121">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K26" s="31">
-        <f>7*17</f>
-        <v>119</v>
-      </c>
-      <c r="L26" s="40">
+      <c r="K26" s="123">
+        <f>6.12*17</f>
+        <v>104.04</v>
+      </c>
+      <c r="L26" s="124">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="M26" s="41">
+        <v>6.12</v>
+      </c>
+      <c r="M26" s="123">
         <f t="shared" si="0"/>
-        <v>148512</v>
-      </c>
-      <c r="N26" s="27">
-        <v>0</v>
-      </c>
-      <c r="O26" s="40">
+        <v>129841.92000000001</v>
+      </c>
+      <c r="N26" s="123">
+        <v>45000</v>
+      </c>
+      <c r="O26" s="124">
         <f t="shared" si="1"/>
-        <v>148512</v>
-      </c>
-      <c r="P26" s="32">
-        <v>0.1</v>
-      </c>
-      <c r="Q26" s="40">
+        <v>84841.920000000013</v>
+      </c>
+      <c r="P26" s="175">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="124">
         <f t="shared" si="7"/>
-        <v>14851.2</v>
-      </c>
-      <c r="R26" s="42">
+        <v>0</v>
+      </c>
+      <c r="R26" s="126">
         <f t="shared" si="2"/>
-        <v>133660.79999999999</v>
-      </c>
-      <c r="S26" s="40">
+        <v>84841.920000000013</v>
+      </c>
+      <c r="S26" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T26" s="23">
+      <c r="T26" s="126">
         <f t="shared" si="4"/>
-        <v>133660.79999999999</v>
+        <v>84841.920000000013</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -3851,40 +3842,61 @@
       </c>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
+      <c r="B31" s="24">
+        <v>46154</v>
+      </c>
+      <c r="C31" s="25">
+        <v>46</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="28">
+        <v>104</v>
+      </c>
+      <c r="H31" s="29">
+        <v>104</v>
+      </c>
       <c r="I31" s="19"/>
       <c r="J31" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K31" s="31"/>
+      <c r="K31" s="31">
+        <f>5.23*17</f>
+        <v>88.910000000000011</v>
+      </c>
       <c r="L31" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="M31" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="27"/>
+        <v>9246.6400000000012</v>
+      </c>
+      <c r="N31" s="27">
+        <v>0</v>
+      </c>
       <c r="O31" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="32"/>
+        <v>9246.6400000000012</v>
+      </c>
+      <c r="P31" s="32">
+        <v>0.1</v>
+      </c>
       <c r="Q31" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>924.66400000000021</v>
       </c>
       <c r="R31" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8321.9760000000006</v>
       </c>
       <c r="S31" s="40">
         <f t="shared" si="3"/>
@@ -3892,7 +3904,7 @@
       </c>
       <c r="T31" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8321.9760000000006</v>
       </c>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
@@ -12234,7 +12246,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631DB7E5-46D0-410B-A49E-BCCBB7DAB626}">
-  <dimension ref="A2:AC104"/>
+  <dimension ref="A2:AC105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
@@ -12274,60 +12286,60 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f>SUM(G4:G494)</f>
-        <v>1250</v>
+        <f>SUM(G4:G495)</f>
+        <v>1587</v>
       </c>
       <c r="H2" s="5">
-        <f>SUM(H4:H494)</f>
-        <v>1250</v>
+        <f>SUM(H4:H495)</f>
+        <v>1587</v>
       </c>
       <c r="I2" s="6">
-        <f>SUM(I4:I494)</f>
+        <f>SUM(I4:I495)</f>
         <v>0</v>
       </c>
       <c r="J2" s="7">
-        <f>SUM(J4:J494)</f>
+        <f>SUM(J4:J495)</f>
         <v>0</v>
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>478.05431040000002</v>
+        <v>452.91670321361062</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>31.245379764705884</v>
+        <v>29.602398902850368</v>
       </c>
       <c r="M2" s="8">
-        <f>SUM(M4:M494)</f>
-        <v>663964.32000000007</v>
+        <f>SUM(M4:M495)</f>
+        <v>798643.12000000011</v>
       </c>
       <c r="N2" s="8">
-        <f>SUM(N4:N494)</f>
+        <f>SUM(N4:N495)</f>
         <v>0</v>
       </c>
       <c r="O2" s="8">
-        <f>SUM(O4:O494)</f>
-        <v>663964.32000000007</v>
+        <f>SUM(O4:O495)</f>
+        <v>798643.12000000011</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="Q2" s="8">
-        <f>SUM(Q4:Q494)</f>
-        <v>66396.432000000001</v>
+        <f>SUM(Q4:Q495)</f>
+        <v>79864.312000000005</v>
       </c>
       <c r="R2" s="10">
-        <f>SUM(R4:R494)</f>
-        <v>597567.88800000004</v>
+        <f>SUM(R4:R495)</f>
+        <v>718778.80800000008</v>
       </c>
       <c r="S2" s="10">
-        <f>SUM(S4:S494)</f>
+        <f>SUM(S4:S495)</f>
         <v>0</v>
       </c>
       <c r="T2" s="10">
-        <f>SUM(T4:T494)</f>
-        <v>597567.88800000004</v>
+        <f>SUM(T4:T495)</f>
+        <v>718778.80800000008</v>
       </c>
       <c r="V2" s="12"/>
     </row>
@@ -12425,14 +12437,14 @@
         <v>48</v>
       </c>
       <c r="M4" s="40">
-        <f t="shared" ref="M4:M35" si="0">K4*H4</f>
+        <f t="shared" ref="M4:M36" si="0">K4*H4</f>
         <v>20400</v>
       </c>
       <c r="N4" s="21">
         <v>0</v>
       </c>
       <c r="O4" s="40">
-        <f t="shared" ref="O4:O35" si="1">IF(H4="",0,M4-N4)</f>
+        <f t="shared" ref="O4:O36" si="1">IF(H4="",0,M4-N4)</f>
         <v>20400</v>
       </c>
       <c r="P4" s="22">
@@ -12443,15 +12455,15 @@
         <v>2040</v>
       </c>
       <c r="R4" s="42">
-        <f t="shared" ref="R4:R35" si="2">IF(J4=0,O4-Q4,0)</f>
+        <f t="shared" ref="R4:R36" si="2">IF(J4=0,O4-Q4,0)</f>
         <v>18360</v>
       </c>
       <c r="S4" s="40">
-        <f t="shared" ref="S4:S35" si="3">IF(J4=0,0,(J4*K4)-N4-(J4*K4-N4)*P4)</f>
+        <f t="shared" ref="S4:S36" si="3">IF(J4=0,0,(J4*K4)-N4-(J4*K4-N4)*P4)</f>
         <v>0</v>
       </c>
       <c r="T4" s="23">
-        <f t="shared" ref="T4:T66" si="4">R4+S4</f>
+        <f t="shared" ref="T4:T67" si="4">R4+S4</f>
         <v>18360</v>
       </c>
     </row>
@@ -12479,7 +12491,7 @@
       </c>
       <c r="I5" s="44"/>
       <c r="J5" s="43">
-        <f t="shared" ref="J5:J67" si="5">G5-H5-I5</f>
+        <f t="shared" ref="J5:J68" si="5">G5-H5-I5</f>
         <v>0</v>
       </c>
       <c r="K5" s="27">
@@ -12504,7 +12516,7 @@
         <v>0.1</v>
       </c>
       <c r="Q5" s="40">
-        <f t="shared" ref="Q5:Q67" si="6">O5*P5</f>
+        <f t="shared" ref="Q5:Q68" si="6">O5*P5</f>
         <v>5422.473</v>
       </c>
       <c r="R5" s="42">
@@ -12551,7 +12563,7 @@
         <v>648.12</v>
       </c>
       <c r="L6" s="40">
-        <f t="shared" ref="L6:L67" si="7">K6/17</f>
+        <f t="shared" ref="L6:L68" si="7">K6/17</f>
         <v>38.124705882352941</v>
       </c>
       <c r="M6" s="41">
@@ -12913,25 +12925,25 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24">
-        <v>46153</v>
+        <v>46151</v>
       </c>
       <c r="C12" s="25">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="25" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="26">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="H12" s="20">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="I12" s="44"/>
       <c r="J12" s="43">
@@ -12939,33 +12951,33 @@
         <v>0</v>
       </c>
       <c r="K12" s="27">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="L12" s="40">
         <f t="shared" si="7"/>
-        <v>25.294117647058822</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="M12" s="41">
         <f t="shared" si="0"/>
-        <v>34400</v>
+        <v>3220</v>
       </c>
       <c r="N12" s="27">
         <v>0</v>
       </c>
       <c r="O12" s="40">
         <f t="shared" si="1"/>
-        <v>34400</v>
+        <v>3220</v>
       </c>
       <c r="P12" s="22">
         <v>0.1</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="6"/>
-        <v>3440</v>
+        <v>322</v>
       </c>
       <c r="R12" s="42">
         <f t="shared" si="2"/>
-        <v>30960</v>
+        <v>2898</v>
       </c>
       <c r="S12" s="40">
         <f t="shared" si="3"/>
@@ -12973,7 +12985,7 @@
       </c>
       <c r="T12" s="23">
         <f t="shared" si="4"/>
-        <v>30960</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
@@ -12981,22 +12993,22 @@
         <v>46153</v>
       </c>
       <c r="C13" s="25">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="26">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H13" s="20">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="I13" s="44"/>
       <c r="J13" s="43">
@@ -13004,33 +13016,33 @@
         <v>0</v>
       </c>
       <c r="K13" s="27">
-        <v>386.41</v>
+        <v>430</v>
       </c>
       <c r="L13" s="40">
         <f t="shared" si="7"/>
-        <v>22.73</v>
+        <v>25.294117647058822</v>
       </c>
       <c r="M13" s="41">
         <f t="shared" si="0"/>
-        <v>15069.990000000002</v>
+        <v>34400</v>
       </c>
       <c r="N13" s="27">
         <v>0</v>
       </c>
       <c r="O13" s="40">
         <f t="shared" si="1"/>
-        <v>15069.990000000002</v>
+        <v>34400</v>
       </c>
       <c r="P13" s="22">
         <v>0.1</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
-        <v>1506.9990000000003</v>
+        <v>3440</v>
       </c>
       <c r="R13" s="42">
         <f t="shared" si="2"/>
-        <v>13562.991000000002</v>
+        <v>30960</v>
       </c>
       <c r="S13" s="40">
         <f t="shared" si="3"/>
@@ -13038,7 +13050,7 @@
       </c>
       <c r="T13" s="23">
         <f t="shared" si="4"/>
-        <v>13562.991000000002</v>
+        <v>30960</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
@@ -13046,56 +13058,56 @@
         <v>46153</v>
       </c>
       <c r="C14" s="25">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="26">
-        <v>240</v>
+        <v>39</v>
       </c>
       <c r="H14" s="20">
-        <v>240</v>
-      </c>
-      <c r="I14" s="19"/>
+        <v>39</v>
+      </c>
+      <c r="I14" s="44"/>
       <c r="J14" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K14" s="27">
-        <v>400</v>
+        <v>386.41</v>
       </c>
       <c r="L14" s="40">
         <f t="shared" si="7"/>
-        <v>23.529411764705884</v>
+        <v>22.73</v>
       </c>
       <c r="M14" s="41">
         <f t="shared" si="0"/>
-        <v>96000</v>
+        <v>15069.990000000002</v>
       </c>
       <c r="N14" s="27">
         <v>0</v>
       </c>
       <c r="O14" s="40">
         <f t="shared" si="1"/>
-        <v>96000</v>
+        <v>15069.990000000002</v>
       </c>
       <c r="P14" s="22">
         <v>0.1</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
-        <v>9600</v>
+        <v>1506.9990000000003</v>
       </c>
       <c r="R14" s="42">
         <f t="shared" si="2"/>
-        <v>86400</v>
+        <v>13562.991000000002</v>
       </c>
       <c r="S14" s="40">
         <f t="shared" si="3"/>
@@ -13103,48 +13115,64 @@
       </c>
       <c r="T14" s="23">
         <f t="shared" si="4"/>
-        <v>86400</v>
-      </c>
-      <c r="U14" s="37"/>
-      <c r="V14" s="38"/>
+        <v>13562.991000000002</v>
+      </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="20"/>
+      <c r="B15" s="24">
+        <v>46153</v>
+      </c>
+      <c r="C15" s="25">
+        <v>44</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="26">
+        <v>240</v>
+      </c>
+      <c r="H15" s="20">
+        <v>240</v>
+      </c>
       <c r="I15" s="19"/>
       <c r="J15" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K15" s="27"/>
+      <c r="K15" s="27">
+        <v>400</v>
+      </c>
       <c r="L15" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.529411764705884</v>
       </c>
       <c r="M15" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="N15" s="27">
         <v>0</v>
       </c>
       <c r="O15" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="22"/>
+        <v>96000</v>
+      </c>
+      <c r="P15" s="22">
+        <v>0.1</v>
+      </c>
       <c r="Q15" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="R15" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>86400</v>
       </c>
       <c r="S15" s="40">
         <f t="shared" si="3"/>
@@ -13152,48 +13180,66 @@
       </c>
       <c r="T15" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>86400</v>
       </c>
       <c r="U15" s="37"/>
-      <c r="V15" s="39"/>
+      <c r="V15" s="38"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="20"/>
+      <c r="B16" s="24">
+        <v>46153</v>
+      </c>
+      <c r="C16" s="25">
+        <v>45</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="26">
+        <v>330</v>
+      </c>
+      <c r="H16" s="20">
+        <v>330</v>
+      </c>
       <c r="I16" s="19"/>
       <c r="J16" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K16" s="27"/>
+      <c r="K16" s="27">
+        <v>398.36</v>
+      </c>
       <c r="L16" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.432941176470589</v>
       </c>
       <c r="M16" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>131458.80000000002</v>
       </c>
       <c r="N16" s="27">
         <v>0</v>
       </c>
       <c r="O16" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="22"/>
+        <v>131458.80000000002</v>
+      </c>
+      <c r="P16" s="22">
+        <v>0.1</v>
+      </c>
       <c r="Q16" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13145.880000000003</v>
       </c>
       <c r="R16" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>118312.92000000001</v>
       </c>
       <c r="S16" s="40">
         <f t="shared" si="3"/>
@@ -13201,8 +13247,10 @@
       </c>
       <c r="T16" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+        <v>118312.92000000001</v>
+      </c>
+      <c r="U16" s="37"/>
+      <c r="V16" s="39"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="24"/>
@@ -13210,8 +13258,8 @@
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="19"/>
       <c r="J17" s="43">
         <f t="shared" si="5"/>
@@ -13233,7 +13281,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P17" s="30"/>
+      <c r="P17" s="22"/>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -13358,7 +13406,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K20" s="31"/>
+      <c r="K20" s="27"/>
       <c r="L20" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13374,7 +13422,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P20" s="32"/>
+      <c r="P20" s="30"/>
       <c r="Q20" s="40">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -13546,7 +13594,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K24" s="27"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13593,7 +13641,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K25" s="31"/>
+      <c r="K25" s="27"/>
       <c r="L25" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13678,7 +13726,7 @@
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="33"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="25"/>
       <c r="G27" s="28"/>
       <c r="H27" s="29"/>
@@ -13687,7 +13735,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K27" s="27"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13725,7 +13773,7 @@
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="25"/>
       <c r="G28" s="28"/>
       <c r="H28" s="29"/>
@@ -13828,7 +13876,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K30" s="31"/>
+      <c r="K30" s="27"/>
       <c r="L30" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13875,7 +13923,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K31" s="27"/>
+      <c r="K31" s="31"/>
       <c r="L31" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13969,7 +14017,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="31"/>
+      <c r="K33" s="27"/>
       <c r="L33" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14016,7 +14064,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K34" s="27"/>
+      <c r="K34" s="31"/>
       <c r="L34" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14116,14 +14164,14 @@
         <v>0</v>
       </c>
       <c r="M36" s="41">
-        <f t="shared" ref="M36:M67" si="8">K36*H36</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N36" s="27">
         <v>0</v>
       </c>
       <c r="O36" s="40">
-        <f t="shared" ref="O36:O67" si="9">IF(H36="",0,M36-N36)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P36" s="32"/>
@@ -14132,11 +14180,11 @@
         <v>0</v>
       </c>
       <c r="R36" s="42">
-        <f t="shared" ref="R36:R67" si="10">IF(J36=0,O36-Q36,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S36" s="40">
-        <f t="shared" ref="S36:S67" si="11">IF(J36=0,0,(J36*K36)-N36-(J36*K36-N36)*P36)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T36" s="23">
@@ -14163,14 +14211,14 @@
         <v>0</v>
       </c>
       <c r="M37" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="M37:M68" si="8">K37*H37</f>
         <v>0</v>
       </c>
       <c r="N37" s="27">
         <v>0</v>
       </c>
       <c r="O37" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="O37:O68" si="9">IF(H37="",0,M37-N37)</f>
         <v>0</v>
       </c>
       <c r="P37" s="32"/>
@@ -14179,11 +14227,11 @@
         <v>0</v>
       </c>
       <c r="R37" s="42">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="R37:R68" si="10">IF(J37=0,O37-Q37,0)</f>
         <v>0</v>
       </c>
       <c r="S37" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="S37:S68" si="11">IF(J37=0,0,(J37*K37)-N37-(J37*K37-N37)*P37)</f>
         <v>0</v>
       </c>
       <c r="T37" s="23">
@@ -14251,7 +14299,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K39" s="31"/>
+      <c r="K39" s="27"/>
       <c r="L39" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14284,13 +14332,6 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V39" s="34"/>
-      <c r="W39" s="35"/>
-      <c r="X39" s="35"/>
-      <c r="Z39" s="35"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="35"/>
-      <c r="AC39" s="35"/>
     </row>
     <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
@@ -14305,7 +14346,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K40" s="27"/>
+      <c r="K40" s="31"/>
       <c r="L40" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14338,6 +14379,13 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="V40" s="34"/>
+      <c r="W40" s="35"/>
+      <c r="X40" s="35"/>
+      <c r="Z40" s="35"/>
+      <c r="AA40" s="34"/>
+      <c r="AB40" s="35"/>
+      <c r="AC40" s="35"/>
     </row>
     <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
@@ -14385,7 +14433,6 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z41" s="35"/>
     </row>
     <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
@@ -14433,6 +14480,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="Z42" s="35"/>
     </row>
     <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
@@ -14480,8 +14528,6 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V43" s="34"/>
-      <c r="W43" s="35"/>
     </row>
     <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
@@ -14529,6 +14575,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="V44" s="34"/>
+      <c r="W44" s="35"/>
     </row>
     <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
@@ -15335,8 +15383,8 @@
       <c r="D62" s="25"/>
       <c r="E62" s="25"/>
       <c r="F62" s="25"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="20"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="29"/>
       <c r="I62" s="19"/>
       <c r="J62" s="43">
         <f t="shared" si="5"/>
@@ -15375,8 +15423,6 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U62" s="37"/>
-      <c r="V62" s="105"/>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
@@ -15384,8 +15430,8 @@
       <c r="D63" s="25"/>
       <c r="E63" s="25"/>
       <c r="F63" s="25"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="29"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="20"/>
       <c r="I63" s="19"/>
       <c r="J63" s="43">
         <f t="shared" si="5"/>
@@ -15425,6 +15471,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="37"/>
+      <c r="V63" s="105"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
@@ -15521,7 +15568,6 @@
         <v>0</v>
       </c>
       <c r="U65" s="37"/>
-      <c r="V65" s="106"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
@@ -15536,7 +15582,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K66" s="31"/>
+      <c r="K66" s="27"/>
       <c r="L66" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -15570,6 +15616,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="37"/>
+      <c r="V66" s="106"/>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
@@ -15614,9 +15661,10 @@
         <v>0</v>
       </c>
       <c r="T67" s="23">
-        <f t="shared" ref="T67:T104" si="12">R67+S67</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U67" s="37"/>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
@@ -15628,40 +15676,40 @@
       <c r="H68" s="29"/>
       <c r="I68" s="19"/>
       <c r="J68" s="43">
-        <f t="shared" ref="J68:J104" si="13">G68-H68-I68</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="27"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="31"/>
       <c r="L68" s="40">
-        <f t="shared" ref="L68:L104" si="14">K68/17</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M68" s="41">
-        <f t="shared" ref="M68:M104" si="15">K68*H68</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N68" s="27">
         <v>0</v>
       </c>
       <c r="O68" s="40">
-        <f t="shared" ref="O68:O99" si="16">IF(H68="",0,M68-N68)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P68" s="32"/>
       <c r="Q68" s="40">
-        <f t="shared" ref="Q68:Q104" si="17">O68*P68</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R68" s="42">
-        <f t="shared" ref="R68:R99" si="18">IF(J68=0,O68-Q68,0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S68" s="40">
-        <f t="shared" ref="S68:S104" si="19">IF(J68=0,0,(J68*K68)-N68-(J68*K68-N68)*P68)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T68" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="T68:T105" si="12">R68+S68</f>
         <v>0</v>
       </c>
     </row>
@@ -15675,36 +15723,36 @@
       <c r="H69" s="29"/>
       <c r="I69" s="19"/>
       <c r="J69" s="43">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="31"/>
+        <f t="shared" ref="J69:J105" si="13">G69-H69-I69</f>
+        <v>0</v>
+      </c>
+      <c r="K69" s="27"/>
       <c r="L69" s="40">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="L69:L105" si="14">K69/17</f>
         <v>0</v>
       </c>
       <c r="M69" s="41">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="M69:M105" si="15">K69*H69</f>
         <v>0</v>
       </c>
       <c r="N69" s="27">
         <v>0</v>
       </c>
       <c r="O69" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="O69:O100" si="16">IF(H69="",0,M69-N69)</f>
         <v>0</v>
       </c>
       <c r="P69" s="32"/>
       <c r="Q69" s="40">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="Q69:Q105" si="17">O69*P69</f>
         <v>0</v>
       </c>
       <c r="R69" s="42">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="R69:R100" si="18">IF(J69=0,O69-Q69,0)</f>
         <v>0</v>
       </c>
       <c r="S69" s="40">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="S69:S105" si="19">IF(J69=0,0,(J69*K69)-N69-(J69*K69-N69)*P69)</f>
         <v>0</v>
       </c>
       <c r="T69" s="23">
@@ -15725,7 +15773,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K70" s="27"/>
+      <c r="K70" s="31"/>
       <c r="L70" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15819,7 +15867,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K72" s="31"/>
+      <c r="K72" s="27"/>
       <c r="L72" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15960,7 +16008,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K75" s="27"/>
+      <c r="K75" s="31"/>
       <c r="L75" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16371,9 +16419,6 @@
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A84" s="36">
-        <v>46057</v>
-      </c>
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -16386,7 +16431,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K84" s="31"/>
+      <c r="K84" s="27"/>
       <c r="L84" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16421,6 +16466,9 @@
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A85" s="36">
+        <v>46057</v>
+      </c>
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
@@ -16668,7 +16716,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K90" s="27"/>
+      <c r="K90" s="31"/>
       <c r="L90" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16715,7 +16763,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K91" s="31"/>
+      <c r="K91" s="27"/>
       <c r="L91" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16796,7 +16844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -16842,9 +16890,8 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U93" s="11"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -16890,6 +16937,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="U94" s="11"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
@@ -17152,7 +17200,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="40">
-        <f t="shared" ref="O100:O104" si="20">IF(H100="",0,M100-N100)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="P100" s="32"/>
@@ -17161,7 +17209,7 @@
         <v>0</v>
       </c>
       <c r="R100" s="42">
-        <f t="shared" ref="R100:R104" si="21">IF(J100=0,O100-Q100,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="S100" s="40">
@@ -17199,7 +17247,7 @@
         <v>0</v>
       </c>
       <c r="O101" s="40">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="O101:O105" si="20">IF(H101="",0,M101-N101)</f>
         <v>0</v>
       </c>
       <c r="P101" s="32"/>
@@ -17208,7 +17256,7 @@
         <v>0</v>
       </c>
       <c r="R101" s="42">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="R101:R105" si="21">IF(J101=0,O101-Q101,0)</f>
         <v>0</v>
       </c>
       <c r="S101" s="40">
@@ -17233,7 +17281,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K102" s="27"/>
+      <c r="K102" s="31"/>
       <c r="L102" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -17280,7 +17328,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K103" s="31"/>
+      <c r="K103" s="27"/>
       <c r="L103" s="40">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -17315,7 +17363,7 @@
       </c>
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B104" s="25"/>
+      <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
       <c r="E104" s="25"/>
@@ -17343,7 +17391,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P104" s="27"/>
+      <c r="P104" s="32"/>
       <c r="Q104" s="40">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -17361,8 +17409,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="105" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B105" s="25"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="25"/>
+      <c r="E105" s="25"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="29"/>
+      <c r="I105" s="19"/>
+      <c r="J105" s="43">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="31"/>
+      <c r="L105" s="40">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="41">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N105" s="27">
+        <v>0</v>
+      </c>
+      <c r="O105" s="40">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P105" s="27"/>
+      <c r="Q105" s="40">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R105" s="42">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="S105" s="40">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="T105" s="23">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="R4:R104">
+  <conditionalFormatting sqref="R4:R105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>IF($J4&gt;0,TRUE,FALSE)</formula>
     </cfRule>
@@ -17400,7 +17495,7 @@
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>10.835580665156026</v>
+        <v>10.188612480058529</v>
       </c>
       <c r="J1" s="140" t="s">
         <v>36</v>
@@ -17416,15 +17511,15 @@
       </c>
       <c r="G2" s="51">
         <f>I2/F2</f>
-        <v>184.20487130765244</v>
+        <v>173.206412160995</v>
       </c>
       <c r="H2" s="52">
         <f>SUM(H4:H391)</f>
-        <v>4400</v>
+        <v>49400</v>
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I391)</f>
-        <v>1066362</v>
+        <v>1002691.92</v>
       </c>
       <c r="J2" s="54">
         <f>O39</f>
@@ -17432,7 +17527,7 @@
       </c>
       <c r="K2" s="55">
         <f>O45</f>
-        <v>360097</v>
+        <v>305673.56000000006</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -18423,14 +18518,14 @@
       </c>
       <c r="G26" s="83">
         <f>Tomatillo!K26</f>
-        <v>119</v>
+        <v>104.04</v>
       </c>
       <c r="H26" s="93">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I26" s="84">
         <f t="shared" si="3"/>
-        <v>148512</v>
+        <v>84841.920000000013</v>
       </c>
       <c r="J26" s="94" t="s">
         <v>54</v>
@@ -18734,7 +18829,7 @@
       </c>
       <c r="O41" s="67">
         <f>Tomatillo!Q2</f>
-        <v>106636.20000000001</v>
+        <v>92709.664000000019</v>
       </c>
     </row>
     <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18763,7 +18858,7 @@
       </c>
       <c r="O43" s="67">
         <f>Tomatillo!T2</f>
-        <v>959725.8</v>
+        <v>919228.89600000007</v>
       </c>
     </row>
     <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18792,7 +18887,7 @@
       </c>
       <c r="O45" s="67">
         <f>+O43+O41-O39</f>
-        <v>360097</v>
+        <v>305673.56000000006</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
@@ -19545,7 +19640,7 @@
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>165869.32000000007</v>
+        <v>300548.12000000011</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -19921,27 +20016,27 @@
       <c r="O11" s="72"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="176">
-        <f>Roma!B12</f>
+      <c r="B12" s="91">
+        <f>Roma!B13</f>
         <v>46153</v>
       </c>
-      <c r="C12" s="175">
-        <f>Roma!C12</f>
+      <c r="C12" s="85">
+        <f>Roma!C13</f>
         <v>42</v>
       </c>
-      <c r="D12" s="175" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="175" t="str">
-        <f>Roma!E12</f>
-        <v>Epifania Lopez</v>
-      </c>
-      <c r="F12" s="177">
-        <f>Roma!H12</f>
+      <c r="D12" s="85" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="85" t="str">
+        <f>Roma!E13</f>
+        <v>Epifanio Lopez</v>
+      </c>
+      <c r="F12" s="25">
+        <f>Roma!H13</f>
         <v>80</v>
       </c>
       <c r="G12" s="75">
-        <f>Roma!K12</f>
+        <f>Roma!K13</f>
         <v>430</v>
       </c>
       <c r="H12" s="84">
@@ -19951,7 +20046,7 @@
         <f t="shared" si="0"/>
         <v>34400</v>
       </c>
-      <c r="J12" s="178" t="s">
+      <c r="J12" s="94" t="s">
         <v>54</v>
       </c>
       <c r="K12" s="73"/>
@@ -19959,27 +20054,27 @@
       <c r="O12" s="72"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="176">
-        <f>Roma!B13</f>
+      <c r="B13" s="91">
+        <f>Roma!B14</f>
         <v>46153</v>
       </c>
-      <c r="C13" s="175">
-        <f>Roma!C13</f>
+      <c r="C13" s="85">
+        <f>Roma!C14</f>
         <v>43</v>
       </c>
-      <c r="D13" s="175" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="175" t="str">
-        <f>Roma!E13</f>
+      <c r="D13" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="85" t="str">
+        <f>Roma!E14</f>
         <v>Mayojoa</v>
       </c>
-      <c r="F13" s="177">
-        <f>Roma!H13</f>
+      <c r="F13" s="25">
+        <f>Roma!H14</f>
         <v>39</v>
       </c>
       <c r="G13" s="75">
-        <f>Roma!K13</f>
+        <f>Roma!K14</f>
         <v>386.41</v>
       </c>
       <c r="H13" s="84">
@@ -19989,7 +20084,7 @@
         <f>F13*G13-H13</f>
         <v>15069.990000000002</v>
       </c>
-      <c r="J13" s="178" t="s">
+      <c r="J13" s="94" t="s">
         <v>54</v>
       </c>
       <c r="K13" s="73"/>
@@ -19997,37 +20092,37 @@
       <c r="O13" s="72"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="176">
-        <f>Roma!B14</f>
+      <c r="B14" s="91">
+        <f>Roma!B15</f>
         <v>46153</v>
       </c>
-      <c r="C14" s="175">
-        <f>Roma!C14</f>
+      <c r="C14" s="85">
+        <f>Roma!C15</f>
         <v>44</v>
       </c>
-      <c r="D14" s="175" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="175" t="str">
-        <f>Roma!E14</f>
+      <c r="D14" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="85" t="str">
+        <f>Roma!E15</f>
         <v>Efrén Medina</v>
       </c>
-      <c r="F14" s="177">
-        <f>Roma!H14</f>
+      <c r="F14" s="25">
+        <f>Roma!H15</f>
         <v>240</v>
       </c>
       <c r="G14" s="75">
-        <f>Roma!K14</f>
+        <f>Roma!K15</f>
         <v>400</v>
       </c>
       <c r="H14" s="84">
         <v>0</v>
       </c>
       <c r="I14" s="75">
-        <f t="shared" ref="I14:I18" si="2">F14*G14-H14</f>
+        <f t="shared" ref="I14" si="2">F14*G14-H14</f>
         <v>96000</v>
       </c>
-      <c r="J14" s="178" t="s">
+      <c r="J14" s="94" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="73"/>
@@ -20038,7 +20133,7 @@
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="91"/>
-      <c r="C15" s="175"/>
+      <c r="C15" s="85"/>
       <c r="D15" s="85"/>
       <c r="E15" s="85"/>
       <c r="F15" s="25"/>
@@ -20382,7 +20477,7 @@
       </c>
       <c r="O40" s="67">
         <f>Roma!Q2</f>
-        <v>66396.432000000001</v>
+        <v>79864.312000000005</v>
       </c>
     </row>
     <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20411,7 +20506,7 @@
       </c>
       <c r="O42" s="67">
         <f>+Roma!R2</f>
-        <v>597567.88800000004</v>
+        <v>718778.80800000008</v>
       </c>
     </row>
     <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20440,7 +20535,7 @@
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>165869.32000000007</v>
+        <v>300548.12000000011</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
@@ -22671,7 +22766,7 @@
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
-        <v>1066362</v>
+        <v>1011938.56</v>
       </c>
       <c r="F5" s="167">
         <f>+'Estado de Cuenta T'!O39</f>
@@ -22679,19 +22774,19 @@
       </c>
       <c r="G5" s="171">
         <f>+E5-F5</f>
-        <v>360097</v>
+        <v>305673.56000000006</v>
       </c>
       <c r="H5" s="167"/>
       <c r="I5" s="167">
         <f>+Tomatillo!Q2</f>
-        <v>106636.20000000001</v>
+        <v>92709.664000000019</v>
       </c>
       <c r="J5" s="167">
         <v>60149</v>
       </c>
       <c r="K5" s="167">
         <f>+G5-I5+J5</f>
-        <v>313609.8</v>
+        <v>273112.89600000007</v>
       </c>
     </row>
     <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22700,7 +22795,7 @@
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
-        <v>663964.32000000007</v>
+        <v>798643.12000000011</v>
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
@@ -22708,19 +22803,19 @@
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>165869.32000000007</v>
+        <v>300548.12000000011</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
         <f>+Roma!Q2</f>
-        <v>66396.432000000001</v>
+        <v>79864.312000000005</v>
       </c>
       <c r="J6" s="167">
         <v>11968</v>
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>111440.88800000006</v>
+        <v>232651.80800000011</v>
       </c>
     </row>
     <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22764,7 +22859,7 @@
     <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
-        <v>1738706.32</v>
+        <v>1818961.6800000002</v>
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
@@ -22772,12 +22867,12 @@
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>534346.32000000007</v>
+        <v>614601.68000000017</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
         <f>SUM(I5:I8)</f>
-        <v>173870.63200000001</v>
+        <v>173411.97600000002</v>
       </c>
       <c r="J9" s="168">
         <f>SUM(J5:J8)</f>
@@ -22785,7 +22880,7 @@
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>432592.68800000008</v>
+        <v>513306.70400000014</v>
       </c>
     </row>
     <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22805,7 +22900,7 @@
       <c r="H11" s="167"/>
       <c r="I11" s="167">
         <f>+I9-J9</f>
-        <v>101753.63200000001</v>
+        <v>101294.97600000002</v>
       </c>
       <c r="J11" s="167"/>
       <c r="K11" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1493" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1747E9F-6FB8-4C3B-AA20-08E19BC75B22}"/>
+  <xr:revisionPtr revIDLastSave="1495" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC46687-1895-4A1D-8C9E-717A39440413}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="100">
   <si>
     <t>TOTAL</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Epifanio Lopez</t>
+  </si>
+  <si>
+    <t>20260508-01</t>
   </si>
 </sst>
 </file>
@@ -12303,15 +12306,15 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>452.91670321361062</v>
+        <v>452.96204347826091</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>29.602398902850368</v>
+        <v>29.605362318840584</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M495)</f>
-        <v>798643.12000000011</v>
+        <v>798723.07000000007</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N495)</f>
@@ -12319,7 +12322,7 @@
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O495)</f>
-        <v>798643.12000000011</v>
+        <v>798723.07000000007</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
@@ -12327,11 +12330,11 @@
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q495)</f>
-        <v>79864.312000000005</v>
+        <v>79872.307000000001</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R495)</f>
-        <v>718778.80800000008</v>
+        <v>718850.76300000004</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S495)</f>
@@ -12339,7 +12342,7 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T495)</f>
-        <v>718778.80800000008</v>
+        <v>718850.76300000004</v>
       </c>
       <c r="V2" s="12"/>
     </row>
@@ -13081,33 +13084,33 @@
         <v>0</v>
       </c>
       <c r="K14" s="27">
-        <v>386.41</v>
+        <v>388.46</v>
       </c>
       <c r="L14" s="40">
         <f t="shared" si="7"/>
-        <v>22.73</v>
+        <v>22.850588235294115</v>
       </c>
       <c r="M14" s="41">
         <f t="shared" si="0"/>
-        <v>15069.990000000002</v>
+        <v>15149.939999999999</v>
       </c>
       <c r="N14" s="27">
         <v>0</v>
       </c>
       <c r="O14" s="40">
         <f t="shared" si="1"/>
-        <v>15069.990000000002</v>
+        <v>15149.939999999999</v>
       </c>
       <c r="P14" s="22">
         <v>0.1</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
-        <v>1506.9990000000003</v>
+        <v>1514.9939999999999</v>
       </c>
       <c r="R14" s="42">
         <f t="shared" si="2"/>
-        <v>13562.991000000002</v>
+        <v>13634.945999999998</v>
       </c>
       <c r="S14" s="40">
         <f t="shared" si="3"/>
@@ -13115,7 +13118,7 @@
       </c>
       <c r="T14" s="23">
         <f t="shared" si="4"/>
-        <v>13562.991000000002</v>
+        <v>13634.945999999998</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
@@ -18654,7 +18657,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="86" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E30" s="81" t="str">
         <f>Tomatillo!E30</f>
@@ -19608,7 +19611,7 @@
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>31.245379764705884</v>
+        <v>31.249142117647061</v>
       </c>
       <c r="J1" s="140" t="s">
         <v>36</v>
@@ -19624,7 +19627,7 @@
       </c>
       <c r="G2" s="146">
         <f>I2/F2</f>
-        <v>531.17145600000003</v>
+        <v>531.23541599999999</v>
       </c>
       <c r="H2" s="147">
         <f>SUM(H4:H390)</f>
@@ -19632,7 +19635,7 @@
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I390)</f>
-        <v>663964.32000000007</v>
+        <v>664044.27</v>
       </c>
       <c r="J2" s="148">
         <f>O38</f>
@@ -19640,7 +19643,7 @@
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>300548.12000000011</v>
+        <v>300628.07000000007</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -20075,14 +20078,14 @@
       </c>
       <c r="G13" s="75">
         <f>Roma!K14</f>
-        <v>386.41</v>
+        <v>388.46</v>
       </c>
       <c r="H13" s="84">
         <v>0</v>
       </c>
       <c r="I13" s="75">
         <f>F13*G13-H13</f>
-        <v>15069.990000000002</v>
+        <v>15149.939999999999</v>
       </c>
       <c r="J13" s="94" t="s">
         <v>54</v>
@@ -20477,7 +20480,7 @@
       </c>
       <c r="O40" s="67">
         <f>Roma!Q2</f>
-        <v>79864.312000000005</v>
+        <v>79872.307000000001</v>
       </c>
     </row>
     <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20506,7 +20509,7 @@
       </c>
       <c r="O42" s="67">
         <f>+Roma!R2</f>
-        <v>718778.80800000008</v>
+        <v>718850.76300000004</v>
       </c>
     </row>
     <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20535,7 +20538,7 @@
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>300548.12000000011</v>
+        <v>300628.07000000007</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
@@ -22795,7 +22798,7 @@
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
-        <v>798643.12000000011</v>
+        <v>798723.07000000007</v>
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
@@ -22803,19 +22806,19 @@
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>300548.12000000011</v>
+        <v>300628.07000000007</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
         <f>+Roma!Q2</f>
-        <v>79864.312000000005</v>
+        <v>79872.307000000001</v>
       </c>
       <c r="J6" s="167">
         <v>11968</v>
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>232651.80800000011</v>
+        <v>232723.76300000006</v>
       </c>
     </row>
     <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22859,7 +22862,7 @@
     <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
-        <v>1818961.6800000002</v>
+        <v>1819041.6300000001</v>
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
@@ -22867,12 +22870,12 @@
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>614601.68000000017</v>
+        <v>614681.63000000012</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
         <f>SUM(I5:I8)</f>
-        <v>173411.97600000002</v>
+        <v>173419.97100000002</v>
       </c>
       <c r="J9" s="168">
         <f>SUM(J5:J8)</f>
@@ -22880,7 +22883,7 @@
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>513306.70400000014</v>
+        <v>513378.6590000001</v>
       </c>
     </row>
     <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22900,7 +22903,7 @@
       <c r="H11" s="167"/>
       <c r="I11" s="167">
         <f>+I9-J9</f>
-        <v>101294.97600000002</v>
+        <v>101302.97100000002</v>
       </c>
       <c r="J11" s="167"/>
       <c r="K11" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1495" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC46687-1895-4A1D-8C9E-717A39440413}"/>
+  <xr:revisionPtr revIDLastSave="1546" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97330A74-7CD5-4504-A3C9-C10CE62B446E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="102">
   <si>
     <t>TOTAL</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>20260508-01</t>
+  </si>
+  <si>
+    <t>20260511-04</t>
+  </si>
+  <si>
+    <t>20260512-01</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1006,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1525,6 +1531,21 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1585,7 +1606,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1965,27 +1986,27 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>155.98657661632447</v>
+        <v>155.99032343458342</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>10.101102604286243</v>
+        <v>10.101323005360298</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M495)</f>
-        <v>1061338.5599999998</v>
+        <v>1016360.64</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N495)</f>
-        <v>49400</v>
+        <v>4400</v>
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O495)</f>
-        <v>1011938.56</v>
+        <v>1011960.64</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
-        <v>9.1615902056346205E-2</v>
+        <v>9.161390308619119E-2</v>
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q495)</f>
@@ -1993,7 +2014,7 @@
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R495)</f>
-        <v>919228.89600000007</v>
+        <v>919250.97600000002</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S495)</f>
@@ -2001,7 +2022,7 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T495)</f>
-        <v>919228.89600000007</v>
+        <v>919250.97600000002</v>
       </c>
       <c r="V2" s="12"/>
     </row>
@@ -3543,23 +3564,23 @@
         <v>0</v>
       </c>
       <c r="K26" s="123">
-        <f>6.12*17</f>
-        <v>104.04</v>
+        <f>4*17</f>
+        <v>68</v>
       </c>
       <c r="L26" s="124">
         <f t="shared" si="6"/>
-        <v>6.12</v>
+        <v>4</v>
       </c>
       <c r="M26" s="123">
         <f t="shared" si="0"/>
-        <v>129841.92000000001</v>
+        <v>84864</v>
       </c>
       <c r="N26" s="123">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="O26" s="124">
         <f t="shared" si="1"/>
-        <v>84841.920000000013</v>
+        <v>84864</v>
       </c>
       <c r="P26" s="175">
         <v>0</v>
@@ -3570,7 +3591,7 @@
       </c>
       <c r="R26" s="126">
         <f t="shared" si="2"/>
-        <v>84841.920000000013</v>
+        <v>84864</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="3"/>
@@ -3578,7 +3599,7 @@
       </c>
       <c r="T26" s="126">
         <f t="shared" si="4"/>
-        <v>84841.920000000013</v>
+        <v>84864</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -17498,7 +17519,7 @@
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>10.188612480058529</v>
+        <v>10.101323005360298</v>
       </c>
       <c r="J1" s="140" t="s">
         <v>36</v>
@@ -17510,27 +17531,27 @@
       </c>
       <c r="F2" s="50">
         <f>SUM(F4:F391)</f>
-        <v>5789</v>
+        <v>5893</v>
       </c>
       <c r="G2" s="51">
         <f>I2/F2</f>
-        <v>173.206412160995</v>
+        <v>171.72249109112508</v>
       </c>
       <c r="H2" s="52">
         <f>SUM(H4:H391)</f>
-        <v>49400</v>
+        <v>4400</v>
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I391)</f>
-        <v>1002691.92</v>
+        <v>1011960.64</v>
       </c>
       <c r="J2" s="54">
         <f>O39</f>
-        <v>706265</v>
+        <v>731832</v>
       </c>
       <c r="K2" s="55">
         <f>O45</f>
-        <v>305673.56000000006</v>
+        <v>280128.64000000001</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -18124,8 +18145,13 @@
       </c>
       <c r="L15" s="74"/>
       <c r="M15" s="74"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="72"/>
+      <c r="N15" s="71">
+        <v>46154</v>
+      </c>
+      <c r="O15" s="72">
+        <f>16320+9247</f>
+        <v>25567</v>
+      </c>
     </row>
     <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="107">
@@ -18521,14 +18547,14 @@
       </c>
       <c r="G26" s="83">
         <f>Tomatillo!K26</f>
-        <v>104.04</v>
+        <v>68</v>
       </c>
       <c r="H26" s="93">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="I26" s="84">
         <f t="shared" si="3"/>
-        <v>84841.920000000013</v>
+        <v>84864</v>
       </c>
       <c r="J26" s="94" t="s">
         <v>54</v>
@@ -18648,52 +18674,76 @@
       <c r="O29" s="72"/>
     </row>
     <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="136">
+      <c r="B30" s="107">
         <f>Tomatillo!B30</f>
         <v>46150</v>
       </c>
-      <c r="C30" s="81">
+      <c r="C30" s="108">
         <f>Tomatillo!C30</f>
         <v>37</v>
       </c>
-      <c r="D30" s="86" t="s">
+      <c r="D30" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="81" t="str">
+      <c r="E30" s="108" t="str">
         <f>Tomatillo!E30</f>
         <v>Efrén Medina</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="109">
         <f>Tomatillo!G30</f>
         <v>120</v>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="110">
         <f>Tomatillo!K30</f>
         <v>136</v>
       </c>
-      <c r="H30" s="75">
-        <v>0</v>
-      </c>
-      <c r="I30" s="84">
+      <c r="H30" s="115">
+        <v>0</v>
+      </c>
+      <c r="I30" s="111">
         <f t="shared" ref="I30" si="4">F30*G30-H30</f>
         <v>16320</v>
       </c>
-      <c r="J30" s="94" t="s">
-        <v>54</v>
+      <c r="J30" s="138" t="s">
+        <v>45</v>
       </c>
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
     <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="136"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="92"/>
+      <c r="B31" s="107">
+        <f>Tomatillo!B31</f>
+        <v>46154</v>
+      </c>
+      <c r="C31" s="108">
+        <f>Tomatillo!C31</f>
+        <v>46</v>
+      </c>
+      <c r="D31" s="113" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="108" t="str">
+        <f>Tomatillo!E31</f>
+        <v>Mayojoa</v>
+      </c>
+      <c r="F31" s="109">
+        <f>Tomatillo!G31</f>
+        <v>104</v>
+      </c>
+      <c r="G31" s="110">
+        <f>Tomatillo!K31</f>
+        <v>88.910000000000011</v>
+      </c>
+      <c r="H31" s="115">
+        <v>0</v>
+      </c>
+      <c r="I31" s="111">
+        <f t="shared" ref="I31" si="5">F31*G31-H31</f>
+        <v>9246.6400000000012</v>
+      </c>
+      <c r="J31" s="138" t="s">
+        <v>45</v>
+      </c>
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
@@ -18803,7 +18853,7 @@
       </c>
       <c r="O39" s="67">
         <f>SUM(O4:O38)</f>
-        <v>706265</v>
+        <v>731832</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18861,7 +18911,7 @@
       </c>
       <c r="O43" s="67">
         <f>Tomatillo!T2</f>
-        <v>919228.89600000007</v>
+        <v>919250.97600000002</v>
       </c>
     </row>
     <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18890,7 +18940,7 @@
       </c>
       <c r="O45" s="67">
         <f>+O43+O41-O39</f>
-        <v>305673.56000000006</v>
+        <v>280128.64000000001</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
@@ -19611,7 +19661,7 @@
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>31.249142117647061</v>
+        <v>29.6166444527178</v>
       </c>
       <c r="J1" s="140" t="s">
         <v>36</v>
@@ -19623,11 +19673,11 @@
       </c>
       <c r="F2" s="145">
         <f>SUM(F4:F390)</f>
-        <v>1250</v>
+        <v>1580</v>
       </c>
       <c r="G2" s="146">
         <f>I2/F2</f>
-        <v>531.23541599999999</v>
+        <v>503.48295569620257</v>
       </c>
       <c r="H2" s="147">
         <f>SUM(H4:H390)</f>
@@ -19635,15 +19685,15 @@
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I390)</f>
-        <v>664044.27</v>
+        <v>795503.07000000007</v>
       </c>
       <c r="J2" s="148">
         <f>O38</f>
-        <v>498095</v>
+        <v>643645</v>
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>300628.07000000007</v>
+        <v>155078.07000000007</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -19938,8 +19988,12 @@
         <v>45</v>
       </c>
       <c r="K9" s="73"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="72"/>
+      <c r="N9" s="71">
+        <v>46155</v>
+      </c>
+      <c r="O9" s="72">
+        <v>145550</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="173">
@@ -20019,114 +20073,114 @@
       <c r="O11" s="72"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="91">
+      <c r="B12" s="173">
         <f>Roma!B13</f>
         <v>46153</v>
       </c>
-      <c r="C12" s="85">
+      <c r="C12" s="113">
         <f>Roma!C13</f>
         <v>42</v>
       </c>
-      <c r="D12" s="85" t="s">
+      <c r="D12" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="E12" s="85" t="str">
+      <c r="E12" s="113" t="str">
         <f>Roma!E13</f>
         <v>Epifanio Lopez</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="174">
         <f>Roma!H13</f>
         <v>80</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="115">
         <f>Roma!K13</f>
         <v>430</v>
       </c>
-      <c r="H12" s="84">
-        <v>0</v>
-      </c>
-      <c r="I12" s="75">
+      <c r="H12" s="111">
+        <v>0</v>
+      </c>
+      <c r="I12" s="115">
         <f t="shared" si="0"/>
         <v>34400</v>
       </c>
-      <c r="J12" s="94" t="s">
-        <v>54</v>
+      <c r="J12" s="180" t="s">
+        <v>45</v>
       </c>
       <c r="K12" s="73"/>
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="91">
+      <c r="B13" s="173">
         <f>Roma!B14</f>
         <v>46153</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="113">
         <f>Roma!C14</f>
         <v>43</v>
       </c>
-      <c r="D13" s="85" t="s">
+      <c r="D13" s="113" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="85" t="str">
+      <c r="E13" s="113" t="str">
         <f>Roma!E14</f>
         <v>Mayojoa</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="174">
         <f>Roma!H14</f>
         <v>39</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="115">
         <f>Roma!K14</f>
         <v>388.46</v>
       </c>
-      <c r="H13" s="84">
-        <v>0</v>
-      </c>
-      <c r="I13" s="75">
+      <c r="H13" s="111">
+        <v>0</v>
+      </c>
+      <c r="I13" s="115">
         <f>F13*G13-H13</f>
         <v>15149.939999999999</v>
       </c>
-      <c r="J13" s="94" t="s">
-        <v>54</v>
+      <c r="J13" s="180" t="s">
+        <v>45</v>
       </c>
       <c r="K13" s="73"/>
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="91">
+      <c r="B14" s="173">
         <f>Roma!B15</f>
         <v>46153</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="113">
         <f>Roma!C15</f>
         <v>44</v>
       </c>
-      <c r="D14" s="85" t="s">
+      <c r="D14" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="85" t="str">
+      <c r="E14" s="113" t="str">
         <f>Roma!E15</f>
         <v>Efrén Medina</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="174">
         <f>Roma!H15</f>
         <v>240</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="115">
         <f>Roma!K15</f>
         <v>400</v>
       </c>
-      <c r="H14" s="84">
-        <v>0</v>
-      </c>
-      <c r="I14" s="75">
+      <c r="H14" s="111">
+        <v>0</v>
+      </c>
+      <c r="I14" s="115">
         <f t="shared" ref="I14" si="2">F14*G14-H14</f>
         <v>96000</v>
       </c>
-      <c r="J14" s="94" t="s">
-        <v>54</v>
+      <c r="J14" s="180" t="s">
+        <v>45</v>
       </c>
       <c r="K14" s="73"/>
       <c r="L14" s="74"/>
@@ -20135,15 +20189,38 @@
       <c r="O14" s="72"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="91"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="92"/>
+      <c r="B15" s="91">
+        <f>Roma!B16</f>
+        <v>46153</v>
+      </c>
+      <c r="C15" s="85">
+        <f>Roma!C16</f>
+        <v>45</v>
+      </c>
+      <c r="D15" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="25">
+        <f>Roma!H16</f>
+        <v>330</v>
+      </c>
+      <c r="G15" s="75">
+        <f>Roma!K16</f>
+        <v>398.36</v>
+      </c>
+      <c r="H15" s="84">
+        <v>0</v>
+      </c>
+      <c r="I15" s="75">
+        <f t="shared" ref="I15" si="3">F15*G15-H15</f>
+        <v>131458.80000000002</v>
+      </c>
+      <c r="J15" s="94" t="s">
+        <v>54</v>
+      </c>
       <c r="K15" s="73"/>
       <c r="L15" s="74"/>
       <c r="M15" s="74"/>
@@ -20451,7 +20528,7 @@
       </c>
       <c r="O38" s="67">
         <f>SUM(O4:O37)</f>
-        <v>498095</v>
+        <v>643645</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20538,7 +20615,7 @@
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>300628.07000000007</v>
+        <v>155078.07000000007</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
@@ -21287,11 +21364,11 @@
       </c>
       <c r="J2" s="148">
         <f>O38</f>
-        <v>0</v>
+        <v>5980</v>
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>8380</v>
+        <v>2400</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -21382,42 +21459,46 @@
       <c r="L4" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="69"/>
-      <c r="O4" s="70"/>
+      <c r="N4" s="69">
+        <v>46154</v>
+      </c>
+      <c r="O4" s="70">
+        <v>5980</v>
+      </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="149">
+      <c r="B5" s="176">
         <f>Morrón!B5</f>
         <v>46151</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="177">
         <f>Morrón!C5</f>
         <v>40</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="113" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="150" t="str">
+      <c r="E5" s="177" t="str">
         <f>Morrón!E5</f>
         <v>Mayojoa</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="178">
         <f>Morrón!G5</f>
         <v>23</v>
       </c>
-      <c r="G5" s="84">
+      <c r="G5" s="111">
         <f>Morrón!K5</f>
         <v>260</v>
       </c>
-      <c r="H5" s="84">
-        <v>0</v>
-      </c>
-      <c r="I5" s="84">
+      <c r="H5" s="111">
+        <v>0</v>
+      </c>
+      <c r="I5" s="111">
         <f t="shared" ref="I5" si="1">F5*G5-H5</f>
         <v>5980</v>
       </c>
-      <c r="J5" s="157" t="s">
-        <v>54</v>
+      <c r="J5" s="179" t="s">
+        <v>45</v>
       </c>
       <c r="N5" s="71"/>
       <c r="O5" s="72"/>
@@ -21933,7 +22014,7 @@
       </c>
       <c r="O38" s="67">
         <f>SUM(O4:O37)</f>
-        <v>0</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -22020,7 +22101,7 @@
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>8380</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
@@ -22769,15 +22850,15 @@
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
-        <v>1011938.56</v>
+        <v>1011960.64</v>
       </c>
       <c r="F5" s="167">
         <f>+'Estado de Cuenta T'!O39</f>
-        <v>706265</v>
+        <v>731832</v>
       </c>
       <c r="G5" s="171">
         <f>+E5-F5</f>
-        <v>305673.56000000006</v>
+        <v>280128.64000000001</v>
       </c>
       <c r="H5" s="167"/>
       <c r="I5" s="167">
@@ -22789,7 +22870,7 @@
       </c>
       <c r="K5" s="167">
         <f>+G5-I5+J5</f>
-        <v>273112.89600000007</v>
+        <v>247567.976</v>
       </c>
     </row>
     <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22802,11 +22883,11 @@
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
-        <v>498095</v>
+        <v>643645</v>
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>300628.07000000007</v>
+        <v>155078.07000000007</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
@@ -22818,7 +22899,7 @@
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>232723.76300000006</v>
+        <v>87173.763000000064</v>
       </c>
     </row>
     <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22831,11 +22912,11 @@
       </c>
       <c r="F7" s="167">
         <f>+'Estado de Cuenta M'!O38</f>
-        <v>0</v>
+        <v>5980</v>
       </c>
       <c r="G7" s="171">
         <f>+E7-F7</f>
-        <v>8380</v>
+        <v>2400</v>
       </c>
       <c r="H7" s="167"/>
       <c r="I7" s="167">
@@ -22847,7 +22928,7 @@
       </c>
       <c r="K7" s="167">
         <f t="shared" si="0"/>
-        <v>7542</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="8" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22862,15 +22943,15 @@
     <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
-        <v>1819041.6300000001</v>
+        <v>1819063.71</v>
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
-        <v>1204360</v>
+        <v>1381457</v>
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>614681.63000000012</v>
+        <v>437606.71000000008</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
@@ -22883,7 +22964,7 @@
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>513378.6590000001</v>
+        <v>336303.73900000006</v>
       </c>
     </row>
     <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1546" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97330A74-7CD5-4504-A3C9-C10CE62B446E}"/>
+  <xr:revisionPtr revIDLastSave="1610" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50BE2939-4C9C-4BC2-8F23-52F802B58402}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="106">
   <si>
     <t>TOTAL</t>
   </si>
@@ -349,6 +349,18 @@
   </si>
   <si>
     <t>20260512-01</t>
+  </si>
+  <si>
+    <t>$45 mil pesos de flete pagados por H2E</t>
+  </si>
+  <si>
+    <t>20260513-01</t>
+  </si>
+  <si>
+    <t>20260513-02</t>
+  </si>
+  <si>
+    <t>20260513-03</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1018,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1543,9 +1555,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1986,15 +1995,15 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>155.99032343458342</v>
+        <v>163.6227551332089</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>10.101323005360298</v>
+        <v>10.55028957586768</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M495)</f>
-        <v>1016360.64</v>
+        <v>1061338.5599999998</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N495)</f>
@@ -2002,11 +2011,11 @@
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O495)</f>
-        <v>1011960.64</v>
+        <v>1056938.56</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
-        <v>9.161390308619119E-2</v>
+        <v>8.7715282144687781E-2</v>
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q495)</f>
@@ -2014,7 +2023,7 @@
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R495)</f>
-        <v>919250.97600000002</v>
+        <v>964228.89600000007</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S495)</f>
@@ -2022,7 +2031,7 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T495)</f>
-        <v>919250.97600000002</v>
+        <v>964228.89600000007</v>
       </c>
       <c r="V2" s="12"/>
     </row>
@@ -3564,23 +3573,23 @@
         <v>0</v>
       </c>
       <c r="K26" s="123">
-        <f>4*17</f>
-        <v>68</v>
+        <f>6.12*17</f>
+        <v>104.04</v>
       </c>
       <c r="L26" s="124">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>6.12</v>
       </c>
       <c r="M26" s="123">
         <f t="shared" si="0"/>
-        <v>84864</v>
+        <v>129841.92000000001</v>
       </c>
       <c r="N26" s="123">
         <v>0</v>
       </c>
       <c r="O26" s="124">
         <f t="shared" si="1"/>
-        <v>84864</v>
+        <v>129841.92000000001</v>
       </c>
       <c r="P26" s="175">
         <v>0</v>
@@ -3591,7 +3600,7 @@
       </c>
       <c r="R26" s="126">
         <f t="shared" si="2"/>
-        <v>84864</v>
+        <v>129841.92000000001</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="3"/>
@@ -3599,7 +3608,10 @@
       </c>
       <c r="T26" s="126">
         <f t="shared" si="4"/>
-        <v>84864</v>
+        <v>129841.92000000001</v>
+      </c>
+      <c r="U26" s="127" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -12311,11 +12323,11 @@
       </c>
       <c r="G2" s="4">
         <f>SUM(G4:G495)</f>
-        <v>1587</v>
+        <v>1757</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(H4:H495)</f>
-        <v>1587</v>
+        <v>1757</v>
       </c>
       <c r="I2" s="6">
         <f>SUM(I4:I495)</f>
@@ -12327,15 +12339,15 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>452.96204347826091</v>
+        <v>443.04539726807059</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>29.605362318840584</v>
+        <v>28.957215507717034</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M495)</f>
-        <v>798723.07000000007</v>
+        <v>864923.07000000007</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N495)</f>
@@ -12343,7 +12355,7 @@
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O495)</f>
-        <v>798723.07000000007</v>
+        <v>864923.07000000007</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
@@ -12351,11 +12363,11 @@
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q495)</f>
-        <v>79872.307000000001</v>
+        <v>86492.307000000001</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R495)</f>
-        <v>718850.76300000004</v>
+        <v>778430.76300000004</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S495)</f>
@@ -12363,7 +12375,7 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T495)</f>
-        <v>718850.76300000004</v>
+        <v>778430.76300000004</v>
       </c>
       <c r="V2" s="12"/>
     </row>
@@ -13277,42 +13289,60 @@
       <c r="V16" s="39"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="20"/>
+      <c r="B17" s="24">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="25">
+        <v>47</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="26">
+        <v>70</v>
+      </c>
+      <c r="H17" s="20">
+        <v>70</v>
+      </c>
       <c r="I17" s="19"/>
       <c r="J17" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K17" s="27"/>
+      <c r="K17" s="27">
+        <v>380</v>
+      </c>
       <c r="L17" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.352941176470587</v>
       </c>
       <c r="M17" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26600</v>
       </c>
       <c r="N17" s="27">
         <v>0</v>
       </c>
       <c r="O17" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="22"/>
+        <v>26600</v>
+      </c>
+      <c r="P17" s="22">
+        <v>0.1</v>
+      </c>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2660</v>
       </c>
       <c r="R17" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23940</v>
       </c>
       <c r="S17" s="40">
         <f t="shared" si="3"/>
@@ -13320,46 +13350,64 @@
       </c>
       <c r="T17" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23940</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="B18" s="24">
+        <v>46155</v>
+      </c>
+      <c r="C18" s="25">
+        <v>48</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="28">
+        <v>80</v>
+      </c>
+      <c r="H18" s="29">
+        <v>80</v>
+      </c>
       <c r="I18" s="19"/>
       <c r="J18" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="27">
+        <v>400</v>
+      </c>
       <c r="L18" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.529411764705884</v>
       </c>
       <c r="M18" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="N18" s="27">
         <v>0</v>
       </c>
       <c r="O18" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="30"/>
+        <v>32000</v>
+      </c>
+      <c r="P18" s="30">
+        <v>0.1</v>
+      </c>
       <c r="Q18" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R18" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="S18" s="40">
         <f t="shared" si="3"/>
@@ -13367,46 +13415,64 @@
       </c>
       <c r="T18" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
+      <c r="B19" s="24">
+        <v>46155</v>
+      </c>
+      <c r="C19" s="25">
+        <v>49</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="28">
+        <v>20</v>
+      </c>
+      <c r="H19" s="29">
+        <v>20</v>
+      </c>
       <c r="I19" s="19"/>
       <c r="J19" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K19" s="27"/>
+      <c r="K19" s="27">
+        <v>380</v>
+      </c>
       <c r="L19" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.352941176470587</v>
       </c>
       <c r="M19" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="N19" s="27">
         <v>0</v>
       </c>
       <c r="O19" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="30"/>
+        <v>7600</v>
+      </c>
+      <c r="P19" s="30">
+        <v>0.1</v>
+      </c>
       <c r="Q19" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="R19" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6840</v>
       </c>
       <c r="S19" s="40">
         <f t="shared" si="3"/>
@@ -13414,7 +13480,7 @@
       </c>
       <c r="T19" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
@@ -17519,7 +17585,7 @@
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>10.101323005360298</v>
+        <v>10.55028957586768</v>
       </c>
       <c r="J1" s="140" t="s">
         <v>36</v>
@@ -17535,7 +17601,7 @@
       </c>
       <c r="G2" s="51">
         <f>I2/F2</f>
-        <v>171.72249109112508</v>
+        <v>179.35492278975056</v>
       </c>
       <c r="H2" s="52">
         <f>SUM(H4:H391)</f>
@@ -17543,7 +17609,7 @@
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I391)</f>
-        <v>1011960.64</v>
+        <v>1056938.56</v>
       </c>
       <c r="J2" s="54">
         <f>O39</f>
@@ -17551,7 +17617,7 @@
       </c>
       <c r="K2" s="55">
         <f>O45</f>
-        <v>280128.64000000001</v>
+        <v>325106.56000000006</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -18547,14 +18613,14 @@
       </c>
       <c r="G26" s="83">
         <f>Tomatillo!K26</f>
-        <v>68</v>
+        <v>104.04</v>
       </c>
       <c r="H26" s="93">
         <v>0</v>
       </c>
       <c r="I26" s="84">
         <f t="shared" si="3"/>
-        <v>84864</v>
+        <v>129841.92000000001</v>
       </c>
       <c r="J26" s="94" t="s">
         <v>54</v>
@@ -18911,7 +18977,7 @@
       </c>
       <c r="O43" s="67">
         <f>Tomatillo!T2</f>
-        <v>919250.97600000002</v>
+        <v>964228.89600000007</v>
       </c>
     </row>
     <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18940,7 +19006,7 @@
       </c>
       <c r="O45" s="67">
         <f>+O43+O41-O39</f>
-        <v>280128.64000000001</v>
+        <v>325106.56000000006</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
@@ -19661,7 +19727,7 @@
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>29.6166444527178</v>
+        <v>28.964809075630253</v>
       </c>
       <c r="J1" s="140" t="s">
         <v>36</v>
@@ -19673,11 +19739,11 @@
       </c>
       <c r="F2" s="145">
         <f>SUM(F4:F390)</f>
-        <v>1580</v>
+        <v>1750</v>
       </c>
       <c r="G2" s="146">
         <f>I2/F2</f>
-        <v>503.48295569620257</v>
+        <v>492.40175428571433</v>
       </c>
       <c r="H2" s="147">
         <f>SUM(H4:H390)</f>
@@ -19685,15 +19751,15 @@
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I390)</f>
-        <v>795503.07000000007</v>
+        <v>861703.07000000007</v>
       </c>
       <c r="J2" s="148">
         <f>O38</f>
-        <v>643645</v>
+        <v>702245</v>
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>155078.07000000007</v>
+        <v>162678.07000000007</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>37</v>
@@ -19989,7 +20055,7 @@
       </c>
       <c r="K9" s="73"/>
       <c r="N9" s="71">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="O9" s="72">
         <v>145550</v>
@@ -20030,8 +20096,12 @@
         <v>45</v>
       </c>
       <c r="K10" s="73"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="72"/>
+      <c r="N10" s="71">
+        <v>46155</v>
+      </c>
+      <c r="O10" s="72">
+        <v>58600</v>
+      </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="173">
@@ -20103,7 +20173,7 @@
         <f t="shared" si="0"/>
         <v>34400</v>
       </c>
-      <c r="J12" s="180" t="s">
+      <c r="J12" s="138" t="s">
         <v>45</v>
       </c>
       <c r="K12" s="73"/>
@@ -20141,7 +20211,7 @@
         <f>F13*G13-H13</f>
         <v>15149.939999999999</v>
       </c>
-      <c r="J13" s="180" t="s">
+      <c r="J13" s="138" t="s">
         <v>45</v>
       </c>
       <c r="K13" s="73"/>
@@ -20179,7 +20249,7 @@
         <f t="shared" ref="I14" si="2">F14*G14-H14</f>
         <v>96000</v>
       </c>
-      <c r="J14" s="180" t="s">
+      <c r="J14" s="138" t="s">
         <v>45</v>
       </c>
       <c r="K14" s="73"/>
@@ -20200,8 +20270,9 @@
       <c r="D15" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="85" t="s">
-        <v>25</v>
+      <c r="E15" s="85" t="str">
+        <f>Roma!E16</f>
+        <v>Bodega Lizarraga</v>
       </c>
       <c r="F15" s="25">
         <f>Roma!H16</f>
@@ -20228,41 +20299,113 @@
       <c r="O15" s="72"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="91"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="94"/>
+      <c r="B16" s="173">
+        <f>Roma!B17</f>
+        <v>46155</v>
+      </c>
+      <c r="C16" s="113">
+        <f>Roma!C17</f>
+        <v>47</v>
+      </c>
+      <c r="D16" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="113" t="str">
+        <f>Roma!E17</f>
+        <v>Mayojoa</v>
+      </c>
+      <c r="F16" s="174">
+        <f>Roma!H17</f>
+        <v>70</v>
+      </c>
+      <c r="G16" s="115">
+        <f>Roma!K17</f>
+        <v>380</v>
+      </c>
+      <c r="H16" s="111">
+        <v>0</v>
+      </c>
+      <c r="I16" s="115">
+        <f t="shared" ref="I16:I17" si="4">F16*G16-H16</f>
+        <v>26600</v>
+      </c>
+      <c r="J16" s="138" t="s">
+        <v>45</v>
+      </c>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="91"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="94"/>
+      <c r="B17" s="173">
+        <f>Roma!B18</f>
+        <v>46155</v>
+      </c>
+      <c r="C17" s="113">
+        <f>Roma!C18</f>
+        <v>48</v>
+      </c>
+      <c r="D17" s="113" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="113" t="str">
+        <f>Roma!E18</f>
+        <v>Epifanio Lopez</v>
+      </c>
+      <c r="F17" s="174">
+        <f>Roma!H18</f>
+        <v>80</v>
+      </c>
+      <c r="G17" s="115">
+        <f>Roma!K18</f>
+        <v>400</v>
+      </c>
+      <c r="H17" s="111">
+        <v>0</v>
+      </c>
+      <c r="I17" s="115">
+        <f t="shared" si="4"/>
+        <v>32000</v>
+      </c>
+      <c r="J17" s="138" t="s">
+        <v>45</v>
+      </c>
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="91"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="92"/>
+      <c r="B18" s="91">
+        <f>Roma!B19</f>
+        <v>46155</v>
+      </c>
+      <c r="C18" s="85">
+        <f>Roma!C19</f>
+        <v>49</v>
+      </c>
+      <c r="D18" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="85" t="str">
+        <f>Roma!E19</f>
+        <v>Mayojoa</v>
+      </c>
+      <c r="F18" s="25">
+        <f>Roma!H19</f>
+        <v>20</v>
+      </c>
+      <c r="G18" s="75">
+        <f>Roma!K19</f>
+        <v>380</v>
+      </c>
+      <c r="H18" s="84">
+        <v>0</v>
+      </c>
+      <c r="I18" s="75">
+        <f t="shared" ref="I18" si="5">F18*G18-H18</f>
+        <v>7600</v>
+      </c>
+      <c r="J18" s="94" t="s">
+        <v>54</v>
+      </c>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
@@ -20528,7 +20671,7 @@
       </c>
       <c r="O38" s="67">
         <f>SUM(O4:O37)</f>
-        <v>643645</v>
+        <v>702245</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20557,7 +20700,7 @@
       </c>
       <c r="O40" s="67">
         <f>Roma!Q2</f>
-        <v>79872.307000000001</v>
+        <v>86492.307000000001</v>
       </c>
     </row>
     <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20586,7 +20729,7 @@
       </c>
       <c r="O42" s="67">
         <f>+Roma!R2</f>
-        <v>718850.76300000004</v>
+        <v>778430.76300000004</v>
       </c>
     </row>
     <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20615,7 +20758,7 @@
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>155078.07000000007</v>
+        <v>162678.07000000007</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
@@ -22850,7 +22993,7 @@
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
-        <v>1011960.64</v>
+        <v>1056938.56</v>
       </c>
       <c r="F5" s="167">
         <f>+'Estado de Cuenta T'!O39</f>
@@ -22858,7 +23001,7 @@
       </c>
       <c r="G5" s="171">
         <f>+E5-F5</f>
-        <v>280128.64000000001</v>
+        <v>325106.56000000006</v>
       </c>
       <c r="H5" s="167"/>
       <c r="I5" s="167">
@@ -22870,7 +23013,7 @@
       </c>
       <c r="K5" s="167">
         <f>+G5-I5+J5</f>
-        <v>247567.976</v>
+        <v>292545.89600000007</v>
       </c>
     </row>
     <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22879,27 +23022,27 @@
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
-        <v>798723.07000000007</v>
+        <v>864923.07000000007</v>
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
-        <v>643645</v>
+        <v>702245</v>
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>155078.07000000007</v>
+        <v>162678.07000000007</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
         <f>+Roma!Q2</f>
-        <v>79872.307000000001</v>
+        <v>86492.307000000001</v>
       </c>
       <c r="J6" s="167">
         <v>11968</v>
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>87173.763000000064</v>
+        <v>88153.763000000064</v>
       </c>
     </row>
     <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22943,20 +23086,20 @@
     <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
-        <v>1819063.71</v>
+        <v>1930241.6300000001</v>
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
-        <v>1381457</v>
+        <v>1440057</v>
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>437606.71000000008</v>
+        <v>490184.63000000012</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
         <f>SUM(I5:I8)</f>
-        <v>173419.97100000002</v>
+        <v>180039.97100000002</v>
       </c>
       <c r="J9" s="168">
         <f>SUM(J5:J8)</f>
@@ -22964,7 +23107,7 @@
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>336303.73900000006</v>
+        <v>382261.6590000001</v>
       </c>
     </row>
     <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -22984,7 +23127,7 @@
       <c r="H11" s="167"/>
       <c r="I11" s="167">
         <f>+I9-J9</f>
-        <v>101302.97100000002</v>
+        <v>107922.97100000002</v>
       </c>
       <c r="J11" s="167"/>
       <c r="K11" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f087611319785eae/Documentos/GitHub/H2E-Crown/Info para Claude/Reportes/Nacional/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1610" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50BE2939-4C9C-4BC2-8F23-52F802B58402}"/>
+  <xr:revisionPtr revIDLastSave="1612" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98497CDE-96F1-43BA-85E0-239520011780}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -1939,38 +1939,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FC3981-8E5A-4436-B2C6-E1A6D261A1E4}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="1" bestFit="1"/>
-    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1" bestFit="1"/>
+    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.42578125" style="1"/>
+    <col min="21" max="21" width="44.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.44140625" style="1"/>
     <col min="26" max="26" width="16" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.7109375" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="11.42578125" style="1"/>
+    <col min="27" max="27" width="16.6640625" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B4" s="18">
         <v>46128</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B5" s="24">
         <v>46128</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B6" s="24">
         <v>46128</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B7" s="24">
         <v>46128</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B8" s="24">
         <v>46128</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>99878.399999999994</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B9" s="24">
         <v>46129</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B10" s="24">
         <v>46129</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>57283.199999999997</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B11" s="24">
         <v>46129</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>15134.4</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B12" s="24">
         <v>46130</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>31487.4</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B13" s="24">
         <v>46130</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>39015</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B14" s="24">
         <v>46132</v>
       </c>
@@ -2822,7 +2822,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B15" s="24">
         <v>46132</v>
       </c>
@@ -2889,7 +2889,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B16" s="24">
         <v>46133</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>48960</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B17" s="118">
         <v>46133</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B18" s="24">
         <v>46134</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B19" s="24">
         <v>46134</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>76377.600000000006</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B20" s="24">
         <v>46136</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" s="24">
         <v>46046</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>184977</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B22" s="24">
         <v>46137</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B23" s="24">
         <v>46142</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>3855.6</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B24" s="24">
         <v>46142</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>70502.399999999994</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B25" s="24">
         <v>46143</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>15912</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B26" s="118">
         <v>46146</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B27" s="24">
         <v>46147</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>53687.7</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B28" s="24">
         <v>46149</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B29" s="24">
         <v>46149</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>6318.9</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B30" s="24">
         <v>46150</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>14688</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B31" s="24">
         <v>46154</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>8321.9760000000006</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -4078,7 +4078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -4123,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -4168,7 +4168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -4303,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -4355,7 +4355,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -4538,7 +4538,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -4628,7 +4628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -4898,7 +4898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -5078,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -5168,7 +5168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -5303,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -5395,7 +5395,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -5534,7 +5534,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -5625,7 +5625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -5670,7 +5670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -5895,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -5940,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -5985,7 +5985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -6210,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -6345,7 +6345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -6708,7 +6708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -6934,7 +6934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -7114,7 +7114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -7307,38 +7307,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BDE71B-B4DE-46F0-B853-4D73D3E1167B}">
   <dimension ref="A2:AC104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1"/>
-    <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="1"/>
-    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1"/>
+    <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1"/>
+    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.42578125" style="1"/>
+    <col min="21" max="21" width="44.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.44140625" style="1"/>
     <col min="26" max="26" width="16" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.7109375" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="11.42578125" style="1"/>
+    <col min="27" max="27" width="16.6640625" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B4" s="18">
         <v>46139</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B5" s="24">
         <v>46151</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>5382</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B6" s="24"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -7639,7 +7639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B7" s="24"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
@@ -7686,7 +7686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B8" s="24"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B9" s="24"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B10" s="24"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B11" s="24"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B12" s="24"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B13" s="24"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -8017,7 +8017,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B15" s="24"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -8066,7 +8066,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -8160,7 +8160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -8207,7 +8207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="24"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -8254,7 +8254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -8348,7 +8348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -8395,7 +8395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -8630,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -8677,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -8724,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -8771,7 +8771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -8818,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -8912,7 +8912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -8959,7 +8959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -9053,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -9100,7 +9100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -9147,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -9201,7 +9201,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -9248,7 +9248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="Z41" s="35"/>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -9343,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -9392,7 +9392,7 @@
       <c r="V43" s="34"/>
       <c r="W43" s="35"/>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -9439,7 +9439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -9486,7 +9486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -9533,7 +9533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -9580,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -9627,7 +9627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -9674,7 +9674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -9721,7 +9721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -9768,7 +9768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -9815,7 +9815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -9909,7 +9909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -9956,7 +9956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -10003,7 +10003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -10097,7 +10097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -10144,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -10191,7 +10191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -10238,7 +10238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -10287,7 +10287,7 @@
       <c r="U62" s="37"/>
       <c r="V62" s="105"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="U63" s="37"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -10432,7 +10432,7 @@
       <c r="U65" s="37"/>
       <c r="V65" s="106"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="U66" s="37"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -10621,7 +10621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -10668,7 +10668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -10715,7 +10715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -10809,7 +10809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -10856,7 +10856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -10903,7 +10903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -10950,7 +10950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -10997,7 +10997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -11044,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -11091,7 +11091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -11185,7 +11185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -11232,7 +11232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="36">
         <v>46057</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
@@ -11376,7 +11376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -11423,7 +11423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -11517,7 +11517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -11564,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -11658,7 +11658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -11705,7 +11705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -11800,7 +11800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -11847,7 +11847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -11894,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -11941,7 +11941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -12035,7 +12035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -12082,7 +12082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -12129,7 +12129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -12176,7 +12176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -12223,7 +12223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -12283,38 +12283,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631DB7E5-46D0-410B-A49E-BCCBB7DAB626}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1"/>
-    <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="1"/>
-    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1"/>
+    <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1"/>
+    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.42578125" style="1"/>
+    <col min="21" max="21" width="44.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.44140625" style="1"/>
     <col min="26" max="26" width="16" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.7109375" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="11.42578125" style="1"/>
+    <col min="27" max="27" width="16.6640625" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B4" s="18">
         <v>46135</v>
       </c>
@@ -12503,7 +12503,7 @@
         <v>18360</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B5" s="24">
         <v>46140</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>48802.256999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B6" s="24">
         <v>46142</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>58914.108</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B7" s="24">
         <v>46144</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>99854.937000000005</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B8" s="24">
         <v>46147</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>121355.59499999999</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B9" s="24">
         <v>46149</v>
       </c>
@@ -12829,7 +12829,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B10" s="24">
         <v>46150</v>
       </c>
@@ -12894,7 +12894,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B11" s="24">
         <v>46150</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>97200</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B12" s="24">
         <v>46151</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>2898</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B13" s="24">
         <v>46153</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>30960</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B14" s="24">
         <v>46153</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>13634.945999999998</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B15" s="24">
         <v>46153</v>
       </c>
@@ -13221,7 +13221,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="38"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B16" s="24">
         <v>46153</v>
       </c>
@@ -13288,7 +13288,7 @@
       <c r="U16" s="37"/>
       <c r="V16" s="39"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="24">
         <v>46155</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>23940</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="24">
         <v>46155</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>28800</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="24">
         <v>46155</v>
       </c>
@@ -13483,7 +13483,7 @@
         <v>6840</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -13530,7 +13530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -13577,7 +13577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -13624,7 +13624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -13671,7 +13671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -13718,7 +13718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -13765,7 +13765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -13812,7 +13812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -13859,7 +13859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -13953,7 +13953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -14000,7 +14000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -14047,7 +14047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -14094,7 +14094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -14141,7 +14141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -14188,7 +14188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -14235,7 +14235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -14282,7 +14282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -14329,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -14376,7 +14376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -14423,7 +14423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -14477,7 +14477,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -14524,7 +14524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -14619,7 +14619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -14668,7 +14668,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -14715,7 +14715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -14762,7 +14762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -14856,7 +14856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -14903,7 +14903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -14950,7 +14950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -14997,7 +14997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -15044,7 +15044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -15091,7 +15091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -15185,7 +15185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -15232,7 +15232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -15279,7 +15279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -15326,7 +15326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -15373,7 +15373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -15420,7 +15420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -15467,7 +15467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -15563,7 +15563,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -15708,7 +15708,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -15756,7 +15756,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -15803,7 +15803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -15850,7 +15850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -15897,7 +15897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -15944,7 +15944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -15991,7 +15991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -16038,7 +16038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -16085,7 +16085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -16132,7 +16132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -16179,7 +16179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -16226,7 +16226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -16273,7 +16273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -16320,7 +16320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -16367,7 +16367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -16414,7 +16414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -16461,7 +16461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -16508,7 +16508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -16652,7 +16652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -16699,7 +16699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -16746,7 +16746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -16840,7 +16840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -16887,7 +16887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -16934,7 +16934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -16981,7 +16981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -17076,7 +17076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -17123,7 +17123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -17170,7 +17170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -17217,7 +17217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -17264,7 +17264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -17311,7 +17311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -17358,7 +17358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -17405,7 +17405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -17452,7 +17452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -17499,7 +17499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -17559,27 +17559,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14DF8A7-7A30-473E-8FAB-92CB0FE83A84}">
   <dimension ref="B1:P106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="47"/>
-    <col min="4" max="4" width="14.140625" style="47" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="48"/>
-    <col min="8" max="8" width="15.5703125" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="47" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="47"/>
+    <col min="4" max="4" width="14.109375" style="47" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="48"/>
+    <col min="8" max="8" width="15.5546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.5703125" style="47" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.5546875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="47" customWidth="1"/>
     <col min="15" max="15" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="47" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="47"/>
+    <col min="16" max="16" width="13.6640625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="11.44140625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>35</v>
       </c>
@@ -17591,7 +17591,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="49" t="s">
         <v>17</v>
       </c>
@@ -17626,7 +17626,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
@@ -17667,7 +17667,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="107">
         <f>Tomatillo!B4</f>
         <v>46128</v>
@@ -17716,7 +17716,7 @@
         <v>36720</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="107">
         <f>Tomatillo!B5</f>
         <v>46128</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="107">
         <f>Tomatillo!B6</f>
         <v>46128</v>
@@ -17801,7 +17801,7 @@
         <v>40086</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="107">
         <f>Tomatillo!B7</f>
         <v>46128</v>
@@ -17847,7 +17847,7 @@
         <v>123114</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="107">
         <f>Tomatillo!B8</f>
         <v>46128</v>
@@ -17890,7 +17890,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="107">
         <f>Tomatillo!B9</f>
         <v>46129</v>
@@ -17935,7 +17935,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="107">
         <f>Tomatillo!B10</f>
         <v>46129</v>
@@ -17980,7 +17980,7 @@
         <v>5530</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="116">
         <f>Tomatillo!B11</f>
         <v>46129</v>
@@ -18030,7 +18030,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="107">
         <f>Tomatillo!B12</f>
         <v>46130</v>
@@ -18076,7 +18076,7 @@
         <v>110976</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="107">
         <f>Tomatillo!B13</f>
         <v>46130</v>
@@ -18122,7 +18122,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="107">
         <f>Tomatillo!B14</f>
         <v>46132</v>
@@ -18170,7 +18170,7 @@
         <v>97750</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="107">
         <f>Tomatillo!B15</f>
         <v>46132</v>
@@ -18219,7 +18219,7 @@
         <v>25567</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="107">
         <f>Tomatillo!B16</f>
         <v>46133</v>
@@ -18257,7 +18257,7 @@
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="128">
         <f>Tomatillo!B17</f>
         <v>46133</v>
@@ -18293,7 +18293,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="136">
         <f>Tomatillo!B18</f>
         <v>46134</v>
@@ -18331,7 +18331,7 @@
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="107">
         <f>Tomatillo!B19</f>
         <v>46134</v>
@@ -18369,7 +18369,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="107">
         <f>Tomatillo!B20</f>
         <v>46136</v>
@@ -18406,7 +18406,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="107">
         <f>Tomatillo!B21</f>
         <v>46046</v>
@@ -18443,7 +18443,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="136">
         <f>Tomatillo!B22</f>
         <v>46137</v>
@@ -18480,7 +18480,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="136">
         <f>Tomatillo!B23</f>
         <v>46142</v>
@@ -18517,7 +18517,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="136">
         <f>Tomatillo!B24</f>
         <v>46142</v>
@@ -18554,7 +18554,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="136">
         <f>Tomatillo!B25</f>
         <v>46143</v>
@@ -18591,7 +18591,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="136">
         <f>Tomatillo!B26</f>
         <v>46146</v>
@@ -18628,7 +18628,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="136">
         <f>Tomatillo!B27</f>
         <v>46147</v>
@@ -18665,7 +18665,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="107">
         <f>Tomatillo!B28</f>
         <v>46149</v>
@@ -18702,7 +18702,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="107">
         <f>Tomatillo!B29</f>
         <v>46149</v>
@@ -18739,7 +18739,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="107">
         <f>Tomatillo!B30</f>
         <v>46150</v>
@@ -18776,7 +18776,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="107">
         <f>Tomatillo!B31</f>
         <v>46154</v>
@@ -18813,7 +18813,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="136"/>
       <c r="C32" s="81"/>
       <c r="D32" s="86"/>
@@ -18826,7 +18826,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -18839,7 +18839,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -18852,7 +18852,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -18865,7 +18865,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -18878,7 +18878,7 @@
       <c r="N36" s="71"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -18891,7 +18891,7 @@
       <c r="N37" s="76"/>
       <c r="O37" s="72"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -18904,7 +18904,7 @@
       <c r="N38" s="77"/>
       <c r="O38" s="78"/>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -18922,7 +18922,7 @@
         <v>731832</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="89"/>
       <c r="C40" s="86"/>
       <c r="D40" s="86"/>
@@ -18933,7 +18933,7 @@
       <c r="I40" s="88"/>
       <c r="J40" s="90"/>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -18951,7 +18951,7 @@
         <v>92709.664000000019</v>
       </c>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -18962,7 +18962,7 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -18980,7 +18980,7 @@
         <v>964228.89600000007</v>
       </c>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="89"/>
       <c r="C44" s="86"/>
       <c r="D44" s="86"/>
@@ -18991,7 +18991,7 @@
       <c r="I44" s="75"/>
       <c r="J44" s="90"/>
     </row>
-    <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -19009,7 +19009,7 @@
         <v>325106.56000000006</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -19020,7 +19020,7 @@
       <c r="I46" s="75"/>
       <c r="J46" s="92"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" s="89"/>
       <c r="C47" s="86"/>
       <c r="D47" s="86"/>
@@ -19032,7 +19032,7 @@
       <c r="J47" s="90"/>
       <c r="O47" s="79"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -19043,7 +19043,7 @@
       <c r="I48" s="75"/>
       <c r="J48" s="92"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -19055,7 +19055,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -19067,7 +19067,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="96"/>
       <c r="C51" s="87"/>
       <c r="D51" s="86"/>
@@ -19079,7 +19079,7 @@
       <c r="J51" s="90"/>
       <c r="O51" s="80"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="96"/>
       <c r="C52" s="87"/>
       <c r="D52" s="86"/>
@@ -19092,7 +19092,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -19105,7 +19105,7 @@
       <c r="O53" s="80"/>
       <c r="P53" s="80"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="96"/>
       <c r="C54" s="87"/>
       <c r="D54" s="86"/>
@@ -19116,7 +19116,7 @@
       <c r="I54" s="88"/>
       <c r="J54" s="90"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -19129,7 +19129,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="96"/>
       <c r="C56" s="87"/>
       <c r="D56" s="86"/>
@@ -19142,7 +19142,7 @@
       <c r="O56" s="80"/>
       <c r="P56" s="80"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -19153,7 +19153,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -19164,7 +19164,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -19175,7 +19175,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="96"/>
       <c r="C60" s="87"/>
       <c r="D60" s="86"/>
@@ -19186,7 +19186,7 @@
       <c r="I60" s="88"/>
       <c r="J60" s="90"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="96"/>
       <c r="C61" s="87"/>
       <c r="D61" s="86"/>
@@ -19197,7 +19197,7 @@
       <c r="I61" s="88"/>
       <c r="J61" s="90"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="96"/>
       <c r="C62" s="87"/>
       <c r="D62" s="86"/>
@@ -19208,7 +19208,7 @@
       <c r="I62" s="88"/>
       <c r="J62" s="90"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -19219,7 +19219,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -19230,7 +19230,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -19241,7 +19241,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="96"/>
       <c r="C66" s="87"/>
       <c r="D66" s="86"/>
@@ -19252,7 +19252,7 @@
       <c r="I66" s="88"/>
       <c r="J66" s="90"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -19263,7 +19263,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -19274,7 +19274,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="96"/>
       <c r="C69" s="87"/>
       <c r="D69" s="86"/>
@@ -19285,7 +19285,7 @@
       <c r="I69" s="88"/>
       <c r="J69" s="90"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="96"/>
       <c r="C70" s="87"/>
       <c r="D70" s="86"/>
@@ -19296,7 +19296,7 @@
       <c r="I70" s="88"/>
       <c r="J70" s="90"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="96"/>
       <c r="C71" s="87"/>
       <c r="D71" s="86"/>
@@ -19307,7 +19307,7 @@
       <c r="I71" s="88"/>
       <c r="J71" s="90"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -19318,7 +19318,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -19329,7 +19329,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="92"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -19340,7 +19340,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="98"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="96"/>
       <c r="C75" s="87"/>
       <c r="D75" s="86"/>
@@ -19351,7 +19351,7 @@
       <c r="I75" s="88"/>
       <c r="J75" s="90"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="96"/>
       <c r="C76" s="87"/>
       <c r="D76" s="86"/>
@@ -19362,7 +19362,7 @@
       <c r="I76" s="88"/>
       <c r="J76" s="99"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -19373,7 +19373,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -19384,7 +19384,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="96"/>
       <c r="C79" s="87"/>
       <c r="D79" s="86"/>
@@ -19395,7 +19395,7 @@
       <c r="I79" s="88"/>
       <c r="J79" s="90"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="96"/>
       <c r="C80" s="87"/>
       <c r="D80" s="86"/>
@@ -19406,7 +19406,7 @@
       <c r="I80" s="88"/>
       <c r="J80" s="90"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -19417,7 +19417,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="96"/>
       <c r="C82" s="87"/>
       <c r="D82" s="86"/>
@@ -19428,7 +19428,7 @@
       <c r="I82" s="88"/>
       <c r="J82" s="90"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="96"/>
       <c r="C83" s="87"/>
       <c r="D83" s="86"/>
@@ -19439,7 +19439,7 @@
       <c r="I83" s="88"/>
       <c r="J83" s="90"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -19450,7 +19450,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="96"/>
       <c r="C85" s="87"/>
       <c r="D85" s="86"/>
@@ -19461,7 +19461,7 @@
       <c r="I85" s="88"/>
       <c r="J85" s="90"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -19472,7 +19472,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="96"/>
       <c r="C87" s="87"/>
       <c r="D87" s="86"/>
@@ -19483,7 +19483,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="90"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -19494,7 +19494,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="96"/>
       <c r="C89" s="87"/>
       <c r="D89" s="86"/>
@@ -19505,7 +19505,7 @@
       <c r="I89" s="88"/>
       <c r="J89" s="90"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -19516,7 +19516,7 @@
       <c r="I90" s="88"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -19527,7 +19527,7 @@
       <c r="I91" s="88"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="96"/>
       <c r="C92" s="87"/>
       <c r="D92" s="86"/>
@@ -19538,7 +19538,7 @@
       <c r="I92" s="93"/>
       <c r="J92" s="103"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -19549,7 +19549,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -19560,7 +19560,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -19571,7 +19571,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -19582,7 +19582,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="24"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -19593,7 +19593,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="92"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -19604,7 +19604,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="94"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -19615,7 +19615,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -19626,7 +19626,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -19637,7 +19637,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -19648,7 +19648,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="92"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -19659,7 +19659,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="94"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -19670,7 +19670,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -19681,7 +19681,7 @@
       <c r="I105" s="75"/>
       <c r="J105" s="92"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="91"/>
       <c r="C106" s="85"/>
       <c r="D106" s="85"/>
@@ -19701,27 +19701,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A884314C-68A6-4266-8FA4-11EA17178DDD}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="47"/>
-    <col min="4" max="4" width="14.140625" style="47" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="48"/>
-    <col min="8" max="8" width="15.5703125" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="47" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="47"/>
+    <col min="4" max="4" width="14.109375" style="47" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="48"/>
+    <col min="8" max="8" width="15.5546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.5703125" style="47" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.5546875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="47" customWidth="1"/>
     <col min="15" max="15" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="47" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="47"/>
+    <col min="16" max="16" width="13.6640625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="11.44140625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>35</v>
       </c>
@@ -19733,7 +19733,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
@@ -19768,7 +19768,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -19809,7 +19809,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="149">
         <v>46135</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v>54225</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="173">
         <f>Roma!B5</f>
         <v>46140</v>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="173">
         <f>Roma!B6</f>
         <v>46142</v>
@@ -19936,7 +19936,7 @@
         <v>110950</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="173">
         <f>Roma!B7</f>
         <v>46144</v>
@@ -19976,7 +19976,7 @@
         <v>134840</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="173">
         <f>Roma!B8</f>
         <v>46147</v>
@@ -20019,7 +20019,7 @@
         <v>132620</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="173">
         <f>Roma!B9</f>
         <v>46149</v>
@@ -20061,7 +20061,7 @@
         <v>145550</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="173">
         <f>Roma!B10</f>
         <v>46150</v>
@@ -20103,7 +20103,7 @@
         <v>58600</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="173">
         <f>Roma!B11</f>
         <v>46150</v>
@@ -20142,7 +20142,7 @@
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="173">
         <f>Roma!B13</f>
         <v>46153</v>
@@ -20180,7 +20180,7 @@
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="173">
         <f>Roma!B14</f>
         <v>46153</v>
@@ -20218,7 +20218,7 @@
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="173">
         <f>Roma!B15</f>
         <v>46153</v>
@@ -20258,7 +20258,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="91">
         <f>Roma!B16</f>
         <v>46153</v>
@@ -20298,7 +20298,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="173">
         <f>Roma!B17</f>
         <v>46155</v>
@@ -20335,7 +20335,7 @@
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="173">
         <f>Roma!B18</f>
         <v>46155</v>
@@ -20372,7 +20372,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="91">
         <f>Roma!B19</f>
         <v>46155</v>
@@ -20409,7 +20409,7 @@
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -20422,7 +20422,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -20435,7 +20435,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -20448,7 +20448,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -20461,7 +20461,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -20474,7 +20474,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -20487,7 +20487,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -20500,7 +20500,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -20513,7 +20513,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -20526,7 +20526,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -20539,7 +20539,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -20552,7 +20552,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -20565,7 +20565,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -20578,7 +20578,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -20591,7 +20591,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -20604,7 +20604,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -20617,7 +20617,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -20630,7 +20630,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -20643,7 +20643,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -20656,7 +20656,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -20674,7 +20674,7 @@
         <v>702245</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -20685,7 +20685,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -20703,7 +20703,7 @@
         <v>86492.307000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -20714,7 +20714,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -20732,7 +20732,7 @@
         <v>778430.76300000004</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -20743,7 +20743,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -20761,7 +20761,7 @@
         <v>162678.07000000007</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -20772,7 +20772,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -20784,7 +20784,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -20795,7 +20795,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -20807,7 +20807,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -20819,7 +20819,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -20831,7 +20831,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -20844,7 +20844,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -20857,7 +20857,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -20868,7 +20868,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -20881,7 +20881,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -20894,7 +20894,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -20905,7 +20905,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -20916,7 +20916,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -20927,7 +20927,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -20938,7 +20938,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -20949,7 +20949,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -20960,7 +20960,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -20971,7 +20971,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -20982,7 +20982,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -20993,7 +20993,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -21004,7 +21004,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -21015,7 +21015,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -21026,7 +21026,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -21037,7 +21037,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -21048,7 +21048,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -21059,7 +21059,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -21070,7 +21070,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -21081,7 +21081,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -21092,7 +21092,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -21103,7 +21103,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -21114,7 +21114,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -21125,7 +21125,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -21136,7 +21136,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -21147,7 +21147,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -21158,7 +21158,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -21169,7 +21169,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -21180,7 +21180,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -21191,7 +21191,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -21202,7 +21202,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -21213,7 +21213,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -21224,7 +21224,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -21235,7 +21235,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -21246,7 +21246,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -21257,7 +21257,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -21268,7 +21268,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -21279,7 +21279,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -21290,7 +21290,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -21301,7 +21301,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -21312,7 +21312,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -21323,7 +21323,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -21334,7 +21334,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -21345,7 +21345,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -21356,7 +21356,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -21367,7 +21367,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -21378,7 +21378,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -21389,7 +21389,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -21400,7 +21400,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -21411,7 +21411,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -21422,7 +21422,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -21433,7 +21433,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -21453,27 +21453,27 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7F0943-67B8-4148-A349-2B4FA39AA366}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="47"/>
-    <col min="4" max="4" width="14.140625" style="47" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="48"/>
-    <col min="8" max="8" width="15.5703125" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="47" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="47"/>
+    <col min="4" max="4" width="14.109375" style="47" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="48"/>
+    <col min="8" max="8" width="15.5546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.5703125" style="47" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.5546875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="47" customWidth="1"/>
     <col min="15" max="15" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="47" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="47"/>
+    <col min="16" max="16" width="13.6640625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="11.44140625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>35</v>
       </c>
@@ -21485,7 +21485,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
@@ -21520,7 +21520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="149">
         <f>Morrón!B4</f>
         <v>46139</v>
@@ -21609,7 +21609,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="176">
         <f>Morrón!B5</f>
         <v>46151</v>
@@ -21647,7 +21647,7 @@
       <c r="O5" s="72"/>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="91"/>
       <c r="C6" s="85"/>
       <c r="D6" s="85"/>
@@ -21665,7 +21665,7 @@
       <c r="N6" s="71"/>
       <c r="O6" s="72"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="91"/>
       <c r="C7" s="85"/>
       <c r="D7" s="85"/>
@@ -21684,7 +21684,7 @@
       <c r="N7" s="71"/>
       <c r="O7" s="72"/>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="91"/>
       <c r="C8" s="85"/>
       <c r="D8" s="85"/>
@@ -21703,7 +21703,7 @@
       <c r="N8" s="71"/>
       <c r="O8" s="72"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="91"/>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -21722,7 +21722,7 @@
       <c r="N9" s="71"/>
       <c r="O9" s="72"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="91"/>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -21741,7 +21741,7 @@
       <c r="N10" s="71"/>
       <c r="O10" s="72"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="91"/>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -21761,7 +21761,7 @@
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="91"/>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -21780,7 +21780,7 @@
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="91"/>
       <c r="C13" s="85"/>
       <c r="D13" s="85"/>
@@ -21799,7 +21799,7 @@
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="91"/>
       <c r="C14" s="85"/>
       <c r="D14" s="85"/>
@@ -21820,7 +21820,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="91"/>
       <c r="C15" s="85"/>
       <c r="D15" s="85"/>
@@ -21841,7 +21841,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="91"/>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
@@ -21859,7 +21859,7 @@
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="91"/>
       <c r="C17" s="85"/>
       <c r="D17" s="85"/>
@@ -21877,7 +21877,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="91"/>
       <c r="C18" s="85"/>
       <c r="D18" s="85"/>
@@ -21895,7 +21895,7 @@
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -21908,7 +21908,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -21921,7 +21921,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -21934,7 +21934,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -21947,7 +21947,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -21960,7 +21960,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -21973,7 +21973,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -21986,7 +21986,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -21999,7 +21999,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -22012,7 +22012,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -22025,7 +22025,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -22038,7 +22038,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -22051,7 +22051,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -22064,7 +22064,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -22077,7 +22077,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -22090,7 +22090,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -22103,7 +22103,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -22116,7 +22116,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -22129,7 +22129,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -22142,7 +22142,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -22160,7 +22160,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -22171,7 +22171,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -22189,7 +22189,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -22200,7 +22200,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -22218,7 +22218,7 @@
         <v>7542</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -22229,7 +22229,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -22247,7 +22247,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -22258,7 +22258,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -22270,7 +22270,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -22281,7 +22281,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -22293,7 +22293,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -22305,7 +22305,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -22317,7 +22317,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -22330,7 +22330,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -22343,7 +22343,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -22354,7 +22354,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -22367,7 +22367,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -22380,7 +22380,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -22391,7 +22391,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -22402,7 +22402,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -22413,7 +22413,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -22424,7 +22424,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -22435,7 +22435,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -22446,7 +22446,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -22457,7 +22457,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -22468,7 +22468,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -22479,7 +22479,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -22490,7 +22490,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -22501,7 +22501,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -22512,7 +22512,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -22523,7 +22523,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -22534,7 +22534,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -22545,7 +22545,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -22556,7 +22556,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -22567,7 +22567,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -22578,7 +22578,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -22589,7 +22589,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -22600,7 +22600,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -22611,7 +22611,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -22622,7 +22622,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -22633,7 +22633,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -22644,7 +22644,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -22655,7 +22655,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -22666,7 +22666,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -22677,7 +22677,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -22688,7 +22688,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -22699,7 +22699,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -22710,7 +22710,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -22721,7 +22721,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -22732,7 +22732,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -22743,7 +22743,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -22754,7 +22754,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -22765,7 +22765,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -22776,7 +22776,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -22787,7 +22787,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -22798,7 +22798,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -22809,7 +22809,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -22820,7 +22820,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -22831,7 +22831,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -22842,7 +22842,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -22853,7 +22853,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -22864,7 +22864,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -22875,7 +22875,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -22886,7 +22886,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -22897,7 +22897,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -22908,7 +22908,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -22919,7 +22919,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -22938,24 +22938,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFCC301-F59E-4EF9-AD64-E57A9E70782E}">
   <dimension ref="D2:L12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.85546875" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D2" s="169" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:12" x14ac:dyDescent="0.3">
       <c r="E3" s="47"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -22965,7 +22965,7 @@
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
     </row>
-    <row r="4" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E4" s="170" t="s">
         <v>82</v>
       </c>
@@ -22987,7 +22987,7 @@
       </c>
       <c r="L4" s="47"/>
     </row>
-    <row r="5" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>88</v>
       </c>
@@ -23016,7 +23016,7 @@
         <v>292545.89600000007</v>
       </c>
     </row>
-    <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>89</v>
       </c>
@@ -23045,7 +23045,7 @@
         <v>88153.763000000064</v>
       </c>
     </row>
-    <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>90</v>
       </c>
@@ -23074,7 +23074,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="8" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
       <c r="G8" s="171"/>
@@ -23083,7 +23083,7 @@
       <c r="J8" s="167"/>
       <c r="K8" s="167"/>
     </row>
-    <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
         <v>1930241.6300000001</v>
@@ -23110,7 +23110,7 @@
         <v>382261.6590000001</v>
       </c>
     </row>
-    <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E10" s="167"/>
       <c r="F10" s="167"/>
       <c r="G10" s="167"/>
@@ -23120,7 +23120,7 @@
       <c r="K10" s="166"/>
       <c r="L10" s="167"/>
     </row>
-    <row r="11" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E11" s="167"/>
       <c r="F11" s="167"/>
       <c r="G11" s="167"/>
@@ -23133,7 +23133,7 @@
       <c r="K11" s="166"/>
       <c r="L11" s="167"/>
     </row>
-    <row r="12" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:12" x14ac:dyDescent="0.3">
       <c r="E12" s="167"/>
       <c r="F12" s="167"/>
       <c r="G12" s="167"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f087611319785eae/Documentos/GitHub/H2E-Crown/Info para Claude/Reportes/Nacional/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1612" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98497CDE-96F1-43BA-85E0-239520011780}"/>
+  <xr:revisionPtr revIDLastSave="1613" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3780B962-99F6-4BD4-9568-3A7244BC1469}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="107">
   <si>
     <t>TOTAL</t>
   </si>
@@ -144,10 +146,19 @@
     <t>Samuel Cuadras</t>
   </si>
   <si>
+    <t>$45 mil pesos de flete pagados por H2E</t>
+  </si>
+  <si>
+    <t>Prueba</t>
+  </si>
+  <si>
     <t>Morrón V</t>
   </si>
   <si>
     <t>Tomate</t>
+  </si>
+  <si>
+    <t>Epifanio Lopez</t>
   </si>
   <si>
     <t>VENTAS</t>
@@ -261,6 +272,12 @@
     <t>20260507-02</t>
   </si>
   <si>
+    <t>20260508-01</t>
+  </si>
+  <si>
+    <t>20260512-01</t>
+  </si>
+  <si>
     <t>Retorno Com</t>
   </si>
   <si>
@@ -285,7 +302,37 @@
     <t>20260505-01</t>
   </si>
   <si>
+    <t>20260508-02</t>
+  </si>
+  <si>
+    <t>20260508-03</t>
+  </si>
+  <si>
+    <t>20260511-01</t>
+  </si>
+  <si>
+    <t>20260511-02</t>
+  </si>
+  <si>
+    <t>20260511-03</t>
+  </si>
+  <si>
+    <t>20260511-04</t>
+  </si>
+  <si>
+    <t>20260513-01</t>
+  </si>
+  <si>
+    <t>20260513-02</t>
+  </si>
+  <si>
+    <t>20260513-03</t>
+  </si>
+  <si>
     <t>20260427-01</t>
+  </si>
+  <si>
+    <t>20260509-01</t>
   </si>
   <si>
     <t>Balance 2da Etapa</t>
@@ -320,63 +367,21 @@
   <si>
     <t>comision cxp</t>
   </si>
-  <si>
-    <t>20260509-01</t>
-  </si>
-  <si>
-    <t>20260508-03</t>
-  </si>
-  <si>
-    <t>20260508-02</t>
-  </si>
-  <si>
-    <t>20260511-01</t>
-  </si>
-  <si>
-    <t>20260511-02</t>
-  </si>
-  <si>
-    <t>20260511-03</t>
-  </si>
-  <si>
-    <t>Epifanio Lopez</t>
-  </si>
-  <si>
-    <t>20260508-01</t>
-  </si>
-  <si>
-    <t>20260511-04</t>
-  </si>
-  <si>
-    <t>20260512-01</t>
-  </si>
-  <si>
-    <t>$45 mil pesos de flete pagados por H2E</t>
-  </si>
-  <si>
-    <t>20260513-01</t>
-  </si>
-  <si>
-    <t>20260513-02</t>
-  </si>
-  <si>
-    <t>20260513-03</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="169" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,7 +466,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,6 +524,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1014,11 +1025,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1029,31 +1040,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1062,10 +1073,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1077,16 +1088,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1095,22 +1106,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1119,16 +1130,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1137,22 +1148,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1161,7 +1172,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,22 +1181,22 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1200,16 +1211,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1218,31 +1229,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1251,13 +1262,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1266,10 +1277,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1281,7 +1292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1296,7 +1307,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1317,13 +1328,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1347,10 +1358,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1362,7 +1373,7 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1377,28 +1388,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1413,13 +1424,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1434,16 +1445,16 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="9" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1455,13 +1466,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1479,13 +1490,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1494,7 +1505,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1509,17 +1520,17 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1528,10 +1539,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1555,12 +1566,15 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Millares" xfId="1" builtinId="3"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -1939,38 +1953,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FC3981-8E5A-4436-B2C6-E1A6D261A1E4}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1" bestFit="1"/>
-    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1" bestFit="1"/>
+    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.44140625" style="1"/>
+    <col min="21" max="21" width="44.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.42578125" style="1"/>
     <col min="26" max="26" width="16" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.6640625" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="11.44140625" style="1"/>
+    <col min="27" max="27" width="16.7109375" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -2035,7 +2049,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2094,7 +2108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:22">
       <c r="B4" s="18">
         <v>46128</v>
       </c>
@@ -2159,7 +2173,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22">
       <c r="B5" s="24">
         <v>46128</v>
       </c>
@@ -2224,7 +2238,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:22">
       <c r="B6" s="24">
         <v>46128</v>
       </c>
@@ -2289,7 +2303,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:22">
       <c r="B7" s="24">
         <v>46128</v>
       </c>
@@ -2355,7 +2369,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:22">
       <c r="B8" s="24">
         <v>46128</v>
       </c>
@@ -2422,7 +2436,7 @@
         <v>99878.399999999994</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:22">
       <c r="B9" s="24">
         <v>46129</v>
       </c>
@@ -2488,7 +2502,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:22">
       <c r="B10" s="24">
         <v>46129</v>
       </c>
@@ -2555,7 +2569,7 @@
         <v>57283.199999999997</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:22">
       <c r="B11" s="24">
         <v>46129</v>
       </c>
@@ -2621,7 +2635,7 @@
         <v>15134.4</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:22">
       <c r="B12" s="24">
         <v>46130</v>
       </c>
@@ -2688,7 +2702,7 @@
         <v>31487.4</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22">
       <c r="B13" s="24">
         <v>46130</v>
       </c>
@@ -2754,7 +2768,7 @@
         <v>39015</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:22">
       <c r="B14" s="24">
         <v>46132</v>
       </c>
@@ -2822,7 +2836,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:22">
       <c r="B15" s="24">
         <v>46132</v>
       </c>
@@ -2889,7 +2903,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:22">
       <c r="B16" s="24">
         <v>46133</v>
       </c>
@@ -2955,7 +2969,7 @@
         <v>48960</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:21">
       <c r="B17" s="118">
         <v>46133</v>
       </c>
@@ -3019,7 +3033,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:21">
       <c r="B18" s="24">
         <v>46134</v>
       </c>
@@ -3084,7 +3098,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:21">
       <c r="B19" s="24">
         <v>46134</v>
       </c>
@@ -3149,7 +3163,7 @@
         <v>76377.600000000006</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:21">
       <c r="B20" s="24">
         <v>46136</v>
       </c>
@@ -3215,7 +3229,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:21">
       <c r="B21" s="24">
         <v>46046</v>
       </c>
@@ -3281,7 +3295,7 @@
         <v>184977</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:21">
       <c r="B22" s="24">
         <v>46137</v>
       </c>
@@ -3347,7 +3361,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:21">
       <c r="B23" s="24">
         <v>46142</v>
       </c>
@@ -3413,7 +3427,7 @@
         <v>3855.6</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:21">
       <c r="B24" s="24">
         <v>46142</v>
       </c>
@@ -3479,7 +3493,7 @@
         <v>70502.399999999994</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:21">
       <c r="B25" s="24">
         <v>46143</v>
       </c>
@@ -3545,7 +3559,7 @@
         <v>15912</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:21">
       <c r="B26" s="118">
         <v>46146</v>
       </c>
@@ -3611,10 +3625,10 @@
         <v>129841.92000000001</v>
       </c>
       <c r="U26" s="127" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21">
       <c r="B27" s="24">
         <v>46147</v>
       </c>
@@ -3680,7 +3694,7 @@
         <v>53687.7</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:21">
       <c r="B28" s="24">
         <v>46149</v>
       </c>
@@ -3746,7 +3760,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:21">
       <c r="B29" s="24">
         <v>46149</v>
       </c>
@@ -3812,7 +3826,7 @@
         <v>6318.9</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:21">
       <c r="B30" s="24">
         <v>46150</v>
       </c>
@@ -3877,7 +3891,7 @@
         <v>14688</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:21">
       <c r="B31" s="24">
         <v>46154</v>
       </c>
@@ -3943,8 +3957,10 @@
         <v>8321.9760000000006</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B32" s="24"/>
+    <row r="32" spans="2:21">
+      <c r="B32" s="180" t="s">
+        <v>34</v>
+      </c>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
@@ -3988,7 +4004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:29">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -4033,7 +4049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:29">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -4078,7 +4094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:29">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -4123,7 +4139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:29">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -4168,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:29">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -4213,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:29">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -4258,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:29">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -4303,7 +4319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:29">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -4355,7 +4371,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:29">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -4400,7 +4416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:29">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -4446,7 +4462,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:29">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -4491,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:29">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -4538,7 +4554,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:29">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -4583,7 +4599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:29">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -4628,7 +4644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:29">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -4673,7 +4689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:29">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -4718,7 +4734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:22">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -4763,7 +4779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:22">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -4808,7 +4824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:22">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -4853,7 +4869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:22">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -4898,7 +4914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:22">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -4943,7 +4959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:22">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -4988,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:22">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -5033,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:22">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -5078,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:22">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -5123,7 +5139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:22">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -5168,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:22">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -5213,7 +5229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:22">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -5258,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:22">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -5303,7 +5319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:22">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -5348,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:22">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -5395,7 +5411,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:22">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -5441,7 +5457,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:22">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -5487,7 +5503,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:22">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -5534,7 +5550,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:22">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -5580,7 +5596,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:22">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -5625,7 +5641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:22">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -5670,7 +5686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:22">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -5715,7 +5731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:22">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -5760,7 +5776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:22">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -5805,7 +5821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:22">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -5850,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:22">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -5895,7 +5911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:22">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -5940,7 +5956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:22">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -5985,7 +6001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:22">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -6030,7 +6046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:22">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -6075,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:22">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -6120,7 +6136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:22">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -6165,7 +6181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -6210,7 +6226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -6255,7 +6271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -6300,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -6345,7 +6361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -6393,7 +6409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -6438,7 +6454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -6483,7 +6499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -6528,7 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -6573,7 +6589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -6618,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -6663,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -6708,7 +6724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -6753,7 +6769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" s="2" customFormat="1">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -6799,7 +6815,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -6844,7 +6860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -6889,7 +6905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:20">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -6934,7 +6950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:20">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -6979,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:20">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -7024,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:20">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -7069,7 +7085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:20">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -7114,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:20">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -7159,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:20">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -7204,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:20">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -7249,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:20">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -7307,38 +7323,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BDE71B-B4DE-46F0-B853-4D73D3E1167B}">
   <dimension ref="A2:AC104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="1"/>
-    <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1"/>
-    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1"/>
+    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.44140625" style="1"/>
+    <col min="21" max="21" width="44.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.42578125" style="1"/>
     <col min="26" max="26" width="16" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.6640625" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="11.44140625" style="1"/>
+    <col min="27" max="27" width="16.7109375" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -7403,7 +7419,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -7462,7 +7478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:22">
       <c r="B4" s="18">
         <v>46139</v>
       </c>
@@ -7476,7 +7492,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4" s="20">
         <v>10</v>
@@ -7527,7 +7543,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22">
       <c r="B5" s="24">
         <v>46151</v>
       </c>
@@ -7541,7 +7557,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" s="26">
         <v>23</v>
@@ -7592,7 +7608,7 @@
         <v>5382</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:22">
       <c r="B6" s="24"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -7639,7 +7655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:22">
       <c r="B7" s="24"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
@@ -7686,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:22">
       <c r="B8" s="24"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -7733,7 +7749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:22">
       <c r="B9" s="24"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -7780,7 +7796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:22">
       <c r="B10" s="24"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
@@ -7827,7 +7843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:22">
       <c r="B11" s="24"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -7874,7 +7890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:22">
       <c r="B12" s="24"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -7921,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22">
       <c r="B13" s="24"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -7968,7 +7984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:22">
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -8017,7 +8033,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:22">
       <c r="B15" s="24"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -8066,7 +8082,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:22">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -8113,7 +8129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -8160,7 +8176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -8207,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20">
       <c r="B19" s="24"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -8254,7 +8270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -8301,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -8348,7 +8364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -8395,7 +8411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -8442,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -8489,7 +8505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -8536,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -8583,7 +8599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -8630,7 +8646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -8677,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -8724,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -8771,7 +8787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -8818,7 +8834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -8865,7 +8881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:29">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -8912,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:29">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -8959,7 +8975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:29">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -9006,7 +9022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:29">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -9053,7 +9069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:29">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -9100,7 +9116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:29">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -9147,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:29">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -9201,7 +9217,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:29">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -9248,7 +9264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:29">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -9296,7 +9312,7 @@
       </c>
       <c r="Z41" s="35"/>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:29">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -9343,7 +9359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:29">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -9392,7 +9408,7 @@
       <c r="V43" s="34"/>
       <c r="W43" s="35"/>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:29">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -9439,7 +9455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:29">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -9486,7 +9502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:29">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -9533,7 +9549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:29">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -9580,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:29">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -9627,7 +9643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:22">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -9674,7 +9690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:22">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -9721,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:22">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -9768,7 +9784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:22">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -9815,7 +9831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:22">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -9862,7 +9878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:22">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -9909,7 +9925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:22">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -9956,7 +9972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:22">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -10003,7 +10019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:22">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -10050,7 +10066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:22">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -10097,7 +10113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:22">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -10144,7 +10160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:22">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -10191,7 +10207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:22">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -10238,7 +10254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:22">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -10287,7 +10303,7 @@
       <c r="U62" s="37"/>
       <c r="V62" s="105"/>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:22">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -10335,7 +10351,7 @@
       </c>
       <c r="U63" s="37"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:22">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -10383,7 +10399,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:22">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -10432,7 +10448,7 @@
       <c r="U65" s="37"/>
       <c r="V65" s="106"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:22">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -10480,7 +10496,7 @@
       </c>
       <c r="U66" s="37"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:22">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -10527,7 +10543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:22">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -10574,7 +10590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:22">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -10621,7 +10637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:22">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -10668,7 +10684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:22">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -10715,7 +10731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:22">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -10762,7 +10778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:22">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -10809,7 +10825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:22">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -10856,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:22">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -10903,7 +10919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:22">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -10950,7 +10966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:22">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -10997,7 +11013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:22">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -11044,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:22">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -11091,7 +11107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:22">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -11138,7 +11154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -11185,7 +11201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -11232,7 +11248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -11279,7 +11295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21">
       <c r="A84" s="36">
         <v>46057</v>
       </c>
@@ -11329,7 +11345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
@@ -11376,7 +11392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -11423,7 +11439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -11470,7 +11486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -11517,7 +11533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -11564,7 +11580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -11611,7 +11627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -11658,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -11705,7 +11721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" s="2" customFormat="1">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -11753,7 +11769,7 @@
       </c>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -11800,7 +11816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -11847,7 +11863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -11894,7 +11910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:20">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -11941,7 +11957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:20">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -11988,7 +12004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:20">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -12035,7 +12051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:20">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -12082,7 +12098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:20">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -12129,7 +12145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:20">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -12176,7 +12192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:20">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -12223,7 +12239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:20">
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -12283,38 +12299,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631DB7E5-46D0-410B-A49E-BCCBB7DAB626}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="1"/>
-    <col min="4" max="4" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1"/>
-    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1"/>
+    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.44140625" style="1"/>
+    <col min="21" max="21" width="44.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.42578125" style="1"/>
     <col min="26" max="26" width="16" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.6640625" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="11.44140625" style="1"/>
+    <col min="27" max="27" width="16.7109375" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -12379,7 +12395,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -12438,7 +12454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:22">
       <c r="B4" s="18">
         <v>46135</v>
       </c>
@@ -12452,7 +12468,7 @@
         <v>29</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="20">
         <v>34</v>
@@ -12503,7 +12519,7 @@
         <v>18360</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22">
       <c r="B5" s="24">
         <v>46140</v>
       </c>
@@ -12517,7 +12533,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" s="26">
         <v>83</v>
@@ -12568,7 +12584,7 @@
         <v>48802.256999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:22">
       <c r="B6" s="24">
         <v>46142</v>
       </c>
@@ -12582,7 +12598,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" s="26">
         <v>101</v>
@@ -12633,7 +12649,7 @@
         <v>58914.108</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:22">
       <c r="B7" s="24">
         <v>46144</v>
       </c>
@@ -12647,7 +12663,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" s="26">
         <v>171</v>
@@ -12698,7 +12714,7 @@
         <v>99854.937000000005</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:22">
       <c r="B8" s="24">
         <v>46147</v>
       </c>
@@ -12712,7 +12728,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" s="26">
         <v>211</v>
@@ -12764,7 +12780,7 @@
         <v>121355.59499999999</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:22">
       <c r="B9" s="24">
         <v>46149</v>
       </c>
@@ -12778,7 +12794,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9" s="26">
         <v>1</v>
@@ -12829,7 +12845,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:22">
       <c r="B10" s="24">
         <v>46150</v>
       </c>
@@ -12843,7 +12859,7 @@
         <v>23</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" s="26">
         <v>50</v>
@@ -12894,7 +12910,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:22">
       <c r="B11" s="24">
         <v>46150</v>
       </c>
@@ -12908,7 +12924,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" s="26">
         <v>240</v>
@@ -12959,7 +12975,7 @@
         <v>97200</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:22">
       <c r="B12" s="24">
         <v>46151</v>
       </c>
@@ -12973,7 +12989,7 @@
         <v>32</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G12" s="26">
         <v>7</v>
@@ -13024,7 +13040,7 @@
         <v>2898</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22">
       <c r="B13" s="24">
         <v>46153</v>
       </c>
@@ -13035,10 +13051,10 @@
         <v>20</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" s="26">
         <v>80</v>
@@ -13089,7 +13105,7 @@
         <v>30960</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:22">
       <c r="B14" s="24">
         <v>46153</v>
       </c>
@@ -13103,7 +13119,7 @@
         <v>23</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" s="26">
         <v>39</v>
@@ -13154,7 +13170,7 @@
         <v>13634.945999999998</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:22">
       <c r="B15" s="24">
         <v>46153</v>
       </c>
@@ -13168,7 +13184,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" s="26">
         <v>240</v>
@@ -13221,7 +13237,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="38"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:22">
       <c r="B16" s="24">
         <v>46153</v>
       </c>
@@ -13235,7 +13251,7 @@
         <v>25</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" s="26">
         <v>330</v>
@@ -13288,7 +13304,7 @@
       <c r="U16" s="37"/>
       <c r="V16" s="39"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20">
       <c r="B17" s="24">
         <v>46155</v>
       </c>
@@ -13302,7 +13318,7 @@
         <v>23</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" s="26">
         <v>70</v>
@@ -13353,7 +13369,7 @@
         <v>23940</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20">
       <c r="B18" s="24">
         <v>46155</v>
       </c>
@@ -13364,10 +13380,10 @@
         <v>20</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" s="28">
         <v>80</v>
@@ -13418,7 +13434,7 @@
         <v>28800</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20">
       <c r="B19" s="24">
         <v>46155</v>
       </c>
@@ -13432,7 +13448,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" s="28">
         <v>20</v>
@@ -13483,7 +13499,7 @@
         <v>6840</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -13530,7 +13546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -13577,7 +13593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -13624,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -13671,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -13718,7 +13734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -13765,7 +13781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -13812,7 +13828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -13859,7 +13875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -13906,7 +13922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -13953,7 +13969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -14000,7 +14016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -14047,7 +14063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -14094,7 +14110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:29">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -14141,7 +14157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:29">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -14188,7 +14204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:29">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -14235,7 +14251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:29">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -14282,7 +14298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:29">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -14329,7 +14345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:29">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -14376,7 +14392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:29">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -14423,7 +14439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:29">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -14477,7 +14493,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:29">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -14524,7 +14540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:29">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -14572,7 +14588,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:29">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -14619,7 +14635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:29">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -14668,7 +14684,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:29">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -14715,7 +14731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:29">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -14762,7 +14778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:29">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -14809,7 +14825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:29">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -14856,7 +14872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:22">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -14903,7 +14919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:22">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -14950,7 +14966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:22">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -14997,7 +15013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:22">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -15044,7 +15060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:22">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -15091,7 +15107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:22">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -15138,7 +15154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:22">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -15185,7 +15201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:22">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -15232,7 +15248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:22">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -15279,7 +15295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:22">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -15326,7 +15342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:22">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -15373,7 +15389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:22">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -15420,7 +15436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:22">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -15467,7 +15483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:22">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -15514,7 +15530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:22">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -15563,7 +15579,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:22">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -15611,7 +15627,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:22">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -15659,7 +15675,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:22">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -15708,7 +15724,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:22">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -15756,7 +15772,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:22">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -15803,7 +15819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:22">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -15850,7 +15866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:22">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -15897,7 +15913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:22">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -15944,7 +15960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:22">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -15991,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:22">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -16038,7 +16054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:22">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -16085,7 +16101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:22">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -16132,7 +16148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:22">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -16179,7 +16195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:22">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -16226,7 +16242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:22">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -16273,7 +16289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:22">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -16320,7 +16336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:22">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -16367,7 +16383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -16414,7 +16430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -16461,7 +16477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -16508,7 +16524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -16555,7 +16571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -16605,7 +16621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -16652,7 +16668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -16699,7 +16715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -16746,7 +16762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -16793,7 +16809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -16840,7 +16856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -16887,7 +16903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -16934,7 +16950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -16981,7 +16997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" s="2" customFormat="1">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -17029,7 +17045,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -17076,7 +17092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -17123,7 +17139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:20">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -17170,7 +17186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:20">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -17217,7 +17233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:20">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -17264,7 +17280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:20">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -17311,7 +17327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:20">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -17358,7 +17374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:20">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -17405,7 +17421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:20">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -17452,7 +17468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:20">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -17499,7 +17515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:20">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -17559,39 +17575,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14DF8A7-7A30-473E-8FAB-92CB0FE83A84}">
   <dimension ref="B1:P106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="47" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="47"/>
-    <col min="4" max="4" width="14.109375" style="47" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="48"/>
-    <col min="8" max="8" width="15.5546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="47"/>
+    <col min="4" max="4" width="14.140625" style="47" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="48"/>
+    <col min="8" max="8" width="15.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.5546875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.5703125" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="47" customWidth="1"/>
     <col min="15" max="15" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" style="47" customWidth="1"/>
-    <col min="17" max="17" width="8.33203125" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="11.44140625" style="47"/>
+    <col min="16" max="16" width="13.7109375" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1">
       <c r="B1" s="46" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>10.55028957586768</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1">
       <c r="C2" s="49" t="s">
         <v>17</v>
       </c>
@@ -17620,13 +17636,13 @@
         <v>325106.56000000006</v>
       </c>
       <c r="L2" s="56" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1">
       <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
@@ -17634,13 +17650,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3" s="59" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>10</v>
@@ -17649,25 +17665,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="63" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3" s="64" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K3" s="65">
         <v>0</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1">
       <c r="B4" s="107">
         <f>Tomatillo!B4</f>
         <v>46128</v>
@@ -17677,7 +17693,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" s="108" t="str">
         <f>Tomatillo!E4</f>
@@ -17700,14 +17716,14 @@
         <v>15300</v>
       </c>
       <c r="J4" s="112" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K4" s="68">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N4" s="69">
         <v>46128</v>
@@ -17716,7 +17732,7 @@
         <v>36720</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" ht="15.75" thickBot="1">
       <c r="B5" s="107">
         <f>Tomatillo!B5</f>
         <v>46128</v>
@@ -17726,7 +17742,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" s="108" t="str">
         <f>Tomatillo!E5</f>
@@ -17749,7 +17765,7 @@
         <v>3060</v>
       </c>
       <c r="J5" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N5" s="71">
         <v>46129</v>
@@ -17759,7 +17775,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" ht="15.75" thickBot="1">
       <c r="B6" s="107">
         <f>Tomatillo!B6</f>
         <v>46128</v>
@@ -17769,7 +17785,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" s="108" t="str">
         <f>Tomatillo!E6</f>
@@ -17792,7 +17808,7 @@
         <v>6120</v>
       </c>
       <c r="J6" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N6" s="71">
         <v>46133</v>
@@ -17801,7 +17817,7 @@
         <v>40086</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" ht="15.75" thickBot="1">
       <c r="B7" s="107">
         <f>Tomatillo!B7</f>
         <v>46128</v>
@@ -17811,7 +17827,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E7" s="108" t="str">
         <f>Tomatillo!E7</f>
@@ -17834,7 +17850,7 @@
         <v>12240</v>
       </c>
       <c r="J7" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K7" s="73">
         <f>95764/(434*17)</f>
@@ -17847,7 +17863,7 @@
         <v>123114</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" ht="15.75" thickBot="1">
       <c r="B8" s="107">
         <f>Tomatillo!B8</f>
         <v>46128</v>
@@ -17857,7 +17873,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E8" s="108" t="str">
         <f>Tomatillo!E8</f>
@@ -17880,7 +17896,7 @@
         <v>110976</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K8" s="73"/>
       <c r="N8" s="71">
@@ -17890,7 +17906,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="15.75" thickBot="1">
       <c r="B9" s="107">
         <f>Tomatillo!B9</f>
         <v>46129</v>
@@ -17900,7 +17916,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E9" s="108" t="str">
         <f>Tomatillo!E9</f>
@@ -17922,7 +17938,7 @@
         <v>15300</v>
       </c>
       <c r="J9" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9:K15" si="1">G9/17</f>
@@ -17935,7 +17951,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1">
       <c r="B10" s="107">
         <f>Tomatillo!B10</f>
         <v>46129</v>
@@ -17945,7 +17961,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E10" s="108" t="str">
         <f>Tomatillo!E10</f>
@@ -17967,7 +17983,7 @@
         <v>63648</v>
       </c>
       <c r="J10" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K10" s="73">
         <f t="shared" si="1"/>
@@ -17980,7 +17996,7 @@
         <v>5530</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1">
       <c r="B11" s="116">
         <f>Tomatillo!B11</f>
         <v>46129</v>
@@ -17990,7 +18006,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="85" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E11" s="81" t="str">
         <f>Tomatillo!E11</f>
@@ -18013,7 +18029,7 @@
         <v>16816</v>
       </c>
       <c r="J11" s="104" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K11" s="73">
         <f t="shared" si="1"/>
@@ -18030,7 +18046,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1">
       <c r="B12" s="107">
         <f>Tomatillo!B12</f>
         <v>46130</v>
@@ -18040,7 +18056,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E12" s="108" t="str">
         <f>Tomatillo!E12</f>
@@ -18063,7 +18079,7 @@
         <v>34986</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K12" s="73">
         <f t="shared" si="1"/>
@@ -18076,7 +18092,7 @@
         <v>110976</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1">
       <c r="B13" s="107">
         <f>Tomatillo!B13</f>
         <v>46130</v>
@@ -18086,7 +18102,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="113" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" s="108" t="str">
         <f>Tomatillo!E13</f>
@@ -18109,7 +18125,7 @@
         <v>43350</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K13" s="73">
         <f t="shared" si="1"/>
@@ -18122,7 +18138,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1">
       <c r="B14" s="107">
         <f>Tomatillo!B14</f>
         <v>46132</v>
@@ -18132,7 +18148,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E14" s="108" t="str">
         <f>Tomatillo!E14</f>
@@ -18155,7 +18171,7 @@
         <v>5100</v>
       </c>
       <c r="J14" s="117" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K14" s="73">
         <f t="shared" si="1"/>
@@ -18170,7 +18186,7 @@
         <v>97750</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1">
       <c r="B15" s="107">
         <f>Tomatillo!B15</f>
         <v>46132</v>
@@ -18180,7 +18196,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="113" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="108" t="str">
         <f>Tomatillo!E15</f>
@@ -18203,7 +18219,7 @@
         <v>38250</v>
       </c>
       <c r="J15" s="117" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K15" s="73">
         <f t="shared" si="1"/>
@@ -18219,7 +18235,7 @@
         <v>25567</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1">
       <c r="B16" s="107">
         <f>Tomatillo!B16</f>
         <v>46133</v>
@@ -18229,7 +18245,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="113" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="108" t="str">
         <f>Tomatillo!E16</f>
@@ -18252,12 +18268,12 @@
         <v>54400</v>
       </c>
       <c r="J16" s="117" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" ht="15.75" thickBot="1">
       <c r="B17" s="128">
         <f>Tomatillo!B17</f>
         <v>46133</v>
@@ -18267,7 +18283,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="130" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E17" s="129" t="str">
         <f>Tomatillo!E17</f>
@@ -18293,7 +18309,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" ht="15.75" thickBot="1">
       <c r="B18" s="136">
         <f>Tomatillo!B18</f>
         <v>46134</v>
@@ -18303,7 +18319,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="85" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E18" s="81" t="str">
         <f>Tomatillo!E18</f>
@@ -18326,12 +18342,12 @@
         <v>12240</v>
       </c>
       <c r="J18" s="137" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" ht="15.75" thickBot="1">
       <c r="B19" s="107">
         <f>Tomatillo!B19</f>
         <v>46134</v>
@@ -18341,7 +18357,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E19" s="108" t="str">
         <f>Tomatillo!E19</f>
@@ -18364,12 +18380,12 @@
         <v>84864</v>
       </c>
       <c r="J19" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" ht="15.75" thickBot="1">
       <c r="B20" s="107">
         <f>Tomatillo!B20</f>
         <v>46136</v>
@@ -18379,7 +18395,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="163" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E20" s="108" t="str">
         <f>Tomatillo!E20</f>
@@ -18401,12 +18417,12 @@
         <v>6120</v>
       </c>
       <c r="J20" s="165" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" ht="15.75" thickBot="1">
       <c r="B21" s="107">
         <f>Tomatillo!B21</f>
         <v>46046</v>
@@ -18416,7 +18432,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="158" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E21" s="108" t="str">
         <f>Tomatillo!E21</f>
@@ -18438,12 +18454,12 @@
         <v>205530</v>
       </c>
       <c r="J21" s="160" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" ht="15.75" thickBot="1">
       <c r="B22" s="136">
         <f>Tomatillo!B22</f>
         <v>46137</v>
@@ -18453,7 +18469,7 @@
         <v>23</v>
       </c>
       <c r="D22" s="161" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E22" s="81" t="str">
         <f>Tomatillo!E22</f>
@@ -18475,12 +18491,12 @@
         <v>6120</v>
       </c>
       <c r="J22" s="162" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" ht="15.75" thickBot="1">
       <c r="B23" s="136">
         <f>Tomatillo!B23</f>
         <v>46142</v>
@@ -18490,7 +18506,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="161" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E23" s="81" t="str">
         <f>Tomatillo!E23</f>
@@ -18512,12 +18528,12 @@
         <v>4284</v>
       </c>
       <c r="J23" s="162" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" ht="15.75" thickBot="1">
       <c r="B24" s="136">
         <f>Tomatillo!B24</f>
         <v>46142</v>
@@ -18527,7 +18543,7 @@
         <v>28</v>
       </c>
       <c r="D24" s="161" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E24" s="81" t="str">
         <f>Tomatillo!E24</f>
@@ -18549,12 +18565,12 @@
         <v>78336</v>
       </c>
       <c r="J24" s="162" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" ht="15.75" thickBot="1">
       <c r="B25" s="136">
         <f>Tomatillo!B25</f>
         <v>46143</v>
@@ -18564,7 +18580,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="161" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E25" s="81" t="str">
         <f>Tomatillo!E25</f>
@@ -18586,12 +18602,12 @@
         <v>17680</v>
       </c>
       <c r="J25" s="162" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" ht="15.75" thickBot="1">
       <c r="B26" s="136">
         <f>Tomatillo!B26</f>
         <v>46146</v>
@@ -18601,7 +18617,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="85" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E26" s="81" t="str">
         <f>Tomatillo!E26</f>
@@ -18623,12 +18639,12 @@
         <v>129841.92000000001</v>
       </c>
       <c r="J26" s="94" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" ht="15.75" thickBot="1">
       <c r="B27" s="136">
         <f>Tomatillo!B27</f>
         <v>46147</v>
@@ -18638,7 +18654,7 @@
         <v>34</v>
       </c>
       <c r="D27" s="86" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E27" s="81" t="str">
         <f>Tomatillo!E27</f>
@@ -18660,12 +18676,12 @@
         <v>59653</v>
       </c>
       <c r="J27" s="137" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" ht="15.75" thickBot="1">
       <c r="B28" s="107">
         <f>Tomatillo!B28</f>
         <v>46149</v>
@@ -18675,7 +18691,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="113" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E28" s="108" t="str">
         <f>Tomatillo!E28</f>
@@ -18697,12 +18713,12 @@
         <v>136</v>
       </c>
       <c r="J28" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" ht="15.75" thickBot="1">
       <c r="B29" s="107">
         <f>Tomatillo!B29</f>
         <v>46149</v>
@@ -18712,7 +18728,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="113" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E29" s="108" t="str">
         <f>Tomatillo!E29</f>
@@ -18734,12 +18750,12 @@
         <v>7021</v>
       </c>
       <c r="J29" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" ht="15.75" thickBot="1">
       <c r="B30" s="107">
         <f>Tomatillo!B30</f>
         <v>46150</v>
@@ -18749,7 +18765,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="163" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="E30" s="108" t="str">
         <f>Tomatillo!E30</f>
@@ -18771,12 +18787,12 @@
         <v>16320</v>
       </c>
       <c r="J30" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" ht="15.75" thickBot="1">
       <c r="B31" s="107">
         <f>Tomatillo!B31</f>
         <v>46154</v>
@@ -18786,7 +18802,7 @@
         <v>46</v>
       </c>
       <c r="D31" s="113" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E31" s="108" t="str">
         <f>Tomatillo!E31</f>
@@ -18808,12 +18824,12 @@
         <v>9246.6400000000012</v>
       </c>
       <c r="J31" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15">
       <c r="B32" s="136"/>
       <c r="C32" s="81"/>
       <c r="D32" s="86"/>
@@ -18826,7 +18842,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -18839,7 +18855,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -18852,7 +18868,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -18865,7 +18881,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -18878,7 +18894,7 @@
       <c r="N36" s="71"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -18891,7 +18907,7 @@
       <c r="N37" s="76"/>
       <c r="O37" s="72"/>
     </row>
-    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -18904,7 +18920,7 @@
       <c r="N38" s="77"/>
       <c r="O38" s="78"/>
     </row>
-    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -18922,7 +18938,7 @@
         <v>731832</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1">
       <c r="B40" s="89"/>
       <c r="C40" s="86"/>
       <c r="D40" s="86"/>
@@ -18933,7 +18949,7 @@
       <c r="I40" s="88"/>
       <c r="J40" s="90"/>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -18944,14 +18960,14 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
       <c r="N41" s="66" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O41" s="67">
         <f>Tomatillo!Q2</f>
         <v>92709.664000000019</v>
       </c>
     </row>
-    <row r="42" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -18962,7 +18978,7 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -18973,14 +18989,14 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
       <c r="N43" s="66" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O43" s="67">
         <f>Tomatillo!T2</f>
         <v>964228.89600000007</v>
       </c>
     </row>
-    <row r="44" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1">
       <c r="B44" s="89"/>
       <c r="C44" s="86"/>
       <c r="D44" s="86"/>
@@ -18991,7 +19007,7 @@
       <c r="I44" s="75"/>
       <c r="J44" s="90"/>
     </row>
-    <row r="45" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:15" ht="15.75" thickBot="1">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -19002,14 +19018,14 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
       <c r="N45" s="66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O45" s="67">
         <f>+O43+O41-O39</f>
         <v>325106.56000000006</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -19020,7 +19036,7 @@
       <c r="I46" s="75"/>
       <c r="J46" s="92"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15">
       <c r="B47" s="89"/>
       <c r="C47" s="86"/>
       <c r="D47" s="86"/>
@@ -19032,7 +19048,7 @@
       <c r="J47" s="90"/>
       <c r="O47" s="79"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -19043,7 +19059,7 @@
       <c r="I48" s="75"/>
       <c r="J48" s="92"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -19055,7 +19071,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -19067,7 +19083,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16">
       <c r="B51" s="96"/>
       <c r="C51" s="87"/>
       <c r="D51" s="86"/>
@@ -19079,7 +19095,7 @@
       <c r="J51" s="90"/>
       <c r="O51" s="80"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16">
       <c r="B52" s="96"/>
       <c r="C52" s="87"/>
       <c r="D52" s="86"/>
@@ -19092,7 +19108,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -19105,7 +19121,7 @@
       <c r="O53" s="80"/>
       <c r="P53" s="80"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16">
       <c r="B54" s="96"/>
       <c r="C54" s="87"/>
       <c r="D54" s="86"/>
@@ -19116,7 +19132,7 @@
       <c r="I54" s="88"/>
       <c r="J54" s="90"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -19129,7 +19145,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16">
       <c r="B56" s="96"/>
       <c r="C56" s="87"/>
       <c r="D56" s="86"/>
@@ -19142,7 +19158,7 @@
       <c r="O56" s="80"/>
       <c r="P56" s="80"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -19153,7 +19169,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -19164,7 +19180,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -19175,7 +19191,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16">
       <c r="B60" s="96"/>
       <c r="C60" s="87"/>
       <c r="D60" s="86"/>
@@ -19186,7 +19202,7 @@
       <c r="I60" s="88"/>
       <c r="J60" s="90"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16">
       <c r="B61" s="96"/>
       <c r="C61" s="87"/>
       <c r="D61" s="86"/>
@@ -19197,7 +19213,7 @@
       <c r="I61" s="88"/>
       <c r="J61" s="90"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16">
       <c r="B62" s="96"/>
       <c r="C62" s="87"/>
       <c r="D62" s="86"/>
@@ -19208,7 +19224,7 @@
       <c r="I62" s="88"/>
       <c r="J62" s="90"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -19219,7 +19235,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -19230,7 +19246,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -19241,7 +19257,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10">
       <c r="B66" s="96"/>
       <c r="C66" s="87"/>
       <c r="D66" s="86"/>
@@ -19252,7 +19268,7 @@
       <c r="I66" s="88"/>
       <c r="J66" s="90"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -19263,7 +19279,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -19274,7 +19290,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10">
       <c r="B69" s="96"/>
       <c r="C69" s="87"/>
       <c r="D69" s="86"/>
@@ -19285,7 +19301,7 @@
       <c r="I69" s="88"/>
       <c r="J69" s="90"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10">
       <c r="B70" s="96"/>
       <c r="C70" s="87"/>
       <c r="D70" s="86"/>
@@ -19296,7 +19312,7 @@
       <c r="I70" s="88"/>
       <c r="J70" s="90"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10">
       <c r="B71" s="96"/>
       <c r="C71" s="87"/>
       <c r="D71" s="86"/>
@@ -19307,7 +19323,7 @@
       <c r="I71" s="88"/>
       <c r="J71" s="90"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -19318,7 +19334,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -19329,7 +19345,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="92"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -19340,7 +19356,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="98"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10">
       <c r="B75" s="96"/>
       <c r="C75" s="87"/>
       <c r="D75" s="86"/>
@@ -19351,7 +19367,7 @@
       <c r="I75" s="88"/>
       <c r="J75" s="90"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10">
       <c r="B76" s="96"/>
       <c r="C76" s="87"/>
       <c r="D76" s="86"/>
@@ -19362,7 +19378,7 @@
       <c r="I76" s="88"/>
       <c r="J76" s="99"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -19373,7 +19389,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -19384,7 +19400,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10">
       <c r="B79" s="96"/>
       <c r="C79" s="87"/>
       <c r="D79" s="86"/>
@@ -19395,7 +19411,7 @@
       <c r="I79" s="88"/>
       <c r="J79" s="90"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10">
       <c r="B80" s="96"/>
       <c r="C80" s="87"/>
       <c r="D80" s="86"/>
@@ -19406,7 +19422,7 @@
       <c r="I80" s="88"/>
       <c r="J80" s="90"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -19417,7 +19433,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10">
       <c r="B82" s="96"/>
       <c r="C82" s="87"/>
       <c r="D82" s="86"/>
@@ -19428,7 +19444,7 @@
       <c r="I82" s="88"/>
       <c r="J82" s="90"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10">
       <c r="B83" s="96"/>
       <c r="C83" s="87"/>
       <c r="D83" s="86"/>
@@ -19439,7 +19455,7 @@
       <c r="I83" s="88"/>
       <c r="J83" s="90"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -19450,7 +19466,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10">
       <c r="B85" s="96"/>
       <c r="C85" s="87"/>
       <c r="D85" s="86"/>
@@ -19461,7 +19477,7 @@
       <c r="I85" s="88"/>
       <c r="J85" s="90"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -19472,7 +19488,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10">
       <c r="B87" s="96"/>
       <c r="C87" s="87"/>
       <c r="D87" s="86"/>
@@ -19483,7 +19499,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="90"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -19494,7 +19510,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10">
       <c r="B89" s="96"/>
       <c r="C89" s="87"/>
       <c r="D89" s="86"/>
@@ -19505,7 +19521,7 @@
       <c r="I89" s="88"/>
       <c r="J89" s="90"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -19516,7 +19532,7 @@
       <c r="I90" s="88"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -19527,7 +19543,7 @@
       <c r="I91" s="88"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10">
       <c r="B92" s="96"/>
       <c r="C92" s="87"/>
       <c r="D92" s="86"/>
@@ -19538,7 +19554,7 @@
       <c r="I92" s="93"/>
       <c r="J92" s="103"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -19549,7 +19565,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -19560,7 +19576,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -19571,7 +19587,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -19582,7 +19598,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10">
       <c r="B97" s="24"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -19593,7 +19609,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="92"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -19604,7 +19620,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="94"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -19615,7 +19631,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -19626,7 +19642,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -19637,7 +19653,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:10">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -19648,7 +19664,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="92"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:10">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -19659,7 +19675,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="94"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:10">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -19670,7 +19686,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:10">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -19681,7 +19697,7 @@
       <c r="I105" s="75"/>
       <c r="J105" s="92"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:10">
       <c r="B106" s="91"/>
       <c r="C106" s="85"/>
       <c r="D106" s="85"/>
@@ -19701,39 +19717,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A884314C-68A6-4266-8FA4-11EA17178DDD}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="47" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="47"/>
-    <col min="4" max="4" width="14.109375" style="47" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="48"/>
-    <col min="8" max="8" width="15.5546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="47"/>
+    <col min="4" max="4" width="14.140625" style="47" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="48"/>
+    <col min="8" max="8" width="15.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.5546875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.5703125" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="47" customWidth="1"/>
     <col min="15" max="15" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" style="47" customWidth="1"/>
-    <col min="17" max="17" width="8.33203125" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="11.44140625" style="47"/>
+    <col min="16" max="16" width="13.7109375" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1">
       <c r="B1" s="46" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>28.964809075630253</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
@@ -19762,13 +19778,13 @@
         <v>162678.07000000007</v>
       </c>
       <c r="L2" s="56" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -19776,13 +19792,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3" s="152" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="154" t="s">
         <v>10</v>
@@ -19791,25 +19807,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="156" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3" s="67" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K3" s="143">
         <v>0</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1">
       <c r="B4" s="149">
         <v>46135</v>
       </c>
@@ -19817,7 +19833,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E4" s="150" t="s">
         <v>29</v>
@@ -19836,14 +19852,14 @@
         <v>20400</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K4" s="142">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N4" s="69">
         <v>46140</v>
@@ -19852,7 +19868,7 @@
         <v>54225</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16">
       <c r="B5" s="173">
         <f>Roma!B5</f>
         <v>46140</v>
@@ -19862,7 +19878,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E5" s="113" t="str">
         <f>Roma!E5</f>
@@ -19885,7 +19901,7 @@
         <v>54224.729999999996</v>
       </c>
       <c r="J5" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N5" s="71">
         <v>46142</v>
@@ -19895,7 +19911,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16">
       <c r="B6" s="173">
         <f>Roma!B6</f>
         <v>46142</v>
@@ -19905,7 +19921,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E6" s="113" t="str">
         <f>Roma!E6</f>
@@ -19927,7 +19943,7 @@
         <v>65460.12</v>
       </c>
       <c r="J6" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N6" s="71">
         <v>46146</v>
@@ -19936,7 +19952,7 @@
         <v>110950</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16">
       <c r="B7" s="173">
         <f>Roma!B7</f>
         <v>46144</v>
@@ -19946,7 +19962,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E7" s="113" t="str">
         <f>Roma!E7</f>
@@ -19966,7 +19982,7 @@
         <v>110949.93000000001</v>
       </c>
       <c r="J7" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K7" s="73"/>
       <c r="N7" s="71">
@@ -19976,7 +19992,7 @@
         <v>134840</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16">
       <c r="B8" s="173">
         <f>Roma!B8</f>
         <v>46147</v>
@@ -19986,7 +20002,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E8" s="113" t="str">
         <f>Roma!E8</f>
@@ -20008,7 +20024,7 @@
         <v>134839.54999999999</v>
       </c>
       <c r="J8" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K8" s="73"/>
       <c r="N8" s="71">
@@ -20019,7 +20035,7 @@
         <v>132620</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16">
       <c r="B9" s="173">
         <f>Roma!B9</f>
         <v>46149</v>
@@ -20029,7 +20045,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E9" s="113" t="str">
         <f>Roma!E9</f>
@@ -20051,7 +20067,7 @@
         <v>620</v>
       </c>
       <c r="J9" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K9" s="73"/>
       <c r="N9" s="71">
@@ -20061,7 +20077,7 @@
         <v>145550</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16">
       <c r="B10" s="173">
         <f>Roma!B10</f>
         <v>46150</v>
@@ -20071,7 +20087,7 @@
         <v>38</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E10" s="113" t="str">
         <f>Roma!E10</f>
@@ -20093,7 +20109,7 @@
         <v>24000</v>
       </c>
       <c r="J10" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K10" s="73"/>
       <c r="N10" s="71">
@@ -20103,7 +20119,7 @@
         <v>58600</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16">
       <c r="B11" s="173">
         <f>Roma!B11</f>
         <v>46150</v>
@@ -20113,7 +20129,7 @@
         <v>39</v>
       </c>
       <c r="D11" s="113" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E11" s="113" t="str">
         <f>Roma!E11</f>
@@ -20135,14 +20151,14 @@
         <v>108000</v>
       </c>
       <c r="J11" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="79"/>
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16">
       <c r="B12" s="173">
         <f>Roma!B13</f>
         <v>46153</v>
@@ -20152,7 +20168,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E12" s="113" t="str">
         <f>Roma!E13</f>
@@ -20174,13 +20190,13 @@
         <v>34400</v>
       </c>
       <c r="J12" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K12" s="73"/>
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16">
       <c r="B13" s="173">
         <f>Roma!B14</f>
         <v>46153</v>
@@ -20190,7 +20206,7 @@
         <v>43</v>
       </c>
       <c r="D13" s="113" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E13" s="113" t="str">
         <f>Roma!E14</f>
@@ -20212,13 +20228,13 @@
         <v>15149.939999999999</v>
       </c>
       <c r="J13" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K13" s="73"/>
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16">
       <c r="B14" s="173">
         <f>Roma!B15</f>
         <v>46153</v>
@@ -20228,7 +20244,7 @@
         <v>44</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E14" s="113" t="str">
         <f>Roma!E15</f>
@@ -20250,7 +20266,7 @@
         <v>96000</v>
       </c>
       <c r="J14" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K14" s="73"/>
       <c r="L14" s="74"/>
@@ -20258,7 +20274,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16">
       <c r="B15" s="91">
         <f>Roma!B16</f>
         <v>46153</v>
@@ -20268,7 +20284,7 @@
         <v>45</v>
       </c>
       <c r="D15" s="85" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E15" s="85" t="str">
         <f>Roma!E16</f>
@@ -20290,7 +20306,7 @@
         <v>131458.80000000002</v>
       </c>
       <c r="J15" s="94" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K15" s="73"/>
       <c r="L15" s="74"/>
@@ -20298,7 +20314,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16">
       <c r="B16" s="173">
         <f>Roma!B17</f>
         <v>46155</v>
@@ -20308,7 +20324,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="113" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E16" s="113" t="str">
         <f>Roma!E17</f>
@@ -20330,12 +20346,12 @@
         <v>26600</v>
       </c>
       <c r="J16" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15">
       <c r="B17" s="173">
         <f>Roma!B18</f>
         <v>46155</v>
@@ -20345,7 +20361,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="113" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E17" s="113" t="str">
         <f>Roma!E18</f>
@@ -20367,12 +20383,12 @@
         <v>32000</v>
       </c>
       <c r="J17" s="138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15">
       <c r="B18" s="91">
         <f>Roma!B19</f>
         <v>46155</v>
@@ -20382,7 +20398,7 @@
         <v>49</v>
       </c>
       <c r="D18" s="85" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E18" s="85" t="str">
         <f>Roma!E19</f>
@@ -20404,12 +20420,12 @@
         <v>7600</v>
       </c>
       <c r="J18" s="94" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -20422,7 +20438,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -20435,7 +20451,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -20448,7 +20464,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -20461,7 +20477,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -20474,7 +20490,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -20487,7 +20503,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -20500,7 +20516,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -20513,7 +20529,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -20526,7 +20542,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -20539,7 +20555,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -20552,7 +20568,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -20565,7 +20581,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -20578,7 +20594,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -20591,7 +20607,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -20604,7 +20620,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -20617,7 +20633,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -20630,7 +20646,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -20643,7 +20659,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" ht="15.75" thickBot="1">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -20656,7 +20672,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -20674,7 +20690,7 @@
         <v>702245</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -20685,7 +20701,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -20696,14 +20712,14 @@
       <c r="I40" s="75"/>
       <c r="J40" s="92"/>
       <c r="N40" s="66" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O40" s="67">
         <f>Roma!Q2</f>
         <v>86492.307000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -20714,7 +20730,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -20725,14 +20741,14 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
       <c r="N42" s="66" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O42" s="67">
         <f>+Roma!R2</f>
         <v>778430.76300000004</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -20743,7 +20759,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -20754,14 +20770,14 @@
       <c r="I44" s="75"/>
       <c r="J44" s="92"/>
       <c r="N44" s="66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
         <v>162678.07000000007</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -20772,7 +20788,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -20784,7 +20800,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -20795,7 +20811,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -20807,7 +20823,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -20819,7 +20835,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -20831,7 +20847,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -20844,7 +20860,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -20857,7 +20873,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -20868,7 +20884,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -20881,7 +20897,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -20894,7 +20910,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -20905,7 +20921,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -20916,7 +20932,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -20927,7 +20943,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -20938,7 +20954,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -20949,7 +20965,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -20960,7 +20976,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -20971,7 +20987,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -20982,7 +20998,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -20993,7 +21009,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -21004,7 +21020,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -21015,7 +21031,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -21026,7 +21042,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -21037,7 +21053,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -21048,7 +21064,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -21059,7 +21075,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -21070,7 +21086,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -21081,7 +21097,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -21092,7 +21108,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -21103,7 +21119,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -21114,7 +21130,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -21125,7 +21141,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -21136,7 +21152,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -21147,7 +21163,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -21158,7 +21174,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -21169,7 +21185,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -21180,7 +21196,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -21191,7 +21207,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -21202,7 +21218,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -21213,7 +21229,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -21224,7 +21240,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -21235,7 +21251,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -21246,7 +21262,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -21257,7 +21273,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -21268,7 +21284,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -21279,7 +21295,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -21290,7 +21306,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -21301,7 +21317,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -21312,7 +21328,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -21323,7 +21339,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -21334,7 +21350,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -21345,7 +21361,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -21356,7 +21372,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -21367,7 +21383,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -21378,7 +21394,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -21389,7 +21405,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -21400,7 +21416,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:10">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -21411,7 +21427,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:10">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -21422,7 +21438,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:10">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -21433,7 +21449,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:10">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -21453,39 +21469,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7F0943-67B8-4148-A349-2B4FA39AA366}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="47" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="47"/>
-    <col min="4" max="4" width="14.109375" style="47" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="48"/>
-    <col min="8" max="8" width="15.5546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="47"/>
+    <col min="4" max="4" width="14.140625" style="47" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="48"/>
+    <col min="8" max="8" width="15.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.5546875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.5703125" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="47" customWidth="1"/>
     <col min="15" max="15" width="16" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" style="47" customWidth="1"/>
-    <col min="17" max="17" width="8.33203125" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="11.44140625" style="47"/>
+    <col min="16" max="16" width="13.7109375" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1">
       <c r="B1" s="46" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>14.937611408199643</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
@@ -21514,13 +21530,13 @@
         <v>2400</v>
       </c>
       <c r="L2" s="56" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -21528,13 +21544,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3" s="152" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G3" s="154" t="s">
         <v>10</v>
@@ -21543,25 +21559,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="156" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3" s="67" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K3" s="143">
         <v>0</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1">
       <c r="B4" s="149">
         <f>Morrón!B4</f>
         <v>46139</v>
@@ -21571,7 +21587,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E4" s="150" t="str">
         <f>Morrón!E4</f>
@@ -21593,14 +21609,14 @@
         <v>2400</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K4" s="142">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N4" s="69">
         <v>46154</v>
@@ -21609,7 +21625,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16">
       <c r="B5" s="176">
         <f>Morrón!B5</f>
         <v>46151</v>
@@ -21619,7 +21635,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" s="177" t="str">
         <f>Morrón!E5</f>
@@ -21641,13 +21657,13 @@
         <v>5980</v>
       </c>
       <c r="J5" s="179" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N5" s="71"/>
       <c r="O5" s="72"/>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16">
       <c r="B6" s="91"/>
       <c r="C6" s="85"/>
       <c r="D6" s="85"/>
@@ -21665,7 +21681,7 @@
       <c r="N6" s="71"/>
       <c r="O6" s="72"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16">
       <c r="B7" s="91"/>
       <c r="C7" s="85"/>
       <c r="D7" s="85"/>
@@ -21684,7 +21700,7 @@
       <c r="N7" s="71"/>
       <c r="O7" s="72"/>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16">
       <c r="B8" s="91"/>
       <c r="C8" s="85"/>
       <c r="D8" s="85"/>
@@ -21703,7 +21719,7 @@
       <c r="N8" s="71"/>
       <c r="O8" s="72"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16">
       <c r="B9" s="91"/>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -21722,7 +21738,7 @@
       <c r="N9" s="71"/>
       <c r="O9" s="72"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16">
       <c r="B10" s="91"/>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -21741,7 +21757,7 @@
       <c r="N10" s="71"/>
       <c r="O10" s="72"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16">
       <c r="B11" s="91"/>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -21761,7 +21777,7 @@
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16">
       <c r="B12" s="91"/>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -21780,7 +21796,7 @@
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16">
       <c r="B13" s="91"/>
       <c r="C13" s="85"/>
       <c r="D13" s="85"/>
@@ -21799,7 +21815,7 @@
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16">
       <c r="B14" s="91"/>
       <c r="C14" s="85"/>
       <c r="D14" s="85"/>
@@ -21820,7 +21836,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16">
       <c r="B15" s="91"/>
       <c r="C15" s="85"/>
       <c r="D15" s="85"/>
@@ -21841,7 +21857,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16">
       <c r="B16" s="91"/>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
@@ -21859,7 +21875,7 @@
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15">
       <c r="B17" s="91"/>
       <c r="C17" s="85"/>
       <c r="D17" s="85"/>
@@ -21877,7 +21893,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15">
       <c r="B18" s="91"/>
       <c r="C18" s="85"/>
       <c r="D18" s="85"/>
@@ -21895,7 +21911,7 @@
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -21908,7 +21924,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -21921,7 +21937,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -21934,7 +21950,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -21947,7 +21963,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -21960,7 +21976,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -21973,7 +21989,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -21986,7 +22002,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -21999,7 +22015,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -22012,7 +22028,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -22025,7 +22041,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -22038,7 +22054,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -22051,7 +22067,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -22064,7 +22080,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -22077,7 +22093,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -22090,7 +22106,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -22103,7 +22119,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -22116,7 +22132,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -22129,7 +22145,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" ht="15.75" thickBot="1">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -22142,7 +22158,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -22160,7 +22176,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -22171,7 +22187,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -22182,14 +22198,14 @@
       <c r="I40" s="75"/>
       <c r="J40" s="92"/>
       <c r="N40" s="66" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O40" s="67">
         <f>Morrón!Q2</f>
         <v>838</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -22200,7 +22216,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -22211,14 +22227,14 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
       <c r="N42" s="66" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O42" s="67">
         <f>+Morrón!R2</f>
         <v>7542</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -22229,7 +22245,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -22240,14 +22256,14 @@
       <c r="I44" s="75"/>
       <c r="J44" s="92"/>
       <c r="N44" s="66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -22258,7 +22274,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -22270,7 +22286,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -22281,7 +22297,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -22293,7 +22309,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -22305,7 +22321,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -22317,7 +22333,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -22330,7 +22346,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -22343,7 +22359,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -22354,7 +22370,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -22367,7 +22383,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -22380,7 +22396,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -22391,7 +22407,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -22402,7 +22418,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -22413,7 +22429,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -22424,7 +22440,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -22435,7 +22451,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -22446,7 +22462,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -22457,7 +22473,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -22468,7 +22484,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -22479,7 +22495,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -22490,7 +22506,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -22501,7 +22517,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -22512,7 +22528,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -22523,7 +22539,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -22534,7 +22550,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -22545,7 +22561,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -22556,7 +22572,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -22567,7 +22583,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -22578,7 +22594,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -22589,7 +22605,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -22600,7 +22616,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -22611,7 +22627,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -22622,7 +22638,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -22633,7 +22649,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -22644,7 +22660,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -22655,7 +22671,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -22666,7 +22682,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -22677,7 +22693,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -22688,7 +22704,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -22699,7 +22715,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -22710,7 +22726,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -22721,7 +22737,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -22732,7 +22748,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -22743,7 +22759,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -22754,7 +22770,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -22765,7 +22781,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -22776,7 +22792,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -22787,7 +22803,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -22798,7 +22814,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -22809,7 +22825,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -22820,7 +22836,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -22831,7 +22847,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -22842,7 +22858,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -22853,7 +22869,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -22864,7 +22880,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -22875,7 +22891,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -22886,7 +22902,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:10">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -22897,7 +22913,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:10">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -22908,7 +22924,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:10">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -22919,7 +22935,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:10">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -22938,24 +22954,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFCC301-F59E-4EF9-AD64-E57A9E70782E}">
   <dimension ref="D2:L12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.88671875" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="4:12" ht="30">
       <c r="D2" s="169" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="4:12" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="4:12">
       <c r="E3" s="47"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -22965,31 +22981,31 @@
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
     </row>
-    <row r="4" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:12" ht="23.25" customHeight="1">
       <c r="E4" s="170" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F4" s="170" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G4" s="170" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="H4" s="170"/>
       <c r="I4" s="170" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J4" s="170" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="K4" s="170" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="L4" s="47"/>
     </row>
-    <row r="5" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:12" ht="23.25" customHeight="1">
       <c r="D5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
@@ -23016,9 +23032,9 @@
         <v>292545.89600000007</v>
       </c>
     </row>
-    <row r="6" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:12" ht="23.25" customHeight="1">
       <c r="D6" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
@@ -23045,9 +23061,9 @@
         <v>88153.763000000064</v>
       </c>
     </row>
-    <row r="7" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:12" ht="23.25" customHeight="1">
       <c r="D7" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E7" s="167">
         <f>+Morrón!O2</f>
@@ -23074,7 +23090,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="8" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:12" ht="23.25" customHeight="1">
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
       <c r="G8" s="171"/>
@@ -23083,7 +23099,7 @@
       <c r="J8" s="167"/>
       <c r="K8" s="167"/>
     </row>
-    <row r="9" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:12" ht="23.25" customHeight="1">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
         <v>1930241.6300000001</v>
@@ -23110,7 +23126,7 @@
         <v>382261.6590000001</v>
       </c>
     </row>
-    <row r="10" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:12" ht="23.25" customHeight="1">
       <c r="E10" s="167"/>
       <c r="F10" s="167"/>
       <c r="G10" s="167"/>
@@ -23120,7 +23136,7 @@
       <c r="K10" s="166"/>
       <c r="L10" s="167"/>
     </row>
-    <row r="11" spans="4:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:12" ht="23.25" customHeight="1">
       <c r="E11" s="167"/>
       <c r="F11" s="167"/>
       <c r="G11" s="167"/>
@@ -23133,13 +23149,13 @@
       <c r="K11" s="166"/>
       <c r="L11" s="167"/>
     </row>
-    <row r="12" spans="4:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:12">
       <c r="E12" s="167"/>
       <c r="F12" s="167"/>
       <c r="G12" s="167"/>
       <c r="H12" s="167"/>
       <c r="I12" s="167" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="J12" s="167"/>
       <c r="K12" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1613" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3780B962-99F6-4BD4-9568-3A7244BC1469}"/>
+  <xr:revisionPtr revIDLastSave="1631" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A602EA6F-F732-489A-AE17-8F473139152C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="109">
   <si>
     <t>TOTAL</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>balance p/h2e</t>
+  </si>
+  <si>
+    <t>Venta Neta H2E</t>
+  </si>
+  <si>
+    <t>Pagos a H2E</t>
   </si>
   <si>
     <t>tomatillo</t>
@@ -1029,7 +1035,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1569,6 +1575,8 @@
     <xf numFmtId="14" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -22953,7 +22961,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFCC301-F59E-4EF9-AD64-E57A9E70782E}">
-  <dimension ref="D2:L12"/>
+  <dimension ref="D2:O12"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
@@ -22964,14 +22972,18 @@
     <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="1.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:12" ht="30">
+    <row r="2" spans="4:15" ht="30">
       <c r="D2" s="169" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="4:12">
+    <row r="3" spans="4:15">
       <c r="E3" s="47"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -22981,7 +22993,7 @@
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
     </row>
-    <row r="4" spans="4:12" ht="23.25" customHeight="1">
+    <row r="4" spans="4:15" ht="23.25" customHeight="1">
       <c r="E4" s="170" t="s">
         <v>97</v>
       </c>
@@ -23002,10 +23014,16 @@
         <v>102</v>
       </c>
       <c r="L4" s="47"/>
-    </row>
-    <row r="5" spans="4:12" ht="23.25" customHeight="1">
+      <c r="M4" s="182" t="s">
+        <v>103</v>
+      </c>
+      <c r="N4" s="182" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="4:15" ht="23.25" customHeight="1">
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
@@ -23031,10 +23049,18 @@
         <f>+G5-I5+J5</f>
         <v>292545.89600000007</v>
       </c>
-    </row>
-    <row r="6" spans="4:12" ht="23.25" customHeight="1">
+      <c r="M5" s="166">
+        <f>F5-I5</f>
+        <v>639122.33600000001</v>
+      </c>
+      <c r="N5" s="166">
+        <f>M5-J5</f>
+        <v>578973.33600000001</v>
+      </c>
+    </row>
+    <row r="6" spans="4:15" ht="23.25" customHeight="1">
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
@@ -23060,10 +23086,18 @@
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
         <v>88153.763000000064</v>
       </c>
-    </row>
-    <row r="7" spans="4:12" ht="23.25" customHeight="1">
+      <c r="M6" s="166">
+        <f t="shared" ref="M6:M8" si="1">F6-I6</f>
+        <v>615752.69299999997</v>
+      </c>
+      <c r="N6" s="166">
+        <f t="shared" ref="N6:N8" si="2">M6-J6</f>
+        <v>603784.69299999997</v>
+      </c>
+    </row>
+    <row r="7" spans="4:15" ht="23.25" customHeight="1">
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" s="167">
         <f>+Morrón!O2</f>
@@ -23089,8 +23123,16 @@
         <f t="shared" si="0"/>
         <v>1562</v>
       </c>
-    </row>
-    <row r="8" spans="4:12" ht="23.25" customHeight="1">
+      <c r="M7" s="166">
+        <f t="shared" si="1"/>
+        <v>5142</v>
+      </c>
+      <c r="N7" s="166">
+        <f t="shared" si="2"/>
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="8" spans="4:15" ht="23.25" customHeight="1">
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
       <c r="G8" s="171"/>
@@ -23098,8 +23140,16 @@
       <c r="I8" s="167"/>
       <c r="J8" s="167"/>
       <c r="K8" s="167"/>
-    </row>
-    <row r="9" spans="4:12" ht="23.25" customHeight="1">
+      <c r="M8" s="166">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="4:15" ht="23.25" customHeight="1">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
         <v>1930241.6300000001</v>
@@ -23125,8 +23175,20 @@
         <f>+G9-I9+J9</f>
         <v>382261.6590000001</v>
       </c>
-    </row>
-    <row r="10" spans="4:12" ht="23.25" customHeight="1">
+      <c r="M9" s="181">
+        <f t="shared" ref="M6:N9" si="3">E9-I9</f>
+        <v>1750201.659</v>
+      </c>
+      <c r="N9" s="181">
+        <f t="shared" si="3"/>
+        <v>1367940</v>
+      </c>
+      <c r="O9" s="166">
+        <f>M9-N9</f>
+        <v>382261.65899999999</v>
+      </c>
+    </row>
+    <row r="10" spans="4:15" ht="23.25" customHeight="1">
       <c r="E10" s="167"/>
       <c r="F10" s="167"/>
       <c r="G10" s="167"/>
@@ -23136,7 +23198,7 @@
       <c r="K10" s="166"/>
       <c r="L10" s="167"/>
     </row>
-    <row r="11" spans="4:12" ht="23.25" customHeight="1">
+    <row r="11" spans="4:15" ht="23.25" customHeight="1">
       <c r="E11" s="167"/>
       <c r="F11" s="167"/>
       <c r="G11" s="167"/>
@@ -23149,13 +23211,13 @@
       <c r="K11" s="166"/>
       <c r="L11" s="167"/>
     </row>
-    <row r="12" spans="4:12">
+    <row r="12" spans="4:15">
       <c r="E12" s="167"/>
       <c r="F12" s="167"/>
       <c r="G12" s="167"/>
       <c r="H12" s="167"/>
       <c r="I12" s="167" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J12" s="167"/>
       <c r="K12" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1631" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A602EA6F-F732-489A-AE17-8F473139152C}"/>
+  <xr:revisionPtr revIDLastSave="1682" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDFB221C-B969-4193-9EA9-4A6D5053E81E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="6" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -13521,14 +13521,8 @@
         <v>0</v>
       </c>
       <c r="K20" s="27"/>
-      <c r="L20" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="41">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="L20" s="40"/>
+      <c r="M20" s="41"/>
       <c r="N20" s="27">
         <v>0</v>
       </c>
@@ -22973,7 +22967,7 @@
     <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.7109375" customWidth="1"/>
     <col min="12" max="12" width="1.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -23050,12 +23044,12 @@
         <v>292545.89600000007</v>
       </c>
       <c r="M5" s="166">
-        <f>F5-I5</f>
-        <v>639122.33600000001</v>
+        <f>E5-I5</f>
+        <v>964228.89600000007</v>
       </c>
       <c r="N5" s="166">
-        <f>M5-J5</f>
-        <v>578973.33600000001</v>
+        <f>F5-J5</f>
+        <v>671683</v>
       </c>
     </row>
     <row r="6" spans="4:15" ht="23.25" customHeight="1">
@@ -23087,12 +23081,12 @@
         <v>88153.763000000064</v>
       </c>
       <c r="M6" s="166">
-        <f t="shared" ref="M6:M8" si="1">F6-I6</f>
-        <v>615752.69299999997</v>
+        <f t="shared" ref="M6:M8" si="1">E6-I6</f>
+        <v>778430.76300000004</v>
       </c>
       <c r="N6" s="166">
-        <f t="shared" ref="N6:N8" si="2">M6-J6</f>
-        <v>603784.69299999997</v>
+        <f t="shared" ref="N6:N8" si="2">F6-J6</f>
+        <v>690277</v>
       </c>
     </row>
     <row r="7" spans="4:15" ht="23.25" customHeight="1">
@@ -23125,11 +23119,11 @@
       </c>
       <c r="M7" s="166">
         <f t="shared" si="1"/>
-        <v>5142</v>
+        <v>7542</v>
       </c>
       <c r="N7" s="166">
         <f t="shared" si="2"/>
-        <v>5142</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="8" spans="4:15" ht="23.25" customHeight="1">
@@ -23176,7 +23170,7 @@
         <v>382261.6590000001</v>
       </c>
       <c r="M9" s="181">
-        <f t="shared" ref="M6:N9" si="3">E9-I9</f>
+        <f t="shared" ref="M9:N9" si="3">E9-I9</f>
         <v>1750201.659</v>
       </c>
       <c r="N9" s="181">

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1682" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDFB221C-B969-4193-9EA9-4A6D5053E81E}"/>
+  <xr:revisionPtr revIDLastSave="1743" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE5D679-4362-4019-82EF-9D7CFBB037CA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="6" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="112">
   <si>
     <t>TOTAL</t>
   </si>
@@ -147,9 +145,6 @@
   </si>
   <si>
     <t>$45 mil pesos de flete pagados por H2E</t>
-  </si>
-  <si>
-    <t>Prueba</t>
   </si>
   <si>
     <t>Morrón V</t>
@@ -373,21 +368,33 @@
   <si>
     <t>comision cxp</t>
   </si>
+  <si>
+    <t>Julio Mendoza</t>
+  </si>
+  <si>
+    <t>20260514-01</t>
+  </si>
+  <si>
+    <t>20260515-01</t>
+  </si>
+  <si>
+    <t>20260515-02</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="169" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,7 +479,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,12 +537,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1031,11 +1032,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1046,31 +1047,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1079,10 +1080,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1094,16 +1095,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1112,22 +1113,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1136,16 +1137,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1154,22 +1155,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1178,7 +1179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1187,22 +1188,22 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1217,16 +1218,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1235,31 +1236,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1268,13 +1269,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1283,10 +1284,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1298,7 +1299,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1313,7 +1314,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1334,13 +1335,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1364,10 +1365,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1379,7 +1380,7 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1394,28 +1395,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1430,13 +1431,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1451,16 +1452,16 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="9" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1472,13 +1473,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1496,13 +1497,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1511,7 +1512,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1526,17 +1527,17 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1545,10 +1546,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1572,17 +1573,14 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -1961,7 +1959,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FC3981-8E5A-4436-B2C6-E1A6D261A1E4}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1992,7 +1990,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -2057,7 +2055,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2116,7 +2114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>46128</v>
       </c>
@@ -2181,7 +2179,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="24">
         <v>46128</v>
       </c>
@@ -2246,7 +2244,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>46128</v>
       </c>
@@ -2311,7 +2309,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="24">
         <v>46128</v>
       </c>
@@ -2377,7 +2375,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="24">
         <v>46128</v>
       </c>
@@ -2444,7 +2442,7 @@
         <v>99878.399999999994</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="24">
         <v>46129</v>
       </c>
@@ -2510,7 +2508,7 @@
         <v>13770</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="24">
         <v>46129</v>
       </c>
@@ -2577,7 +2575,7 @@
         <v>57283.199999999997</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="24">
         <v>46129</v>
       </c>
@@ -2643,7 +2641,7 @@
         <v>15134.4</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24">
         <v>46130</v>
       </c>
@@ -2710,7 +2708,7 @@
         <v>31487.4</v>
       </c>
     </row>
-    <row r="13" spans="2:22">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="24">
         <v>46130</v>
       </c>
@@ -2776,7 +2774,7 @@
         <v>39015</v>
       </c>
     </row>
-    <row r="14" spans="2:22">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="24">
         <v>46132</v>
       </c>
@@ -2844,7 +2842,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="24">
         <v>46132</v>
       </c>
@@ -2911,7 +2909,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="24">
         <v>46133</v>
       </c>
@@ -2977,7 +2975,7 @@
         <v>48960</v>
       </c>
     </row>
-    <row r="17" spans="2:21">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="118">
         <v>46133</v>
       </c>
@@ -3041,7 +3039,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:21">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="24">
         <v>46134</v>
       </c>
@@ -3106,7 +3104,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="19" spans="2:21">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="24">
         <v>46134</v>
       </c>
@@ -3171,7 +3169,7 @@
         <v>76377.600000000006</v>
       </c>
     </row>
-    <row r="20" spans="2:21">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="24">
         <v>46136</v>
       </c>
@@ -3237,9 +3235,9 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="21" spans="2:21">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="24">
-        <v>46046</v>
+        <v>46136</v>
       </c>
       <c r="C21" s="25">
         <v>21</v>
@@ -3303,7 +3301,7 @@
         <v>184977</v>
       </c>
     </row>
-    <row r="22" spans="2:21">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="24">
         <v>46137</v>
       </c>
@@ -3369,7 +3367,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="23" spans="2:21">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="24">
         <v>46142</v>
       </c>
@@ -3435,7 +3433,7 @@
         <v>3855.6</v>
       </c>
     </row>
-    <row r="24" spans="2:21">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="24">
         <v>46142</v>
       </c>
@@ -3501,7 +3499,7 @@
         <v>70502.399999999994</v>
       </c>
     </row>
-    <row r="25" spans="2:21">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="24">
         <v>46143</v>
       </c>
@@ -3567,7 +3565,7 @@
         <v>15912</v>
       </c>
     </row>
-    <row r="26" spans="2:21">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="118">
         <v>46146</v>
       </c>
@@ -3636,7 +3634,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:21">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="24">
         <v>46147</v>
       </c>
@@ -3702,7 +3700,7 @@
         <v>53687.7</v>
       </c>
     </row>
-    <row r="28" spans="2:21">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="24">
         <v>46149</v>
       </c>
@@ -3768,7 +3766,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="29" spans="2:21">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="24">
         <v>46149</v>
       </c>
@@ -3834,7 +3832,7 @@
         <v>6318.9</v>
       </c>
     </row>
-    <row r="30" spans="2:21">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="24">
         <v>46150</v>
       </c>
@@ -3899,7 +3897,7 @@
         <v>14688</v>
       </c>
     </row>
-    <row r="31" spans="2:21">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="24">
         <v>46154</v>
       </c>
@@ -3965,10 +3963,8 @@
         <v>8321.9760000000006</v>
       </c>
     </row>
-    <row r="32" spans="2:21">
-      <c r="B32" s="180" t="s">
-        <v>34</v>
-      </c>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
@@ -4012,7 +4008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -4057,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -4102,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -4147,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -4192,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -4237,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -4282,7 +4278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -4327,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -4379,7 +4375,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -4424,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -4470,7 +4466,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -4515,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -4562,7 +4558,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -4607,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -4652,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -4697,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -4742,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -4787,7 +4783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -4832,7 +4828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -4877,7 +4873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -4922,7 +4918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -4967,7 +4963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -5012,7 +5008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -5057,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -5102,7 +5098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -5147,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -5192,7 +5188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -5237,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -5282,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -5327,7 +5323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -5372,7 +5368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -5419,7 +5415,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -5465,7 +5461,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -5511,7 +5507,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -5558,7 +5554,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -5604,7 +5600,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -5649,7 +5645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -5694,7 +5690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -5739,7 +5735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -5784,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -5829,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -5874,7 +5870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -5919,7 +5915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -5964,7 +5960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -6009,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -6054,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -6099,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -6144,7 +6140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -6189,7 +6185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -6234,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -6279,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -6324,7 +6320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -6369,7 +6365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -6417,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -6462,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -6507,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -6552,7 +6548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -6597,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -6642,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -6687,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -6732,7 +6728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -6777,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1">
+    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -6823,7 +6819,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -6868,7 +6864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -6913,7 +6909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -6958,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -7003,7 +6999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -7048,7 +7044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -7093,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -7138,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -7183,7 +7179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -7228,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -7273,7 +7269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20">
+    <row r="105" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -7331,7 +7327,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BDE71B-B4DE-46F0-B853-4D73D3E1167B}">
   <dimension ref="A2:AC104"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -7362,7 +7358,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -7427,7 +7423,7 @@
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -7486,7 +7482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>46139</v>
       </c>
@@ -7500,7 +7496,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" s="20">
         <v>10</v>
@@ -7551,7 +7547,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="24">
         <v>46151</v>
       </c>
@@ -7565,7 +7561,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="26">
         <v>23</v>
@@ -7616,7 +7612,7 @@
         <v>5382</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="24"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -7663,7 +7659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="24"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
@@ -7710,7 +7706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="24"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -7757,7 +7753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="24"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -7804,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="24"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
@@ -7851,7 +7847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="24"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -7898,7 +7894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -7945,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:22">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="24"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -7992,7 +7988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:22">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -8041,7 +8037,7 @@
       <c r="U14" s="37"/>
       <c r="V14" s="38"/>
     </row>
-    <row r="15" spans="2:22">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="24"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -8090,7 +8086,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="39"/>
     </row>
-    <row r="16" spans="2:22">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -8137,7 +8133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -8184,7 +8180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:20">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -8231,7 +8227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:20">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="24"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -8278,7 +8274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:20">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -8325,7 +8321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:20">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -8372,7 +8368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:20">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -8419,7 +8415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:20">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -8466,7 +8462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -8513,7 +8509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -8560,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -8607,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -8654,7 +8650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -8701,7 +8697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -8748,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -8795,7 +8791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -8842,7 +8838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -8889,7 +8885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -8936,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -8983,7 +8979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -9030,7 +9026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -9077,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -9124,7 +9120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -9171,7 +9167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -9225,7 +9221,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -9272,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -9320,7 +9316,7 @@
       </c>
       <c r="Z41" s="35"/>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -9367,7 +9363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -9416,7 +9412,7 @@
       <c r="V43" s="34"/>
       <c r="W43" s="35"/>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -9463,7 +9459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -9510,7 +9506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -9557,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -9604,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -9651,7 +9647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -9698,7 +9694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -9745,7 +9741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -9792,7 +9788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -9839,7 +9835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -9886,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -9933,7 +9929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -9980,7 +9976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -10027,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -10074,7 +10070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -10121,7 +10117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -10168,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -10215,7 +10211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -10262,7 +10258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -10311,7 +10307,7 @@
       <c r="U62" s="37"/>
       <c r="V62" s="105"/>
     </row>
-    <row r="63" spans="2:22">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -10359,7 +10355,7 @@
       </c>
       <c r="U63" s="37"/>
     </row>
-    <row r="64" spans="2:22">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -10407,7 +10403,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -10456,7 +10452,7 @@
       <c r="U65" s="37"/>
       <c r="V65" s="106"/>
     </row>
-    <row r="66" spans="2:22">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -10504,7 +10500,7 @@
       </c>
       <c r="U66" s="37"/>
     </row>
-    <row r="67" spans="2:22">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -10551,7 +10547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:22">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -10598,7 +10594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -10645,7 +10641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -10692,7 +10688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -10739,7 +10735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -10786,7 +10782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -10833,7 +10829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -10880,7 +10876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -10927,7 +10923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -10974,7 +10970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -11021,7 +11017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -11068,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -11115,7 +11111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -11162,7 +11158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -11209,7 +11205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -11256,7 +11252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -11303,7 +11299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="36">
         <v>46057</v>
       </c>
@@ -11353,7 +11349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
@@ -11400,7 +11396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -11447,7 +11443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -11494,7 +11490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -11541,7 +11537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -11588,7 +11584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -11635,7 +11631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -11682,7 +11678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -11729,7 +11725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="2" customFormat="1">
+    <row r="93" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -11777,7 +11773,7 @@
       </c>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -11824,7 +11820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -11871,7 +11867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -11918,7 +11914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -11965,7 +11961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -12012,7 +12008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -12059,7 +12055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -12106,7 +12102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -12153,7 +12149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -12200,7 +12196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -12247,7 +12243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -12307,7 +12303,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631DB7E5-46D0-410B-A49E-BCCBB7DAB626}">
   <dimension ref="A2:AC105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -12338,7 +12334,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="45"/>
       <c r="E2" s="2"/>
@@ -12347,11 +12343,11 @@
       </c>
       <c r="G2" s="4">
         <f>SUM(G4:G495)</f>
-        <v>1757</v>
+        <v>2190</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(H4:H495)</f>
-        <v>1757</v>
+        <v>2190</v>
       </c>
       <c r="I2" s="6">
         <f>SUM(I4:I495)</f>
@@ -12363,15 +12359,15 @@
       </c>
       <c r="K2" s="8">
         <f>R2/H2</f>
-        <v>443.04539726807059</v>
+        <v>415.38619315068496</v>
       </c>
       <c r="L2" s="8">
         <f>O2/(G2*17)</f>
-        <v>28.957215507717034</v>
+        <v>27.149424388933657</v>
       </c>
       <c r="M2" s="8">
         <f>SUM(M4:M495)</f>
-        <v>864923.07000000007</v>
+        <v>1010773.0700000001</v>
       </c>
       <c r="N2" s="8">
         <f>SUM(N4:N495)</f>
@@ -12379,7 +12375,7 @@
       </c>
       <c r="O2" s="8">
         <f>SUM(O4:O495)</f>
-        <v>864923.07000000007</v>
+        <v>1010773.0700000001</v>
       </c>
       <c r="P2" s="9">
         <f>Q2/O2</f>
@@ -12387,11 +12383,11 @@
       </c>
       <c r="Q2" s="8">
         <f>SUM(Q4:Q495)</f>
-        <v>86492.307000000001</v>
+        <v>101077.307</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(R4:R495)</f>
-        <v>778430.76300000004</v>
+        <v>909695.76300000004</v>
       </c>
       <c r="S2" s="10">
         <f>SUM(S4:S495)</f>
@@ -12399,11 +12395,11 @@
       </c>
       <c r="T2" s="10">
         <f>SUM(T4:T495)</f>
-        <v>778430.76300000004</v>
+        <v>909695.76300000004</v>
       </c>
       <c r="V2" s="12"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
@@ -12462,7 +12458,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:22">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>46135</v>
       </c>
@@ -12476,7 +12472,7 @@
         <v>29</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="20">
         <v>34</v>
@@ -12527,7 +12523,7 @@
         <v>18360</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="24">
         <v>46140</v>
       </c>
@@ -12541,7 +12537,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" s="26">
         <v>83</v>
@@ -12592,7 +12588,7 @@
         <v>48802.256999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>46142</v>
       </c>
@@ -12606,7 +12602,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="26">
         <v>101</v>
@@ -12657,7 +12653,7 @@
         <v>58914.108</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="24">
         <v>46144</v>
       </c>
@@ -12671,7 +12667,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="26">
         <v>171</v>
@@ -12722,7 +12718,7 @@
         <v>99854.937000000005</v>
       </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="24">
         <v>46147</v>
       </c>
@@ -12736,7 +12732,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="26">
         <v>211</v>
@@ -12788,7 +12784,7 @@
         <v>121355.59499999999</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="24">
         <v>46149</v>
       </c>
@@ -12802,7 +12798,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="26">
         <v>1</v>
@@ -12853,7 +12849,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="24">
         <v>46150</v>
       </c>
@@ -12867,7 +12863,7 @@
         <v>23</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="26">
         <v>50</v>
@@ -12918,7 +12914,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="11" spans="2:22">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="24">
         <v>46150</v>
       </c>
@@ -12932,7 +12928,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" s="26">
         <v>240</v>
@@ -12983,7 +12979,7 @@
         <v>97200</v>
       </c>
     </row>
-    <row r="12" spans="2:22">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="24">
         <v>46151</v>
       </c>
@@ -12997,7 +12993,7 @@
         <v>32</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" s="26">
         <v>7</v>
@@ -13048,7 +13044,7 @@
         <v>2898</v>
       </c>
     </row>
-    <row r="13" spans="2:22">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="24">
         <v>46153</v>
       </c>
@@ -13059,10 +13055,10 @@
         <v>20</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13" s="26">
         <v>80</v>
@@ -13113,7 +13109,7 @@
         <v>30960</v>
       </c>
     </row>
-    <row r="14" spans="2:22">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="24">
         <v>46153</v>
       </c>
@@ -13127,7 +13123,7 @@
         <v>23</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G14" s="26">
         <v>39</v>
@@ -13178,7 +13174,7 @@
         <v>13634.945999999998</v>
       </c>
     </row>
-    <row r="15" spans="2:22">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="24">
         <v>46153</v>
       </c>
@@ -13192,7 +13188,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="26">
         <v>240</v>
@@ -13245,7 +13241,7 @@
       <c r="U15" s="37"/>
       <c r="V15" s="38"/>
     </row>
-    <row r="16" spans="2:22">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="24">
         <v>46153</v>
       </c>
@@ -13259,7 +13255,7 @@
         <v>25</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" s="26">
         <v>330</v>
@@ -13312,7 +13308,7 @@
       <c r="U16" s="37"/>
       <c r="V16" s="39"/>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="24">
         <v>46155</v>
       </c>
@@ -13326,7 +13322,7 @@
         <v>23</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" s="26">
         <v>70</v>
@@ -13377,7 +13373,7 @@
         <v>23940</v>
       </c>
     </row>
-    <row r="18" spans="2:20">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="24">
         <v>46155</v>
       </c>
@@ -13388,10 +13384,10 @@
         <v>20</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" s="28">
         <v>80</v>
@@ -13442,7 +13438,7 @@
         <v>28800</v>
       </c>
     </row>
-    <row r="19" spans="2:20">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="24">
         <v>46155</v>
       </c>
@@ -13456,7 +13452,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="28">
         <v>20</v>
@@ -13507,37 +13503,62 @@
         <v>6840</v>
       </c>
     </row>
-    <row r="20" spans="2:20">
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B20" s="24">
+        <v>46156</v>
+      </c>
+      <c r="C20" s="25">
+        <v>50</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="28">
+        <v>38</v>
+      </c>
+      <c r="H20" s="29">
+        <v>38</v>
+      </c>
       <c r="I20" s="19"/>
       <c r="J20" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K20" s="27"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="41"/>
+      <c r="K20" s="27">
+        <f>7700/38</f>
+        <v>202.63157894736841</v>
+      </c>
+      <c r="L20" s="40">
+        <f t="shared" si="7"/>
+        <v>11.919504643962847</v>
+      </c>
+      <c r="M20" s="41">
+        <f t="shared" si="0"/>
+        <v>7700</v>
+      </c>
       <c r="N20" s="27">
         <v>0</v>
       </c>
       <c r="O20" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="30"/>
+        <v>7700</v>
+      </c>
+      <c r="P20" s="30">
+        <v>0.1</v>
+      </c>
       <c r="Q20" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6930</v>
       </c>
       <c r="S20" s="40">
         <f t="shared" si="3"/>
@@ -13545,46 +13566,64 @@
       </c>
       <c r="T20" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20">
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+        <v>6930</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B21" s="24">
+        <v>46157</v>
+      </c>
+      <c r="C21" s="25">
+        <v>51</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="28">
+        <v>30</v>
+      </c>
+      <c r="H21" s="29">
+        <v>30</v>
+      </c>
       <c r="I21" s="19"/>
       <c r="J21" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K21" s="31"/>
+      <c r="K21" s="31">
+        <v>380</v>
+      </c>
       <c r="L21" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.352941176470587</v>
       </c>
       <c r="M21" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="N21" s="27">
         <v>0</v>
       </c>
       <c r="O21" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="32"/>
+        <v>11400</v>
+      </c>
+      <c r="P21" s="32">
+        <v>0.1</v>
+      </c>
       <c r="Q21" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="R21" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="S21" s="40">
         <f t="shared" si="3"/>
@@ -13592,46 +13631,65 @@
       </c>
       <c r="T21" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20">
-      <c r="B22" s="24"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+        <v>10260</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B22" s="24">
+        <v>46157</v>
+      </c>
+      <c r="C22" s="25">
+        <v>52</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="28">
+        <v>365</v>
+      </c>
+      <c r="H22" s="29">
+        <v>365</v>
+      </c>
       <c r="I22" s="19"/>
       <c r="J22" s="43">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K22" s="31"/>
+      <c r="K22" s="31">
+        <f>126750/365</f>
+        <v>347.26027397260276</v>
+      </c>
       <c r="L22" s="40">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.427074939564868</v>
       </c>
       <c r="M22" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>126750.00000000001</v>
       </c>
       <c r="N22" s="27">
         <v>0</v>
       </c>
       <c r="O22" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="32"/>
+        <v>126750.00000000001</v>
+      </c>
+      <c r="P22" s="32">
+        <v>0.1</v>
+      </c>
       <c r="Q22" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12675.000000000002</v>
       </c>
       <c r="R22" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>114075.00000000001</v>
       </c>
       <c r="S22" s="40">
         <f t="shared" si="3"/>
@@ -13639,10 +13697,10 @@
       </c>
       <c r="T22" s="23">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20">
+        <v>114075.00000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="24"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -13689,7 +13747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -13736,7 +13794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="24"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -13783,7 +13841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -13830,7 +13888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:20">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -13877,7 +13935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:20">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -13924,7 +13982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="24"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -13971,7 +14029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -14018,7 +14076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -14065,7 +14123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -14112,7 +14170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="24"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -14159,7 +14217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:29">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="24"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -14206,7 +14264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:29">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="24"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -14253,7 +14311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:29">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -14300,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="24"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -14347,7 +14405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="24"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -14394,7 +14452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -14441,7 +14499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -14495,7 +14553,7 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="24"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -14542,7 +14600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -14590,7 +14648,7 @@
       </c>
       <c r="Z42" s="35"/>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -14637,7 +14695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -14686,7 +14744,7 @@
       <c r="V44" s="34"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="24"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -14733,7 +14791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
@@ -14780,7 +14838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
@@ -14827,7 +14885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
@@ -14874,7 +14932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -14921,7 +14979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:22">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -14968,7 +15026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:22">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
@@ -15015,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:22">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -15062,7 +15120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:22">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -15109,7 +15167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:22">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
@@ -15156,7 +15214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:22">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
@@ -15203,7 +15261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:22">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
@@ -15250,7 +15308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:22">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
@@ -15297,7 +15355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:22">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
@@ -15344,7 +15402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:22">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
@@ -15391,7 +15449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:22">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
@@ -15438,7 +15496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:22">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
@@ -15485,7 +15543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:22">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
@@ -15532,7 +15590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:22">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
@@ -15581,7 +15639,7 @@
       <c r="U63" s="37"/>
       <c r="V63" s="105"/>
     </row>
-    <row r="64" spans="2:22">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -15629,7 +15687,7 @@
       </c>
       <c r="U64" s="37"/>
     </row>
-    <row r="65" spans="2:22">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -15677,7 +15735,7 @@
       </c>
       <c r="U65" s="37"/>
     </row>
-    <row r="66" spans="2:22">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -15726,7 +15784,7 @@
       <c r="U66" s="37"/>
       <c r="V66" s="106"/>
     </row>
-    <row r="67" spans="2:22">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
@@ -15774,7 +15832,7 @@
       </c>
       <c r="U67" s="37"/>
     </row>
-    <row r="68" spans="2:22">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
@@ -15821,7 +15879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -15868,7 +15926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:22">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -15915,7 +15973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:22">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
@@ -15962,7 +16020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:22">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -16009,7 +16067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:22">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
@@ -16056,7 +16114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:22">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -16103,7 +16161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:22">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -16150,7 +16208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:22">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -16197,7 +16255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:22">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -16244,7 +16302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:22">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -16291,7 +16349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:22">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -16338,7 +16396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:22">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -16385,7 +16443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
@@ -16432,7 +16490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
@@ -16479,7 +16537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
@@ -16526,7 +16584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
@@ -16573,7 +16631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="36">
         <v>46057</v>
       </c>
@@ -16623,7 +16681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
@@ -16670,7 +16728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -16717,7 +16775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
@@ -16764,7 +16822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
@@ -16811,7 +16869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
@@ -16858,7 +16916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
@@ -16905,7 +16963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
@@ -16952,7 +17010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
@@ -16999,7 +17057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="2" customFormat="1">
+    <row r="94" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
@@ -17047,7 +17105,7 @@
       </c>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
@@ -17094,7 +17152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
@@ -17141,7 +17199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:20">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
@@ -17188,7 +17246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:20">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="24"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
@@ -17235,7 +17293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:20">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
@@ -17282,7 +17340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:20">
+    <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" s="24"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
@@ -17329,7 +17387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:20">
+    <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" s="24"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
@@ -17376,7 +17434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:20">
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" s="24"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
@@ -17423,7 +17481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:20">
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" s="24"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
@@ -17470,7 +17528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:20">
+    <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" s="24"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
@@ -17517,7 +17575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:20">
+    <row r="105" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -17577,7 +17635,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14DF8A7-7A30-473E-8FAB-92CB0FE83A84}">
   <dimension ref="B1:P106"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" style="47"/>
@@ -17597,19 +17655,19 @@
     <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>10.55028957586768</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="49" t="s">
         <v>17</v>
       </c>
@@ -17638,13 +17696,13 @@
         <v>325106.56000000006</v>
       </c>
       <c r="L2" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="46" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
@@ -17652,13 +17710,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="59" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>10</v>
@@ -17667,25 +17725,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="K3" s="65">
+        <v>0</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="K3" s="65">
-        <v>0</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>46</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="107">
         <f>Tomatillo!B4</f>
         <v>46128</v>
@@ -17695,7 +17753,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="108" t="str">
         <f>Tomatillo!E4</f>
@@ -17718,14 +17776,14 @@
         <v>15300</v>
       </c>
       <c r="J4" s="112" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="68">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N4" s="69">
         <v>46128</v>
@@ -17734,7 +17792,7 @@
         <v>36720</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15.75" thickBot="1">
+    <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="107">
         <f>Tomatillo!B5</f>
         <v>46128</v>
@@ -17744,7 +17802,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="108" t="str">
         <f>Tomatillo!E5</f>
@@ -17767,7 +17825,7 @@
         <v>3060</v>
       </c>
       <c r="J5" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="71">
         <v>46129</v>
@@ -17777,7 +17835,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16" ht="15.75" thickBot="1">
+    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="107">
         <f>Tomatillo!B6</f>
         <v>46128</v>
@@ -17787,7 +17845,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" s="108" t="str">
         <f>Tomatillo!E6</f>
@@ -17810,7 +17868,7 @@
         <v>6120</v>
       </c>
       <c r="J6" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="71">
         <v>46133</v>
@@ -17819,7 +17877,7 @@
         <v>40086</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15.75" thickBot="1">
+    <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="107">
         <f>Tomatillo!B7</f>
         <v>46128</v>
@@ -17829,7 +17887,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="108" t="str">
         <f>Tomatillo!E7</f>
@@ -17852,7 +17910,7 @@
         <v>12240</v>
       </c>
       <c r="J7" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="73">
         <f>95764/(434*17)</f>
@@ -17865,7 +17923,7 @@
         <v>123114</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="15.75" thickBot="1">
+    <row r="8" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="107">
         <f>Tomatillo!B8</f>
         <v>46128</v>
@@ -17875,7 +17933,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="108" t="str">
         <f>Tomatillo!E8</f>
@@ -17898,7 +17956,7 @@
         <v>110976</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="73"/>
       <c r="N8" s="71">
@@ -17908,7 +17966,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15.75" thickBot="1">
+    <row r="9" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="107">
         <f>Tomatillo!B9</f>
         <v>46129</v>
@@ -17918,7 +17976,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="108" t="str">
         <f>Tomatillo!E9</f>
@@ -17940,7 +17998,7 @@
         <v>15300</v>
       </c>
       <c r="J9" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9:K15" si="1">G9/17</f>
@@ -17953,7 +18011,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="107">
         <f>Tomatillo!B10</f>
         <v>46129</v>
@@ -17963,7 +18021,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="108" t="str">
         <f>Tomatillo!E10</f>
@@ -17985,7 +18043,7 @@
         <v>63648</v>
       </c>
       <c r="J10" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="73">
         <f t="shared" si="1"/>
@@ -17998,7 +18056,7 @@
         <v>5530</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="116">
         <f>Tomatillo!B11</f>
         <v>46129</v>
@@ -18008,7 +18066,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="81" t="str">
         <f>Tomatillo!E11</f>
@@ -18031,7 +18089,7 @@
         <v>16816</v>
       </c>
       <c r="J11" s="104" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="73">
         <f t="shared" si="1"/>
@@ -18048,7 +18106,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="107">
         <f>Tomatillo!B12</f>
         <v>46130</v>
@@ -18058,7 +18116,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="108" t="str">
         <f>Tomatillo!E12</f>
@@ -18081,7 +18139,7 @@
         <v>34986</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12" s="73">
         <f t="shared" si="1"/>
@@ -18094,7 +18152,7 @@
         <v>110976</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="107">
         <f>Tomatillo!B13</f>
         <v>46130</v>
@@ -18104,7 +18162,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="113" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="108" t="str">
         <f>Tomatillo!E13</f>
@@ -18127,7 +18185,7 @@
         <v>43350</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="73">
         <f t="shared" si="1"/>
@@ -18140,7 +18198,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15.75" thickBot="1">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="107">
         <f>Tomatillo!B14</f>
         <v>46132</v>
@@ -18150,7 +18208,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="108" t="str">
         <f>Tomatillo!E14</f>
@@ -18173,7 +18231,7 @@
         <v>5100</v>
       </c>
       <c r="J14" s="117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="73">
         <f t="shared" si="1"/>
@@ -18188,7 +18246,7 @@
         <v>97750</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="107">
         <f>Tomatillo!B15</f>
         <v>46132</v>
@@ -18198,7 +18256,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" s="108" t="str">
         <f>Tomatillo!E15</f>
@@ -18221,7 +18279,7 @@
         <v>38250</v>
       </c>
       <c r="J15" s="117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="73">
         <f t="shared" si="1"/>
@@ -18237,7 +18295,7 @@
         <v>25567</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="107">
         <f>Tomatillo!B16</f>
         <v>46133</v>
@@ -18247,7 +18305,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="113" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="108" t="str">
         <f>Tomatillo!E16</f>
@@ -18270,12 +18328,12 @@
         <v>54400</v>
       </c>
       <c r="J16" s="117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15" ht="15.75" thickBot="1">
+    <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="128">
         <f>Tomatillo!B17</f>
         <v>46133</v>
@@ -18285,7 +18343,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" s="129" t="str">
         <f>Tomatillo!E17</f>
@@ -18311,7 +18369,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15" ht="15.75" thickBot="1">
+    <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="136">
         <f>Tomatillo!B18</f>
         <v>46134</v>
@@ -18321,7 +18379,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="85" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="81" t="str">
         <f>Tomatillo!E18</f>
@@ -18344,12 +18402,12 @@
         <v>12240</v>
       </c>
       <c r="J18" s="137" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15" ht="15.75" thickBot="1">
+    <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="107">
         <f>Tomatillo!B19</f>
         <v>46134</v>
@@ -18359,7 +18417,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="108" t="str">
         <f>Tomatillo!E19</f>
@@ -18382,12 +18440,12 @@
         <v>84864</v>
       </c>
       <c r="J19" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15" ht="15.75" thickBot="1">
+    <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="107">
         <f>Tomatillo!B20</f>
         <v>46136</v>
@@ -18397,7 +18455,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="163" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="108" t="str">
         <f>Tomatillo!E20</f>
@@ -18419,22 +18477,22 @@
         <v>6120</v>
       </c>
       <c r="J20" s="165" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15" ht="15.75" thickBot="1">
+    <row r="21" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="107">
         <f>Tomatillo!B21</f>
-        <v>46046</v>
+        <v>46136</v>
       </c>
       <c r="C21" s="108">
         <f>Tomatillo!C21</f>
         <v>21</v>
       </c>
       <c r="D21" s="158" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" s="108" t="str">
         <f>Tomatillo!E21</f>
@@ -18456,12 +18514,12 @@
         <v>205530</v>
       </c>
       <c r="J21" s="160" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15" ht="15.75" thickBot="1">
+    <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="136">
         <f>Tomatillo!B22</f>
         <v>46137</v>
@@ -18471,7 +18529,7 @@
         <v>23</v>
       </c>
       <c r="D22" s="161" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" s="81" t="str">
         <f>Tomatillo!E22</f>
@@ -18493,12 +18551,12 @@
         <v>6120</v>
       </c>
       <c r="J22" s="162" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15" ht="15.75" thickBot="1">
+    <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="136">
         <f>Tomatillo!B23</f>
         <v>46142</v>
@@ -18508,7 +18566,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="161" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" s="81" t="str">
         <f>Tomatillo!E23</f>
@@ -18530,12 +18588,12 @@
         <v>4284</v>
       </c>
       <c r="J23" s="162" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15" ht="15.75" thickBot="1">
+    <row r="24" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="136">
         <f>Tomatillo!B24</f>
         <v>46142</v>
@@ -18545,7 +18603,7 @@
         <v>28</v>
       </c>
       <c r="D24" s="161" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="81" t="str">
         <f>Tomatillo!E24</f>
@@ -18567,12 +18625,12 @@
         <v>78336</v>
       </c>
       <c r="J24" s="162" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15" ht="15.75" thickBot="1">
+    <row r="25" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="136">
         <f>Tomatillo!B25</f>
         <v>46143</v>
@@ -18582,7 +18640,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" s="81" t="str">
         <f>Tomatillo!E25</f>
@@ -18604,12 +18662,12 @@
         <v>17680</v>
       </c>
       <c r="J25" s="162" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15" ht="15.75" thickBot="1">
+    <row r="26" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="136">
         <f>Tomatillo!B26</f>
         <v>46146</v>
@@ -18619,7 +18677,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" s="81" t="str">
         <f>Tomatillo!E26</f>
@@ -18641,12 +18699,12 @@
         <v>129841.92000000001</v>
       </c>
       <c r="J26" s="94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15" ht="15.75" thickBot="1">
+    <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="136">
         <f>Tomatillo!B27</f>
         <v>46147</v>
@@ -18656,7 +18714,7 @@
         <v>34</v>
       </c>
       <c r="D27" s="86" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" s="81" t="str">
         <f>Tomatillo!E27</f>
@@ -18678,12 +18736,12 @@
         <v>59653</v>
       </c>
       <c r="J27" s="137" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15" ht="15.75" thickBot="1">
+    <row r="28" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="107">
         <f>Tomatillo!B28</f>
         <v>46149</v>
@@ -18693,7 +18751,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="113" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" s="108" t="str">
         <f>Tomatillo!E28</f>
@@ -18715,12 +18773,12 @@
         <v>136</v>
       </c>
       <c r="J28" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15" ht="15.75" thickBot="1">
+    <row r="29" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="107">
         <f>Tomatillo!B29</f>
         <v>46149</v>
@@ -18730,7 +18788,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="113" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" s="108" t="str">
         <f>Tomatillo!E29</f>
@@ -18752,12 +18810,12 @@
         <v>7021</v>
       </c>
       <c r="J29" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15" ht="15.75" thickBot="1">
+    <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="107">
         <f>Tomatillo!B30</f>
         <v>46150</v>
@@ -18767,7 +18825,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="163" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" s="108" t="str">
         <f>Tomatillo!E30</f>
@@ -18789,12 +18847,12 @@
         <v>16320</v>
       </c>
       <c r="J30" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15" ht="15.75" thickBot="1">
+    <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="107">
         <f>Tomatillo!B31</f>
         <v>46154</v>
@@ -18804,7 +18862,7 @@
         <v>46</v>
       </c>
       <c r="D31" s="113" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" s="108" t="str">
         <f>Tomatillo!E31</f>
@@ -18826,12 +18884,12 @@
         <v>9246.6400000000012</v>
       </c>
       <c r="J31" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="136"/>
       <c r="C32" s="81"/>
       <c r="D32" s="86"/>
@@ -18844,7 +18902,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -18857,7 +18915,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -18870,7 +18928,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -18883,7 +18941,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -18896,7 +18954,7 @@
       <c r="N36" s="71"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -18909,7 +18967,7 @@
       <c r="N37" s="76"/>
       <c r="O37" s="72"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -18922,7 +18980,7 @@
       <c r="N38" s="77"/>
       <c r="O38" s="78"/>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -18940,7 +18998,7 @@
         <v>731832</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="89"/>
       <c r="C40" s="86"/>
       <c r="D40" s="86"/>
@@ -18951,7 +19009,7 @@
       <c r="I40" s="88"/>
       <c r="J40" s="90"/>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -18962,14 +19020,14 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
       <c r="N41" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O41" s="67">
         <f>Tomatillo!Q2</f>
         <v>92709.664000000019</v>
       </c>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -18980,7 +19038,7 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -18991,14 +19049,14 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
       <c r="N43" s="66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O43" s="67">
         <f>Tomatillo!T2</f>
         <v>964228.89600000007</v>
       </c>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="89"/>
       <c r="C44" s="86"/>
       <c r="D44" s="86"/>
@@ -19009,7 +19067,7 @@
       <c r="I44" s="75"/>
       <c r="J44" s="90"/>
     </row>
-    <row r="45" spans="2:15" ht="15.75" thickBot="1">
+    <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -19020,14 +19078,14 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
       <c r="N45" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O45" s="67">
         <f>+O43+O41-O39</f>
         <v>325106.56000000006</v>
       </c>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -19038,7 +19096,7 @@
       <c r="I46" s="75"/>
       <c r="J46" s="92"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="89"/>
       <c r="C47" s="86"/>
       <c r="D47" s="86"/>
@@ -19050,7 +19108,7 @@
       <c r="J47" s="90"/>
       <c r="O47" s="79"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -19061,7 +19119,7 @@
       <c r="I48" s="75"/>
       <c r="J48" s="92"/>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -19073,7 +19131,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -19085,7 +19143,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="96"/>
       <c r="C51" s="87"/>
       <c r="D51" s="86"/>
@@ -19097,7 +19155,7 @@
       <c r="J51" s="90"/>
       <c r="O51" s="80"/>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="96"/>
       <c r="C52" s="87"/>
       <c r="D52" s="86"/>
@@ -19110,7 +19168,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -19123,7 +19181,7 @@
       <c r="O53" s="80"/>
       <c r="P53" s="80"/>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="96"/>
       <c r="C54" s="87"/>
       <c r="D54" s="86"/>
@@ -19134,7 +19192,7 @@
       <c r="I54" s="88"/>
       <c r="J54" s="90"/>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -19147,7 +19205,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="96"/>
       <c r="C56" s="87"/>
       <c r="D56" s="86"/>
@@ -19160,7 +19218,7 @@
       <c r="O56" s="80"/>
       <c r="P56" s="80"/>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -19171,7 +19229,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -19182,7 +19240,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -19193,7 +19251,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="96"/>
       <c r="C60" s="87"/>
       <c r="D60" s="86"/>
@@ -19204,7 +19262,7 @@
       <c r="I60" s="88"/>
       <c r="J60" s="90"/>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="96"/>
       <c r="C61" s="87"/>
       <c r="D61" s="86"/>
@@ -19215,7 +19273,7 @@
       <c r="I61" s="88"/>
       <c r="J61" s="90"/>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="96"/>
       <c r="C62" s="87"/>
       <c r="D62" s="86"/>
@@ -19226,7 +19284,7 @@
       <c r="I62" s="88"/>
       <c r="J62" s="90"/>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -19237,7 +19295,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -19248,7 +19306,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -19259,7 +19317,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="96"/>
       <c r="C66" s="87"/>
       <c r="D66" s="86"/>
@@ -19270,7 +19328,7 @@
       <c r="I66" s="88"/>
       <c r="J66" s="90"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -19281,7 +19339,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -19292,7 +19350,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="96"/>
       <c r="C69" s="87"/>
       <c r="D69" s="86"/>
@@ -19303,7 +19361,7 @@
       <c r="I69" s="88"/>
       <c r="J69" s="90"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="96"/>
       <c r="C70" s="87"/>
       <c r="D70" s="86"/>
@@ -19314,7 +19372,7 @@
       <c r="I70" s="88"/>
       <c r="J70" s="90"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="96"/>
       <c r="C71" s="87"/>
       <c r="D71" s="86"/>
@@ -19325,7 +19383,7 @@
       <c r="I71" s="88"/>
       <c r="J71" s="90"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -19336,7 +19394,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -19347,7 +19405,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="92"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -19358,7 +19416,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="98"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="96"/>
       <c r="C75" s="87"/>
       <c r="D75" s="86"/>
@@ -19369,7 +19427,7 @@
       <c r="I75" s="88"/>
       <c r="J75" s="90"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="96"/>
       <c r="C76" s="87"/>
       <c r="D76" s="86"/>
@@ -19380,7 +19438,7 @@
       <c r="I76" s="88"/>
       <c r="J76" s="99"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -19391,7 +19449,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -19402,7 +19460,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="96"/>
       <c r="C79" s="87"/>
       <c r="D79" s="86"/>
@@ -19413,7 +19471,7 @@
       <c r="I79" s="88"/>
       <c r="J79" s="90"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="96"/>
       <c r="C80" s="87"/>
       <c r="D80" s="86"/>
@@ -19424,7 +19482,7 @@
       <c r="I80" s="88"/>
       <c r="J80" s="90"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -19435,7 +19493,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="96"/>
       <c r="C82" s="87"/>
       <c r="D82" s="86"/>
@@ -19446,7 +19504,7 @@
       <c r="I82" s="88"/>
       <c r="J82" s="90"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="96"/>
       <c r="C83" s="87"/>
       <c r="D83" s="86"/>
@@ -19457,7 +19515,7 @@
       <c r="I83" s="88"/>
       <c r="J83" s="90"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -19468,7 +19526,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="96"/>
       <c r="C85" s="87"/>
       <c r="D85" s="86"/>
@@ -19479,7 +19537,7 @@
       <c r="I85" s="88"/>
       <c r="J85" s="90"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -19490,7 +19548,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="96"/>
       <c r="C87" s="87"/>
       <c r="D87" s="86"/>
@@ -19501,7 +19559,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="90"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -19512,7 +19570,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="96"/>
       <c r="C89" s="87"/>
       <c r="D89" s="86"/>
@@ -19523,7 +19581,7 @@
       <c r="I89" s="88"/>
       <c r="J89" s="90"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -19534,7 +19592,7 @@
       <c r="I90" s="88"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -19545,7 +19603,7 @@
       <c r="I91" s="88"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="96"/>
       <c r="C92" s="87"/>
       <c r="D92" s="86"/>
@@ -19556,7 +19614,7 @@
       <c r="I92" s="93"/>
       <c r="J92" s="103"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -19567,7 +19625,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -19578,7 +19636,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -19589,7 +19647,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -19600,7 +19658,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="24"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -19611,7 +19669,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="92"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -19622,7 +19680,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="94"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -19633,7 +19691,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -19644,7 +19702,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -19655,7 +19713,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -19666,7 +19724,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="92"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -19677,7 +19735,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="94"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -19688,7 +19746,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -19699,7 +19757,7 @@
       <c r="I105" s="75"/>
       <c r="J105" s="92"/>
     </row>
-    <row r="106" spans="2:10">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="91"/>
       <c r="C106" s="85"/>
       <c r="D106" s="85"/>
@@ -19719,7 +19777,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A884314C-68A6-4266-8FA4-11EA17178DDD}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" style="47"/>
@@ -19739,29 +19797,29 @@
     <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
-        <v>28.964809075630253</v>
+        <v>27.149714909326079</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="145">
         <f>SUM(F4:F390)</f>
-        <v>1750</v>
+        <v>2183</v>
       </c>
       <c r="G2" s="146">
         <f>I2/F2</f>
-        <v>492.40175428571433</v>
+        <v>461.54515345854333</v>
       </c>
       <c r="H2" s="147">
         <f>SUM(H4:H390)</f>
@@ -19769,7 +19827,7 @@
       </c>
       <c r="I2" s="53">
         <f>SUM(I4:I390)</f>
-        <v>861703.07000000007</v>
+        <v>1007553.0700000001</v>
       </c>
       <c r="J2" s="148">
         <f>O38</f>
@@ -19777,16 +19835,16 @@
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>162678.07000000007</v>
+        <v>308528.07000000007</v>
       </c>
       <c r="L2" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="46" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -19794,13 +19852,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="152" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="153" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="154" t="s">
         <v>10</v>
@@ -19809,25 +19867,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="156" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="K3" s="143">
+        <v>0</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="K3" s="143">
-        <v>0</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>46</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="149">
         <v>46135</v>
       </c>
@@ -19835,7 +19893,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="150" t="s">
         <v>29</v>
@@ -19854,14 +19912,14 @@
         <v>20400</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K4" s="142">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N4" s="69">
         <v>46140</v>
@@ -19870,7 +19928,7 @@
         <v>54225</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="173">
         <f>Roma!B5</f>
         <v>46140</v>
@@ -19880,7 +19938,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" s="113" t="str">
         <f>Roma!E5</f>
@@ -19903,7 +19961,7 @@
         <v>54224.729999999996</v>
       </c>
       <c r="J5" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="71">
         <v>46142</v>
@@ -19913,7 +19971,7 @@
       </c>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="173">
         <f>Roma!B6</f>
         <v>46142</v>
@@ -19923,7 +19981,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" s="113" t="str">
         <f>Roma!E6</f>
@@ -19945,7 +20003,7 @@
         <v>65460.12</v>
       </c>
       <c r="J6" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="71">
         <v>46146</v>
@@ -19954,7 +20012,7 @@
         <v>110950</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="173">
         <f>Roma!B7</f>
         <v>46144</v>
@@ -19964,7 +20022,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" s="113" t="str">
         <f>Roma!E7</f>
@@ -19984,7 +20042,7 @@
         <v>110949.93000000001</v>
       </c>
       <c r="J7" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="73"/>
       <c r="N7" s="71">
@@ -19994,7 +20052,7 @@
         <v>134840</v>
       </c>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="173">
         <f>Roma!B8</f>
         <v>46147</v>
@@ -20004,7 +20062,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="113" t="str">
         <f>Roma!E8</f>
@@ -20026,7 +20084,7 @@
         <v>134839.54999999999</v>
       </c>
       <c r="J8" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="73"/>
       <c r="N8" s="71">
@@ -20037,7 +20095,7 @@
         <v>132620</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="173">
         <f>Roma!B9</f>
         <v>46149</v>
@@ -20047,7 +20105,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" s="113" t="str">
         <f>Roma!E9</f>
@@ -20069,7 +20127,7 @@
         <v>620</v>
       </c>
       <c r="J9" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="73"/>
       <c r="N9" s="71">
@@ -20079,7 +20137,7 @@
         <v>145550</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="173">
         <f>Roma!B10</f>
         <v>46150</v>
@@ -20089,7 +20147,7 @@
         <v>38</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="113" t="str">
         <f>Roma!E10</f>
@@ -20111,7 +20169,7 @@
         <v>24000</v>
       </c>
       <c r="J10" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="73"/>
       <c r="N10" s="71">
@@ -20121,7 +20179,7 @@
         <v>58600</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="173">
         <f>Roma!B11</f>
         <v>46150</v>
@@ -20131,7 +20189,7 @@
         <v>39</v>
       </c>
       <c r="D11" s="113" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" s="113" t="str">
         <f>Roma!E11</f>
@@ -20153,14 +20211,14 @@
         <v>108000</v>
       </c>
       <c r="J11" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="79"/>
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="173">
         <f>Roma!B13</f>
         <v>46153</v>
@@ -20170,7 +20228,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" s="113" t="str">
         <f>Roma!E13</f>
@@ -20192,13 +20250,13 @@
         <v>34400</v>
       </c>
       <c r="J12" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12" s="73"/>
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="173">
         <f>Roma!B14</f>
         <v>46153</v>
@@ -20208,7 +20266,7 @@
         <v>43</v>
       </c>
       <c r="D13" s="113" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="113" t="str">
         <f>Roma!E14</f>
@@ -20230,13 +20288,13 @@
         <v>15149.939999999999</v>
       </c>
       <c r="J13" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="73"/>
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="173">
         <f>Roma!B15</f>
         <v>46153</v>
@@ -20246,7 +20304,7 @@
         <v>44</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="113" t="str">
         <f>Roma!E15</f>
@@ -20268,7 +20326,7 @@
         <v>96000</v>
       </c>
       <c r="J14" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="73"/>
       <c r="L14" s="74"/>
@@ -20276,7 +20334,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="91">
         <f>Roma!B16</f>
         <v>46153</v>
@@ -20286,7 +20344,7 @@
         <v>45</v>
       </c>
       <c r="D15" s="85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="85" t="str">
         <f>Roma!E16</f>
@@ -20308,7 +20366,7 @@
         <v>131458.80000000002</v>
       </c>
       <c r="J15" s="94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K15" s="73"/>
       <c r="L15" s="74"/>
@@ -20316,7 +20374,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="173">
         <f>Roma!B17</f>
         <v>46155</v>
@@ -20326,7 +20384,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="113" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="113" t="str">
         <f>Roma!E17</f>
@@ -20348,12 +20406,12 @@
         <v>26600</v>
       </c>
       <c r="J16" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="173">
         <f>Roma!B18</f>
         <v>46155</v>
@@ -20363,7 +20421,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="113" t="str">
         <f>Roma!E18</f>
@@ -20385,12 +20443,12 @@
         <v>32000</v>
       </c>
       <c r="J17" s="138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="91">
         <f>Roma!B19</f>
         <v>46155</v>
@@ -20400,7 +20458,7 @@
         <v>49</v>
       </c>
       <c r="D18" s="85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="85" t="str">
         <f>Roma!E19</f>
@@ -20422,51 +20480,123 @@
         <v>7600</v>
       </c>
       <c r="J18" s="94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="91"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="94"/>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="91">
+        <f>Roma!B20</f>
+        <v>46156</v>
+      </c>
+      <c r="C19" s="85">
+        <f>Roma!C20</f>
+        <v>50</v>
+      </c>
+      <c r="D19" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="85" t="str">
+        <f>Roma!E20</f>
+        <v>Julio Mendoza</v>
+      </c>
+      <c r="F19" s="25">
+        <f>Roma!H20</f>
+        <v>38</v>
+      </c>
+      <c r="G19" s="75">
+        <f>Roma!K20</f>
+        <v>202.63157894736841</v>
+      </c>
+      <c r="H19" s="84">
+        <v>0</v>
+      </c>
+      <c r="I19" s="75">
+        <f t="shared" ref="I19" si="6">F19*G19-H19</f>
+        <v>7700</v>
+      </c>
+      <c r="J19" s="94" t="s">
+        <v>56</v>
+      </c>
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="91"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="92"/>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="91">
+        <f>Roma!B21</f>
+        <v>46157</v>
+      </c>
+      <c r="C20" s="85">
+        <f>Roma!C21</f>
+        <v>51</v>
+      </c>
+      <c r="D20" s="85" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="85" t="str">
+        <f>Roma!E21</f>
+        <v>Samuel Cuadras</v>
+      </c>
+      <c r="F20" s="25">
+        <f>Roma!H21</f>
+        <v>30</v>
+      </c>
+      <c r="G20" s="75">
+        <f>Roma!K21</f>
+        <v>380</v>
+      </c>
+      <c r="H20" s="84">
+        <v>0</v>
+      </c>
+      <c r="I20" s="75">
+        <f t="shared" ref="I20" si="7">F20*G20-H20</f>
+        <v>11400</v>
+      </c>
+      <c r="J20" s="94" t="s">
+        <v>56</v>
+      </c>
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="91"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="92"/>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="91">
+        <f>Roma!B22</f>
+        <v>46157</v>
+      </c>
+      <c r="C21" s="85">
+        <f>Roma!C22</f>
+        <v>52</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="85" t="str">
+        <f>Roma!E22</f>
+        <v>Efrén Medina</v>
+      </c>
+      <c r="F21" s="25">
+        <f>Roma!H22</f>
+        <v>365</v>
+      </c>
+      <c r="G21" s="75">
+        <f>Roma!K22</f>
+        <v>347.26027397260276</v>
+      </c>
+      <c r="H21" s="84">
+        <v>0</v>
+      </c>
+      <c r="I21" s="75">
+        <f t="shared" ref="I21" si="8">F21*G21-H21</f>
+        <v>126750.00000000001</v>
+      </c>
+      <c r="J21" s="94" t="s">
+        <v>56</v>
+      </c>
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -20479,7 +20609,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -20492,7 +20622,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -20505,7 +20635,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -20518,7 +20648,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -20531,7 +20661,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -20544,7 +20674,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -20557,7 +20687,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -20570,7 +20700,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -20583,7 +20713,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -20596,7 +20726,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -20609,7 +20739,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -20622,7 +20752,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -20635,7 +20765,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -20648,7 +20778,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -20661,7 +20791,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1">
+    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -20674,7 +20804,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -20692,7 +20822,7 @@
         <v>702245</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -20703,7 +20833,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -20714,14 +20844,14 @@
       <c r="I40" s="75"/>
       <c r="J40" s="92"/>
       <c r="N40" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O40" s="67">
         <f>Roma!Q2</f>
-        <v>86492.307000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1">
+        <v>101077.307</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -20732,7 +20862,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -20743,14 +20873,14 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
       <c r="N42" s="66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O42" s="67">
         <f>+Roma!R2</f>
-        <v>778430.76300000004</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1">
+        <v>909695.76300000004</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -20761,7 +20891,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -20772,14 +20902,14 @@
       <c r="I44" s="75"/>
       <c r="J44" s="92"/>
       <c r="N44" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>162678.07000000007</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15">
+        <v>308528.07000000007</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -20790,7 +20920,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -20802,7 +20932,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -20813,7 +20943,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -20825,7 +20955,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -20837,7 +20967,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -20849,7 +20979,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -20862,7 +20992,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -20875,7 +21005,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -20886,7 +21016,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -20899,7 +21029,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -20912,7 +21042,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -20923,7 +21053,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -20934,7 +21064,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -20945,7 +21075,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -20956,7 +21086,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -20967,7 +21097,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -20978,7 +21108,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -20989,7 +21119,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -21000,7 +21130,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -21011,7 +21141,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -21022,7 +21152,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -21033,7 +21163,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -21044,7 +21174,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -21055,7 +21185,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -21066,7 +21196,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -21077,7 +21207,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -21088,7 +21218,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -21099,7 +21229,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -21110,7 +21240,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -21121,7 +21251,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -21132,7 +21262,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -21143,7 +21273,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -21154,7 +21284,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -21165,7 +21295,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -21176,7 +21306,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -21187,7 +21317,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -21198,7 +21328,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -21209,7 +21339,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -21220,7 +21350,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -21231,7 +21361,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -21242,7 +21372,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -21253,7 +21383,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -21264,7 +21394,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -21275,7 +21405,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -21286,7 +21416,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -21297,7 +21427,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -21308,7 +21438,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -21319,7 +21449,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -21330,7 +21460,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -21341,7 +21471,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -21352,7 +21482,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -21363,7 +21493,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -21374,7 +21504,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -21385,7 +21515,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -21396,7 +21526,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -21407,7 +21537,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -21418,7 +21548,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -21429,7 +21559,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -21440,7 +21570,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -21451,7 +21581,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -21471,7 +21601,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7F0943-67B8-4148-A349-2B4FA39AA366}">
   <dimension ref="B1:P105"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="47" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" style="47"/>
@@ -21491,19 +21621,19 @@
     <col min="18" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="16.5" thickBot="1">
+    <row r="1" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I1" s="139">
         <f>I2/(F2*17)</f>
         <v>14.937611408199643</v>
       </c>
       <c r="J1" s="140" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="16.5" thickBot="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="144" t="s">
         <v>17</v>
       </c>
@@ -21532,13 +21662,13 @@
         <v>2400</v>
       </c>
       <c r="L2" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="46" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
@@ -21546,13 +21676,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="152" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="153" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="154" t="s">
         <v>10</v>
@@ -21561,25 +21691,25 @@
         <v>13</v>
       </c>
       <c r="I3" s="156" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="K3" s="143">
+        <v>0</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="K3" s="143">
-        <v>0</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>46</v>
       </c>
       <c r="N3" s="66" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="67" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="149">
         <f>Morrón!B4</f>
         <v>46139</v>
@@ -21589,7 +21719,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" s="150" t="str">
         <f>Morrón!E4</f>
@@ -21611,14 +21741,14 @@
         <v>2400</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K4" s="142">
         <f>[1]VENTAS!R2</f>
         <v>691969.5</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N4" s="69">
         <v>46154</v>
@@ -21627,7 +21757,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="176">
         <f>Morrón!B5</f>
         <v>46151</v>
@@ -21637,7 +21767,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" s="177" t="str">
         <f>Morrón!E5</f>
@@ -21659,13 +21789,13 @@
         <v>5980</v>
       </c>
       <c r="J5" s="179" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="71"/>
       <c r="O5" s="72"/>
       <c r="P5" s="141"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="91"/>
       <c r="C6" s="85"/>
       <c r="D6" s="85"/>
@@ -21683,7 +21813,7 @@
       <c r="N6" s="71"/>
       <c r="O6" s="72"/>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="91"/>
       <c r="C7" s="85"/>
       <c r="D7" s="85"/>
@@ -21702,7 +21832,7 @@
       <c r="N7" s="71"/>
       <c r="O7" s="72"/>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="91"/>
       <c r="C8" s="85"/>
       <c r="D8" s="85"/>
@@ -21721,7 +21851,7 @@
       <c r="N8" s="71"/>
       <c r="O8" s="72"/>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="91"/>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -21740,7 +21870,7 @@
       <c r="N9" s="71"/>
       <c r="O9" s="72"/>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="91"/>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -21759,7 +21889,7 @@
       <c r="N10" s="71"/>
       <c r="O10" s="72"/>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="91"/>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -21779,7 +21909,7 @@
       <c r="N11" s="71"/>
       <c r="O11" s="72"/>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="91"/>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -21798,7 +21928,7 @@
       <c r="N12" s="71"/>
       <c r="O12" s="72"/>
     </row>
-    <row r="13" spans="2:16">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="91"/>
       <c r="C13" s="85"/>
       <c r="D13" s="85"/>
@@ -21817,7 +21947,7 @@
       <c r="N13" s="71"/>
       <c r="O13" s="72"/>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="91"/>
       <c r="C14" s="85"/>
       <c r="D14" s="85"/>
@@ -21838,7 +21968,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="72"/>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="91"/>
       <c r="C15" s="85"/>
       <c r="D15" s="85"/>
@@ -21859,7 +21989,7 @@
       <c r="N15" s="71"/>
       <c r="O15" s="72"/>
     </row>
-    <row r="16" spans="2:16">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="91"/>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
@@ -21877,7 +22007,7 @@
       <c r="N16" s="71"/>
       <c r="O16" s="72"/>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="91"/>
       <c r="C17" s="85"/>
       <c r="D17" s="85"/>
@@ -21895,7 +22025,7 @@
       <c r="N17" s="71"/>
       <c r="O17" s="72"/>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="91"/>
       <c r="C18" s="85"/>
       <c r="D18" s="85"/>
@@ -21913,7 +22043,7 @@
       <c r="N18" s="71"/>
       <c r="O18" s="72"/>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="91"/>
       <c r="C19" s="85"/>
       <c r="D19" s="85"/>
@@ -21926,7 +22056,7 @@
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="91"/>
       <c r="C20" s="85"/>
       <c r="D20" s="85"/>
@@ -21939,7 +22069,7 @@
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="91"/>
       <c r="C21" s="85"/>
       <c r="D21" s="85"/>
@@ -21952,7 +22082,7 @@
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="91"/>
       <c r="C22" s="85"/>
       <c r="D22" s="85"/>
@@ -21965,7 +22095,7 @@
       <c r="N22" s="71"/>
       <c r="O22" s="72"/>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="91"/>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -21978,7 +22108,7 @@
       <c r="N23" s="71"/>
       <c r="O23" s="72"/>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="91"/>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -21991,7 +22121,7 @@
       <c r="N24" s="71"/>
       <c r="O24" s="72"/>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="91"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -22004,7 +22134,7 @@
       <c r="N25" s="71"/>
       <c r="O25" s="72"/>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="91"/>
       <c r="C26" s="85"/>
       <c r="D26" s="85"/>
@@ -22017,7 +22147,7 @@
       <c r="N26" s="71"/>
       <c r="O26" s="72"/>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="91"/>
       <c r="C27" s="85"/>
       <c r="D27" s="85"/>
@@ -22030,7 +22160,7 @@
       <c r="N27" s="71"/>
       <c r="O27" s="72"/>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="91"/>
       <c r="C28" s="85"/>
       <c r="D28" s="85"/>
@@ -22043,7 +22173,7 @@
       <c r="N28" s="71"/>
       <c r="O28" s="72"/>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="91"/>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -22056,7 +22186,7 @@
       <c r="N29" s="71"/>
       <c r="O29" s="72"/>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="91"/>
       <c r="C30" s="85"/>
       <c r="D30" s="85"/>
@@ -22069,7 +22199,7 @@
       <c r="N30" s="71"/>
       <c r="O30" s="72"/>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="91"/>
       <c r="C31" s="85"/>
       <c r="D31" s="85"/>
@@ -22082,7 +22212,7 @@
       <c r="N31" s="71"/>
       <c r="O31" s="72"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="91"/>
       <c r="C32" s="85"/>
       <c r="D32" s="85"/>
@@ -22095,7 +22225,7 @@
       <c r="N32" s="71"/>
       <c r="O32" s="72"/>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="91"/>
       <c r="C33" s="85"/>
       <c r="D33" s="85"/>
@@ -22108,7 +22238,7 @@
       <c r="N33" s="71"/>
       <c r="O33" s="72"/>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="91"/>
       <c r="C34" s="85"/>
       <c r="D34" s="85"/>
@@ -22121,7 +22251,7 @@
       <c r="N34" s="71"/>
       <c r="O34" s="72"/>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="91"/>
       <c r="C35" s="85"/>
       <c r="D35" s="85"/>
@@ -22134,7 +22264,7 @@
       <c r="N35" s="71"/>
       <c r="O35" s="72"/>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="91"/>
       <c r="C36" s="85"/>
       <c r="D36" s="85"/>
@@ -22147,7 +22277,7 @@
       <c r="N36" s="76"/>
       <c r="O36" s="72"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1">
+    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="91"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
@@ -22160,7 +22290,7 @@
       <c r="N37" s="77"/>
       <c r="O37" s="78"/>
     </row>
-    <row r="38" spans="2:15" ht="15.75" thickBot="1">
+    <row r="38" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="91"/>
       <c r="C38" s="85"/>
       <c r="D38" s="85"/>
@@ -22178,7 +22308,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="15.75" thickBot="1">
+    <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="91"/>
       <c r="C39" s="85"/>
       <c r="D39" s="85"/>
@@ -22189,7 +22319,7 @@
       <c r="I39" s="75"/>
       <c r="J39" s="92"/>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1">
+    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="91"/>
       <c r="C40" s="85"/>
       <c r="D40" s="85"/>
@@ -22200,14 +22330,14 @@
       <c r="I40" s="75"/>
       <c r="J40" s="92"/>
       <c r="N40" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O40" s="67">
         <f>Morrón!Q2</f>
         <v>838</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1">
+    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="91"/>
       <c r="C41" s="85"/>
       <c r="D41" s="85"/>
@@ -22218,7 +22348,7 @@
       <c r="I41" s="75"/>
       <c r="J41" s="92"/>
     </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1">
+    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="91"/>
       <c r="C42" s="85"/>
       <c r="D42" s="85"/>
@@ -22229,14 +22359,14 @@
       <c r="I42" s="75"/>
       <c r="J42" s="92"/>
       <c r="N42" s="66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O42" s="67">
         <f>+Morrón!R2</f>
         <v>7542</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1">
+    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="91"/>
       <c r="C43" s="85"/>
       <c r="D43" s="85"/>
@@ -22247,7 +22377,7 @@
       <c r="I43" s="75"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1">
+    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="91"/>
       <c r="C44" s="85"/>
       <c r="D44" s="85"/>
@@ -22258,14 +22388,14 @@
       <c r="I44" s="75"/>
       <c r="J44" s="92"/>
       <c r="N44" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="45" spans="2:15">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="91"/>
       <c r="C45" s="85"/>
       <c r="D45" s="85"/>
@@ -22276,7 +22406,7 @@
       <c r="I45" s="75"/>
       <c r="J45" s="92"/>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="91"/>
       <c r="C46" s="85"/>
       <c r="D46" s="85"/>
@@ -22288,7 +22418,7 @@
       <c r="J46" s="92"/>
       <c r="O46" s="79"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="85"/>
@@ -22299,7 +22429,7 @@
       <c r="I47" s="75"/>
       <c r="J47" s="92"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="85"/>
@@ -22311,7 +22441,7 @@
       <c r="J48" s="92"/>
       <c r="O48" s="80"/>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="85"/>
@@ -22323,7 +22453,7 @@
       <c r="J49" s="92"/>
       <c r="O49" s="80"/>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
       <c r="D50" s="85"/>
@@ -22335,7 +22465,7 @@
       <c r="J50" s="92"/>
       <c r="O50" s="80"/>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
       <c r="D51" s="85"/>
@@ -22348,7 +22478,7 @@
       <c r="O51" s="80"/>
       <c r="P51" s="80"/>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
       <c r="D52" s="85"/>
@@ -22361,7 +22491,7 @@
       <c r="O52" s="80"/>
       <c r="P52" s="80"/>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
       <c r="D53" s="85"/>
@@ -22372,7 +22502,7 @@
       <c r="I53" s="75"/>
       <c r="J53" s="92"/>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
       <c r="D54" s="85"/>
@@ -22385,7 +22515,7 @@
       <c r="O54" s="80"/>
       <c r="P54" s="80"/>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
       <c r="D55" s="85"/>
@@ -22398,7 +22528,7 @@
       <c r="O55" s="80"/>
       <c r="P55" s="80"/>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
       <c r="D56" s="85"/>
@@ -22409,7 +22539,7 @@
       <c r="I56" s="75"/>
       <c r="J56" s="92"/>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="24"/>
       <c r="C57" s="25"/>
       <c r="D57" s="85"/>
@@ -22420,7 +22550,7 @@
       <c r="I57" s="75"/>
       <c r="J57" s="92"/>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="24"/>
       <c r="C58" s="25"/>
       <c r="D58" s="85"/>
@@ -22431,7 +22561,7 @@
       <c r="I58" s="75"/>
       <c r="J58" s="92"/>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="24"/>
       <c r="C59" s="25"/>
       <c r="D59" s="85"/>
@@ -22442,7 +22572,7 @@
       <c r="I59" s="75"/>
       <c r="J59" s="92"/>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="24"/>
       <c r="C60" s="25"/>
       <c r="D60" s="85"/>
@@ -22453,7 +22583,7 @@
       <c r="I60" s="75"/>
       <c r="J60" s="92"/>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="85"/>
@@ -22464,7 +22594,7 @@
       <c r="I61" s="75"/>
       <c r="J61" s="92"/>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="85"/>
@@ -22475,7 +22605,7 @@
       <c r="I62" s="75"/>
       <c r="J62" s="92"/>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="24"/>
       <c r="C63" s="25"/>
       <c r="D63" s="85"/>
@@ -22486,7 +22616,7 @@
       <c r="I63" s="75"/>
       <c r="J63" s="92"/>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="24"/>
       <c r="C64" s="25"/>
       <c r="D64" s="85"/>
@@ -22497,7 +22627,7 @@
       <c r="I64" s="75"/>
       <c r="J64" s="92"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="24"/>
       <c r="C65" s="25"/>
       <c r="D65" s="85"/>
@@ -22508,7 +22638,7 @@
       <c r="I65" s="75"/>
       <c r="J65" s="92"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="85"/>
@@ -22519,7 +22649,7 @@
       <c r="I66" s="75"/>
       <c r="J66" s="92"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="24"/>
       <c r="C67" s="25"/>
       <c r="D67" s="85"/>
@@ -22530,7 +22660,7 @@
       <c r="I67" s="75"/>
       <c r="J67" s="92"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="24"/>
       <c r="C68" s="25"/>
       <c r="D68" s="85"/>
@@ -22541,7 +22671,7 @@
       <c r="I68" s="75"/>
       <c r="J68" s="92"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="24"/>
       <c r="C69" s="25"/>
       <c r="D69" s="85"/>
@@ -22552,7 +22682,7 @@
       <c r="I69" s="75"/>
       <c r="J69" s="92"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="24"/>
       <c r="C70" s="25"/>
       <c r="D70" s="85"/>
@@ -22563,7 +22693,7 @@
       <c r="I70" s="75"/>
       <c r="J70" s="92"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
       <c r="D71" s="85"/>
@@ -22574,7 +22704,7 @@
       <c r="I71" s="75"/>
       <c r="J71" s="92"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="24"/>
       <c r="C72" s="25"/>
       <c r="D72" s="85"/>
@@ -22585,7 +22715,7 @@
       <c r="I72" s="75"/>
       <c r="J72" s="92"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="24"/>
       <c r="C73" s="25"/>
       <c r="D73" s="85"/>
@@ -22596,7 +22726,7 @@
       <c r="I73" s="75"/>
       <c r="J73" s="98"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="24"/>
       <c r="C74" s="25"/>
       <c r="D74" s="85"/>
@@ -22607,7 +22737,7 @@
       <c r="I74" s="75"/>
       <c r="J74" s="92"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="85"/>
@@ -22618,7 +22748,7 @@
       <c r="I75" s="75"/>
       <c r="J75" s="98"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="85"/>
@@ -22629,7 +22759,7 @@
       <c r="I76" s="75"/>
       <c r="J76" s="92"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="24"/>
       <c r="C77" s="25"/>
       <c r="D77" s="85"/>
@@ -22640,7 +22770,7 @@
       <c r="I77" s="75"/>
       <c r="J77" s="92"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="24"/>
       <c r="C78" s="25"/>
       <c r="D78" s="85"/>
@@ -22651,7 +22781,7 @@
       <c r="I78" s="75"/>
       <c r="J78" s="92"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="24"/>
       <c r="C79" s="25"/>
       <c r="D79" s="85"/>
@@ -22662,7 +22792,7 @@
       <c r="I79" s="75"/>
       <c r="J79" s="92"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="24"/>
       <c r="C80" s="25"/>
       <c r="D80" s="85"/>
@@ -22673,7 +22803,7 @@
       <c r="I80" s="75"/>
       <c r="J80" s="92"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="24"/>
       <c r="C81" s="25"/>
       <c r="D81" s="85"/>
@@ -22684,7 +22814,7 @@
       <c r="I81" s="75"/>
       <c r="J81" s="92"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="24"/>
       <c r="C82" s="25"/>
       <c r="D82" s="85"/>
@@ -22695,7 +22825,7 @@
       <c r="I82" s="75"/>
       <c r="J82" s="92"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="24"/>
       <c r="C83" s="25"/>
       <c r="D83" s="85"/>
@@ -22706,7 +22836,7 @@
       <c r="I83" s="75"/>
       <c r="J83" s="92"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="24"/>
       <c r="C84" s="25"/>
       <c r="D84" s="85"/>
@@ -22717,7 +22847,7 @@
       <c r="I84" s="75"/>
       <c r="J84" s="92"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="24"/>
       <c r="C85" s="25"/>
       <c r="D85" s="85"/>
@@ -22728,7 +22858,7 @@
       <c r="I85" s="75"/>
       <c r="J85" s="92"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="24"/>
       <c r="C86" s="25"/>
       <c r="D86" s="85"/>
@@ -22739,7 +22869,7 @@
       <c r="I86" s="75"/>
       <c r="J86" s="92"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="85"/>
@@ -22750,7 +22880,7 @@
       <c r="I87" s="75"/>
       <c r="J87" s="92"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="85"/>
@@ -22761,7 +22891,7 @@
       <c r="I88" s="75"/>
       <c r="J88" s="92"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="85"/>
@@ -22772,7 +22902,7 @@
       <c r="I89" s="75"/>
       <c r="J89" s="92"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="85"/>
@@ -22783,7 +22913,7 @@
       <c r="I90" s="75"/>
       <c r="J90" s="92"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="24"/>
       <c r="C91" s="25"/>
       <c r="D91" s="85"/>
@@ -22794,7 +22924,7 @@
       <c r="I91" s="75"/>
       <c r="J91" s="92"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="24"/>
       <c r="C92" s="85"/>
       <c r="D92" s="85"/>
@@ -22805,7 +22935,7 @@
       <c r="I92" s="75"/>
       <c r="J92" s="92"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="24"/>
       <c r="C93" s="85"/>
       <c r="D93" s="85"/>
@@ -22816,7 +22946,7 @@
       <c r="I93" s="75"/>
       <c r="J93" s="92"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="24"/>
       <c r="C94" s="85"/>
       <c r="D94" s="85"/>
@@ -22827,7 +22957,7 @@
       <c r="I94" s="75"/>
       <c r="J94" s="92"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="24"/>
       <c r="C95" s="85"/>
       <c r="D95" s="85"/>
@@ -22838,7 +22968,7 @@
       <c r="I95" s="75"/>
       <c r="J95" s="92"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="24"/>
       <c r="C96" s="85"/>
       <c r="D96" s="85"/>
@@ -22849,7 +22979,7 @@
       <c r="I96" s="75"/>
       <c r="J96" s="92"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="91"/>
       <c r="C97" s="85"/>
       <c r="D97" s="85"/>
@@ -22860,7 +22990,7 @@
       <c r="I97" s="75"/>
       <c r="J97" s="94"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="91"/>
       <c r="C98" s="85"/>
       <c r="D98" s="85"/>
@@ -22871,7 +23001,7 @@
       <c r="I98" s="75"/>
       <c r="J98" s="92"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="91"/>
       <c r="C99" s="85"/>
       <c r="D99" s="85"/>
@@ -22882,7 +23012,7 @@
       <c r="I99" s="75"/>
       <c r="J99" s="92"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="91"/>
       <c r="C100" s="85"/>
       <c r="D100" s="85"/>
@@ -22893,7 +23023,7 @@
       <c r="I100" s="75"/>
       <c r="J100" s="92"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="91"/>
       <c r="C101" s="85"/>
       <c r="D101" s="85"/>
@@ -22904,7 +23034,7 @@
       <c r="I101" s="75"/>
       <c r="J101" s="92"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="91"/>
       <c r="C102" s="85"/>
       <c r="D102" s="85"/>
@@ -22915,7 +23045,7 @@
       <c r="I102" s="75"/>
       <c r="J102" s="94"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="91"/>
       <c r="C103" s="85"/>
       <c r="D103" s="85"/>
@@ -22926,7 +23056,7 @@
       <c r="I103" s="75"/>
       <c r="J103" s="92"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="91"/>
       <c r="C104" s="85"/>
       <c r="D104" s="85"/>
@@ -22937,7 +23067,7 @@
       <c r="I104" s="75"/>
       <c r="J104" s="92"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="91"/>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
@@ -22956,7 +23086,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFCC301-F59E-4EF9-AD64-E57A9E70782E}">
   <dimension ref="D2:O12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
@@ -22972,12 +23102,12 @@
     <col min="15" max="15" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:15" ht="30">
+    <row r="2" spans="4:15" ht="30" x14ac:dyDescent="0.25">
       <c r="D2" s="169" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="4:15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E3" s="47"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -22987,37 +23117,37 @@
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
     </row>
-    <row r="4" spans="4:15" ht="23.25" customHeight="1">
+    <row r="4" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="170" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="170" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="170" t="s">
+      <c r="G4" s="170" t="s">
         <v>98</v>
-      </c>
-      <c r="G4" s="170" t="s">
-        <v>99</v>
       </c>
       <c r="H4" s="170"/>
       <c r="I4" s="170" t="s">
+        <v>99</v>
+      </c>
+      <c r="J4" s="170" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="170" t="s">
+      <c r="K4" s="170" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="170" t="s">
+      <c r="L4" s="47"/>
+      <c r="M4" s="181" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="47"/>
-      <c r="M4" s="182" t="s">
+      <c r="N4" s="181" t="s">
         <v>103</v>
       </c>
-      <c r="N4" s="182" t="s">
+    </row>
+    <row r="5" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="4:15" ht="23.25" customHeight="1">
-      <c r="D5" t="s">
-        <v>105</v>
       </c>
       <c r="E5" s="167">
         <f>+Tomatillo!O2</f>
@@ -23052,13 +23182,13 @@
         <v>671683</v>
       </c>
     </row>
-    <row r="6" spans="4:15" ht="23.25" customHeight="1">
+    <row r="6" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E6" s="167">
         <f>+Roma!O2</f>
-        <v>864923.07000000007</v>
+        <v>1010773.0700000001</v>
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
@@ -23066,32 +23196,32 @@
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>162678.07000000007</v>
+        <v>308528.07000000007</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
         <f>+Roma!Q2</f>
-        <v>86492.307000000001</v>
+        <v>101077.307</v>
       </c>
       <c r="J6" s="167">
         <v>11968</v>
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>88153.763000000064</v>
+        <v>219418.76300000006</v>
       </c>
       <c r="M6" s="166">
         <f t="shared" ref="M6:M8" si="1">E6-I6</f>
-        <v>778430.76300000004</v>
+        <v>909695.76300000004</v>
       </c>
       <c r="N6" s="166">
         <f t="shared" ref="N6:N8" si="2">F6-J6</f>
         <v>690277</v>
       </c>
     </row>
-    <row r="7" spans="4:15" ht="23.25" customHeight="1">
+    <row r="7" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E7" s="167">
         <f>+Morrón!O2</f>
@@ -23126,7 +23256,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="8" spans="4:15" ht="23.25" customHeight="1">
+    <row r="8" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
       <c r="G8" s="171"/>
@@ -23143,10 +23273,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="4:15" ht="23.25" customHeight="1">
+    <row r="9" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="168">
         <f>SUM(E5:E8)</f>
-        <v>1930241.6300000001</v>
+        <v>2076091.6300000001</v>
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
@@ -23154,12 +23284,12 @@
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>490184.63000000012</v>
+        <v>636034.63000000012</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
         <f>SUM(I5:I8)</f>
-        <v>180039.97100000002</v>
+        <v>194624.97100000002</v>
       </c>
       <c r="J9" s="168">
         <f>SUM(J5:J8)</f>
@@ -23167,22 +23297,22 @@
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>382261.6590000001</v>
-      </c>
-      <c r="M9" s="181">
+        <v>513526.6590000001</v>
+      </c>
+      <c r="M9" s="180">
         <f t="shared" ref="M9:N9" si="3">E9-I9</f>
-        <v>1750201.659</v>
-      </c>
-      <c r="N9" s="181">
+        <v>1881466.659</v>
+      </c>
+      <c r="N9" s="180">
         <f t="shared" si="3"/>
         <v>1367940</v>
       </c>
       <c r="O9" s="166">
         <f>M9-N9</f>
-        <v>382261.65899999999</v>
-      </c>
-    </row>
-    <row r="10" spans="4:15" ht="23.25" customHeight="1">
+        <v>513526.65899999999</v>
+      </c>
+    </row>
+    <row r="10" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="167"/>
       <c r="F10" s="167"/>
       <c r="G10" s="167"/>
@@ -23192,26 +23322,26 @@
       <c r="K10" s="166"/>
       <c r="L10" s="167"/>
     </row>
-    <row r="11" spans="4:15" ht="23.25" customHeight="1">
+    <row r="11" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="167"/>
       <c r="F11" s="167"/>
       <c r="G11" s="167"/>
       <c r="H11" s="167"/>
       <c r="I11" s="167">
         <f>+I9-J9</f>
-        <v>107922.97100000002</v>
+        <v>122507.97100000002</v>
       </c>
       <c r="J11" s="167"/>
       <c r="K11" s="166"/>
       <c r="L11" s="167"/>
     </row>
-    <row r="12" spans="4:15">
+    <row r="12" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E12" s="167"/>
       <c r="F12" s="167"/>
       <c r="G12" s="167"/>
       <c r="H12" s="167"/>
       <c r="I12" s="167" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J12" s="167"/>
       <c r="K12" s="166"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1743" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE5D679-4362-4019-82EF-9D7CFBB037CA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="4" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>

--- a/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
+++ b/Info para Claude/Reportes/Nacional/Ventas CBE-H2E 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64c979621066deb/Comercial Batiz Esquer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1743" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE5D679-4362-4019-82EF-9D7CFBB037CA}"/>
+  <xr:revisionPtr revIDLastSave="1753" documentId="8_{101B3648-96E3-491A-B0FE-FBAE7237A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{160E76A9-692F-428D-88FA-CC0201BE1AB5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{8B7D4835-F937-4749-8FAF-12E1D8931F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tomatillo" sheetId="1" r:id="rId1"/>
@@ -19831,11 +19831,11 @@
       </c>
       <c r="J2" s="148">
         <f>O38</f>
-        <v>702245</v>
+        <v>848095</v>
       </c>
       <c r="K2" s="55">
         <f>O44</f>
-        <v>308528.07000000007</v>
+        <v>162678.07000000007</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>39</v>
@@ -20215,8 +20215,12 @@
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="79"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="72"/>
+      <c r="N11" s="71">
+        <v>46158</v>
+      </c>
+      <c r="O11" s="72">
+        <v>145850</v>
+      </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="173">
@@ -20486,112 +20490,112 @@
       <c r="O18" s="72"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="91">
+      <c r="B19" s="173">
         <f>Roma!B20</f>
         <v>46156</v>
       </c>
-      <c r="C19" s="85">
+      <c r="C19" s="113">
         <f>Roma!C20</f>
         <v>50</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="85" t="str">
+      <c r="E19" s="113" t="str">
         <f>Roma!E20</f>
         <v>Julio Mendoza</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="174">
         <f>Roma!H20</f>
         <v>38</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="115">
         <f>Roma!K20</f>
         <v>202.63157894736841</v>
       </c>
-      <c r="H19" s="84">
-        <v>0</v>
-      </c>
-      <c r="I19" s="75">
+      <c r="H19" s="111">
+        <v>0</v>
+      </c>
+      <c r="I19" s="115">
         <f t="shared" ref="I19" si="6">F19*G19-H19</f>
         <v>7700</v>
       </c>
-      <c r="J19" s="94" t="s">
-        <v>56</v>
+      <c r="J19" s="138" t="s">
+        <v>47</v>
       </c>
       <c r="N19" s="71"/>
       <c r="O19" s="72"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="91">
+      <c r="B20" s="173">
         <f>Roma!B21</f>
         <v>46157</v>
       </c>
-      <c r="C20" s="85">
+      <c r="C20" s="113">
         <f>Roma!C21</f>
         <v>51</v>
       </c>
-      <c r="D20" s="85" t="s">
+      <c r="D20" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="85" t="str">
+      <c r="E20" s="113" t="str">
         <f>Roma!E21</f>
         <v>Samuel Cuadras</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="174">
         <f>Roma!H21</f>
         <v>30</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="115">
         <f>Roma!K21</f>
         <v>380</v>
       </c>
-      <c r="H20" s="84">
-        <v>0</v>
-      </c>
-      <c r="I20" s="75">
+      <c r="H20" s="111">
+        <v>0</v>
+      </c>
+      <c r="I20" s="115">
         <f t="shared" ref="I20" si="7">F20*G20-H20</f>
         <v>11400</v>
       </c>
-      <c r="J20" s="94" t="s">
-        <v>56</v>
+      <c r="J20" s="138" t="s">
+        <v>47</v>
       </c>
       <c r="N20" s="71"/>
       <c r="O20" s="72"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="91">
+      <c r="B21" s="173">
         <f>Roma!B22</f>
         <v>46157</v>
       </c>
-      <c r="C21" s="85">
+      <c r="C21" s="113">
         <f>Roma!C22</f>
         <v>52</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="85" t="str">
+      <c r="E21" s="113" t="str">
         <f>Roma!E22</f>
         <v>Efrén Medina</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="174">
         <f>Roma!H22</f>
         <v>365</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="115">
         <f>Roma!K22</f>
         <v>347.26027397260276</v>
       </c>
-      <c r="H21" s="84">
-        <v>0</v>
-      </c>
-      <c r="I21" s="75">
+      <c r="H21" s="111">
+        <v>0</v>
+      </c>
+      <c r="I21" s="115">
         <f t="shared" ref="I21" si="8">F21*G21-H21</f>
         <v>126750.00000000001</v>
       </c>
-      <c r="J21" s="94" t="s">
-        <v>56</v>
+      <c r="J21" s="138" t="s">
+        <v>47</v>
       </c>
       <c r="N21" s="71"/>
       <c r="O21" s="72"/>
@@ -20819,7 +20823,7 @@
       </c>
       <c r="O38" s="67">
         <f>SUM(O4:O37)</f>
-        <v>702245</v>
+        <v>848095</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20906,7 +20910,7 @@
       </c>
       <c r="O44" s="67">
         <f>+O42+O40-O38</f>
-        <v>308528.07000000007</v>
+        <v>162678.07000000007</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
@@ -23167,11 +23171,11 @@
         <v>92709.664000000019</v>
       </c>
       <c r="J5" s="167">
-        <v>60149</v>
+        <v>73196</v>
       </c>
       <c r="K5" s="167">
         <f>+G5-I5+J5</f>
-        <v>292545.89600000007</v>
+        <v>305592.89600000007</v>
       </c>
       <c r="M5" s="166">
         <f>E5-I5</f>
@@ -23179,7 +23183,7 @@
       </c>
       <c r="N5" s="166">
         <f>F5-J5</f>
-        <v>671683</v>
+        <v>658636</v>
       </c>
     </row>
     <row r="6" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -23192,11 +23196,11 @@
       </c>
       <c r="F6" s="167">
         <f>+'Estado de Cuenta R'!O38</f>
-        <v>702245</v>
+        <v>848095</v>
       </c>
       <c r="G6" s="171">
         <f>+E6-F6</f>
-        <v>308528.07000000007</v>
+        <v>162678.07000000007</v>
       </c>
       <c r="H6" s="167"/>
       <c r="I6" s="167">
@@ -23204,11 +23208,11 @@
         <v>101077.307</v>
       </c>
       <c r="J6" s="167">
-        <v>11968</v>
+        <v>84809</v>
       </c>
       <c r="K6" s="167">
         <f t="shared" ref="K6:K7" si="0">+G6-I6+J6</f>
-        <v>219418.76300000006</v>
+        <v>146409.76300000006</v>
       </c>
       <c r="M6" s="166">
         <f t="shared" ref="M6:M8" si="1">E6-I6</f>
@@ -23216,7 +23220,7 @@
       </c>
       <c r="N6" s="166">
         <f t="shared" ref="N6:N8" si="2">F6-J6</f>
-        <v>690277</v>
+        <v>763286</v>
       </c>
     </row>
     <row r="7" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -23241,11 +23245,11 @@
         <v>838</v>
       </c>
       <c r="J7" s="167">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="K7" s="167">
         <f t="shared" si="0"/>
-        <v>1562</v>
+        <v>2160</v>
       </c>
       <c r="M7" s="166">
         <f t="shared" si="1"/>
@@ -23253,7 +23257,7 @@
       </c>
       <c r="N7" s="166">
         <f t="shared" si="2"/>
-        <v>5980</v>
+        <v>5382</v>
       </c>
     </row>
     <row r="8" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -23280,11 +23284,11 @@
       </c>
       <c r="F9" s="168">
         <f>SUM(F5:F8)</f>
-        <v>1440057</v>
+        <v>1585907</v>
       </c>
       <c r="G9" s="172">
         <f>SUM(G5:G8)</f>
-        <v>636034.63000000012</v>
+        <v>490184.63000000012</v>
       </c>
       <c r="H9" s="168"/>
       <c r="I9" s="168">
@@ -23293,11 +23297,11 @@
       </c>
       <c r="J9" s="168">
         <f>SUM(J5:J8)</f>
-        <v>72117</v>
+        <v>158603</v>
       </c>
       <c r="K9" s="168">
         <f>+G9-I9+J9</f>
-        <v>513526.6590000001</v>
+        <v>454162.6590000001</v>
       </c>
       <c r="M9" s="180">
         <f t="shared" ref="M9:N9" si="3">E9-I9</f>
@@ -23305,11 +23309,11 @@
       </c>
       <c r="N9" s="180">
         <f t="shared" si="3"/>
-        <v>1367940</v>
+        <v>1427304</v>
       </c>
       <c r="O9" s="166">
         <f>M9-N9</f>
-        <v>513526.65899999999</v>
+        <v>454162.65899999999</v>
       </c>
     </row>
     <row r="10" spans="4:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -23329,7 +23333,7 @@
       <c r="H11" s="167"/>
       <c r="I11" s="167">
         <f>+I9-J9</f>
-        <v>122507.97100000002</v>
+        <v>36021.97100000002</v>
       </c>
       <c r="J11" s="167"/>
       <c r="K11" s="166"/>
